--- a/WVS_Dataset/WVS7_Country.xlsx
+++ b/WVS_Dataset/WVS7_Country.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD67"/>
+  <dimension ref="A1:AA67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,140 +367,125 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Q167.Yes</t>
+          <t>Q167</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Q167.No</t>
+          <t>Q177</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Q177</t>
+          <t>Q178</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Q178</t>
+          <t>Q179</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Q179</t>
+          <t>Q180</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Q180</t>
+          <t>Q181</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Q181</t>
+          <t>Q182</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Q182</t>
+          <t>Q183</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Q183</t>
+          <t>Q184</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Q184</t>
+          <t>Q185</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Q185</t>
+          <t>Q186</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Q186</t>
+          <t>Q187</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Q187</t>
+          <t>Q188</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Q188</t>
+          <t>Q189</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Q189</t>
+          <t>Q190</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Q190</t>
+          <t>Q191</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Q191</t>
+          <t>Q192</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Q192</t>
+          <t>Q193</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Q193</t>
+          <t>Q194</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Q194</t>
+          <t>Q195</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Q195</t>
+          <t>Q260</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Q260.Male</t>
+          <t>Q262</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Q260.Female</t>
+          <t>Q263</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Q262</t>
+          <t>Q275</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Q263.I_am_born_in_this_country</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Q263.I_am_an_immigrant_to_this_country_born_outside_this_country</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Q275</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Q288</t>
         </is>
@@ -521,84 +506,75 @@
         <v>0.2678751258811682</v>
       </c>
       <c r="D2">
-        <v>0.7321248741188319</v>
+        <v>1.998996990972919</v>
       </c>
       <c r="E2">
-        <v>1.998996990972919</v>
+        <v>1.888223552894212</v>
       </c>
       <c r="F2">
-        <v>1.888223552894212</v>
+        <v>1.505483549351944</v>
       </c>
       <c r="G2">
-        <v>1.505483549351944</v>
+        <v>1.676323676323676</v>
       </c>
       <c r="H2">
-        <v>1.676323676323676</v>
+        <v>1.305694305694306</v>
       </c>
       <c r="I2">
-        <v>1.305694305694306</v>
+        <v>8.025025025025025</v>
       </c>
       <c r="J2">
-        <v>8.025025025025025</v>
+        <v>4.734939759036145</v>
       </c>
       <c r="K2">
-        <v>4.734939759036145</v>
+        <v>6.074074074074074</v>
       </c>
       <c r="L2">
-        <v>6.074074074074074</v>
+        <v>8.244</v>
       </c>
       <c r="M2">
-        <v>8.244</v>
+        <v>8.191767068273093</v>
       </c>
       <c r="N2">
-        <v>8.191767068273093</v>
+        <v>3.638</v>
       </c>
       <c r="O2">
-        <v>3.638</v>
+        <v>6.186304128902316</v>
       </c>
       <c r="P2">
-        <v>6.186304128902316</v>
+        <v>1.203796203796204</v>
       </c>
       <c r="Q2">
-        <v>1.203796203796204</v>
+        <v>1.690927218344965</v>
       </c>
       <c r="R2">
-        <v>1.690927218344965</v>
+        <v>1.296407185628742</v>
       </c>
       <c r="S2">
-        <v>1.296407185628742</v>
+        <v>1.124</v>
       </c>
       <c r="T2">
-        <v>1.124</v>
+        <v>5.68505516549649</v>
       </c>
       <c r="U2">
-        <v>5.68505516549649</v>
+        <v>1.337662337662338</v>
       </c>
       <c r="V2">
-        <v>1.337662337662338</v>
+        <v>3.396603396603397</v>
       </c>
       <c r="W2">
-        <v>3.396603396603397</v>
+        <v>0.5069721115537849</v>
       </c>
       <c r="X2">
-        <v>0.5069721115537849</v>
+        <v>46.82569721115538</v>
       </c>
       <c r="Y2">
-        <v>0.4930278884462151</v>
+        <v>0.2768924302788844</v>
       </c>
       <c r="Z2">
-        <v>46.82569721115538</v>
+        <v>4.856430707876371</v>
       </c>
       <c r="AA2">
-        <v>0.2768924302788844</v>
-      </c>
-      <c r="AB2">
-        <v>0.7231075697211156</v>
-      </c>
-      <c r="AC2">
-        <v>4.856430707876371</v>
-      </c>
-      <c r="AD2">
         <v>5.355605889014723</v>
       </c>
     </row>
@@ -617,84 +593,75 @@
         <v>0.5277185501066098</v>
       </c>
       <c r="D3">
-        <v>0.4722814498933902</v>
+        <v>4.559877175025589</v>
       </c>
       <c r="E3">
-        <v>4.559877175025589</v>
+        <v>3.049645390070922</v>
       </c>
       <c r="F3">
-        <v>3.049645390070922</v>
+        <v>1.7293997965412</v>
       </c>
       <c r="G3">
-        <v>1.7293997965412</v>
+        <v>2.141116751269036</v>
       </c>
       <c r="H3">
-        <v>2.141116751269036</v>
+        <v>1.875757575757576</v>
       </c>
       <c r="I3">
-        <v>1.875757575757576</v>
+        <v>6.023411371237458</v>
       </c>
       <c r="J3">
-        <v>6.023411371237458</v>
+        <v>3.919477693144723</v>
       </c>
       <c r="K3">
-        <v>3.919477693144723</v>
+        <v>3.630252100840336</v>
       </c>
       <c r="L3">
-        <v>3.630252100840336</v>
+        <v>6.530590717299578</v>
       </c>
       <c r="M3">
-        <v>6.530590717299578</v>
+        <v>6.739084132055378</v>
       </c>
       <c r="N3">
-        <v>6.739084132055378</v>
+        <v>2.662740899357602</v>
       </c>
       <c r="O3">
-        <v>2.662740899357602</v>
+        <v>3.857634902411022</v>
       </c>
       <c r="P3">
-        <v>3.857634902411022</v>
+        <v>1.440320962888666</v>
       </c>
       <c r="Q3">
-        <v>1.440320962888666</v>
+        <v>1.944723618090452</v>
       </c>
       <c r="R3">
-        <v>1.944723618090452</v>
+        <v>1.725806451612903</v>
       </c>
       <c r="S3">
-        <v>1.725806451612903</v>
+        <v>1.606924643584521</v>
       </c>
       <c r="T3">
-        <v>1.606924643584521</v>
+        <v>5.269602577873255</v>
       </c>
       <c r="U3">
-        <v>5.269602577873255</v>
+        <v>1.858617131062952</v>
       </c>
       <c r="V3">
-        <v>1.858617131062952</v>
+        <v>3.383575883575884</v>
       </c>
       <c r="W3">
-        <v>3.383575883575884</v>
+        <v>0.4835493519441675</v>
       </c>
       <c r="X3">
-        <v>0.4835493519441675</v>
+        <v>42.55134596211366</v>
       </c>
       <c r="Y3">
-        <v>0.5164506480558325</v>
+        <v>0.9790628115653041</v>
       </c>
       <c r="Z3">
-        <v>42.55134596211366</v>
+        <v>3.735792622133599</v>
       </c>
       <c r="AA3">
-        <v>0.9790628115653041</v>
-      </c>
-      <c r="AB3">
-        <v>0.02093718843469591</v>
-      </c>
-      <c r="AC3">
-        <v>3.735792622133599</v>
-      </c>
-      <c r="AD3">
         <v>5.078616352201258</v>
       </c>
     </row>
@@ -713,84 +680,75 @@
         <v>0.4286995515695067</v>
       </c>
       <c r="D4">
-        <v>0.5713004484304933</v>
+        <v>1.863523573200992</v>
       </c>
       <c r="E4">
-        <v>1.863523573200992</v>
+        <v>1.408230452674897</v>
       </c>
       <c r="F4">
-        <v>1.408230452674897</v>
+        <v>1.136288998357964</v>
       </c>
       <c r="G4">
-        <v>1.136288998357964</v>
+        <v>1.665296052631579</v>
       </c>
       <c r="H4">
-        <v>1.665296052631579</v>
+        <v>1.281481481481481</v>
       </c>
       <c r="I4">
-        <v>1.281481481481481</v>
+        <v>1.372937293729373</v>
       </c>
       <c r="J4">
-        <v>1.372937293729373</v>
+        <v>1.360561056105611</v>
       </c>
       <c r="K4">
-        <v>1.360561056105611</v>
+        <v>2.485762144053601</v>
       </c>
       <c r="L4">
-        <v>2.485762144053601</v>
+        <v>3.611433305716653</v>
       </c>
       <c r="M4">
-        <v>3.611433305716653</v>
+        <v>2.494176372712146</v>
       </c>
       <c r="N4">
-        <v>2.494176372712146</v>
+        <v>1.313886606409203</v>
       </c>
       <c r="O4">
-        <v>1.313886606409203</v>
+        <v>2.460492778249788</v>
       </c>
       <c r="P4">
-        <v>2.460492778249788</v>
+        <v>1.246103363412633</v>
       </c>
       <c r="Q4">
-        <v>1.246103363412633</v>
+        <v>1.911330049261084</v>
       </c>
       <c r="R4">
-        <v>1.911330049261084</v>
+        <v>1.270114942528736</v>
       </c>
       <c r="S4">
-        <v>1.270114942528736</v>
+        <v>1.239202657807309</v>
       </c>
       <c r="T4">
-        <v>1.239202657807309</v>
+        <v>1.684297520661157</v>
       </c>
       <c r="U4">
-        <v>1.684297520661157</v>
+        <v>1.184755592377796</v>
       </c>
       <c r="V4">
-        <v>1.184755592377796</v>
+        <v>2.664739884393064</v>
       </c>
       <c r="W4">
-        <v>2.664739884393064</v>
+        <v>0.3139820114472608</v>
       </c>
       <c r="X4">
-        <v>0.3139820114472608</v>
+        <v>49.04415372035977</v>
       </c>
       <c r="Y4">
-        <v>0.6860179885527392</v>
+        <v>0.9351395730706076</v>
       </c>
       <c r="Z4">
-        <v>49.04415372035977</v>
+        <v>5.438683127572016</v>
       </c>
       <c r="AA4">
-        <v>0.9351395730706076</v>
-      </c>
-      <c r="AB4">
-        <v>0.06486042692939245</v>
-      </c>
-      <c r="AC4">
-        <v>5.438683127572016</v>
-      </c>
-      <c r="AD4">
         <v>4.702145214521452</v>
       </c>
     </row>
@@ -809,84 +767,75 @@
         <v>0.2846674182638106</v>
       </c>
       <c r="D5">
-        <v>0.7153325817361894</v>
+        <v>1.778953229398664</v>
       </c>
       <c r="E5">
-        <v>1.778953229398664</v>
+        <v>2.205701509223029</v>
       </c>
       <c r="F5">
-        <v>2.205701509223029</v>
+        <v>1.40133779264214</v>
       </c>
       <c r="G5">
-        <v>1.40133779264214</v>
+        <v>1.848687883863763</v>
       </c>
       <c r="H5">
-        <v>1.848687883863763</v>
+        <v>1.435025097601785</v>
       </c>
       <c r="I5">
-        <v>1.435025097601785</v>
+        <v>7.387720295622513</v>
       </c>
       <c r="J5">
-        <v>7.387720295622513</v>
+        <v>5.173371104815864</v>
       </c>
       <c r="K5">
-        <v>5.173371104815864</v>
+        <v>6.562323745064861</v>
       </c>
       <c r="L5">
-        <v>6.562323745064861</v>
+        <v>7.738270209157716</v>
       </c>
       <c r="M5">
-        <v>7.738270209157716</v>
+        <v>7.884659090909091</v>
       </c>
       <c r="N5">
-        <v>7.884659090909091</v>
+        <v>4.038439796495195</v>
       </c>
       <c r="O5">
-        <v>4.038439796495195</v>
+        <v>6.688775510204081</v>
       </c>
       <c r="P5">
-        <v>6.688775510204081</v>
+        <v>1.241340782122905</v>
       </c>
       <c r="Q5">
-        <v>1.241340782122905</v>
+        <v>1.608040201005025</v>
       </c>
       <c r="R5">
-        <v>1.608040201005025</v>
+        <v>1.595637583892617</v>
       </c>
       <c r="S5">
-        <v>1.595637583892617</v>
+        <v>1.321967579653438</v>
       </c>
       <c r="T5">
-        <v>1.321967579653438</v>
+        <v>6.078753541076487</v>
       </c>
       <c r="U5">
-        <v>6.078753541076487</v>
+        <v>1.711160964666293</v>
       </c>
       <c r="V5">
-        <v>1.711160964666293</v>
+        <v>4.453168816601234</v>
       </c>
       <c r="W5">
-        <v>4.453168816601234</v>
+        <v>0.3913285158421345</v>
       </c>
       <c r="X5">
-        <v>0.3913285158421345</v>
+        <v>54.2958217270195</v>
       </c>
       <c r="Y5">
-        <v>0.6086714841578654</v>
+        <v>0.9284525790349417</v>
       </c>
       <c r="Z5">
-        <v>54.2958217270195</v>
+        <v>5.655192197360872</v>
       </c>
       <c r="AA5">
-        <v>0.9284525790349417</v>
-      </c>
-      <c r="AB5">
-        <v>0.07154742096505824</v>
-      </c>
-      <c r="AC5">
-        <v>5.655192197360872</v>
-      </c>
-      <c r="AD5">
         <v>5.127574370709382</v>
       </c>
     </row>
@@ -905,84 +854,75 @@
         <v>0.9933166248955723</v>
       </c>
       <c r="D6">
-        <v>0.006683375104427736</v>
+        <v>2.024166666666666</v>
       </c>
       <c r="E6">
-        <v>2.024166666666666</v>
+        <v>1.800833333333333</v>
       </c>
       <c r="F6">
-        <v>1.800833333333333</v>
+        <v>1.554166666666667</v>
       </c>
       <c r="G6">
-        <v>1.554166666666667</v>
+        <v>1.700833333333333</v>
       </c>
       <c r="H6">
-        <v>1.700833333333333</v>
+        <v>1.6075</v>
       </c>
       <c r="I6">
-        <v>1.6075</v>
+        <v>1.6875</v>
       </c>
       <c r="J6">
-        <v>1.6875</v>
+        <v>1.6</v>
       </c>
       <c r="K6">
-        <v>1.6</v>
+        <v>2.021666666666667</v>
       </c>
       <c r="L6">
-        <v>2.021666666666667</v>
+        <v>2.17</v>
       </c>
       <c r="M6">
-        <v>2.17</v>
+        <v>1.505</v>
       </c>
       <c r="N6">
-        <v>1.505</v>
+        <v>1.9</v>
       </c>
       <c r="O6">
-        <v>1.9</v>
+        <v>2.7775</v>
       </c>
       <c r="P6">
-        <v>2.7775</v>
+        <v>1.915</v>
       </c>
       <c r="Q6">
-        <v>1.915</v>
+        <v>2.155833333333333</v>
       </c>
       <c r="R6">
-        <v>2.155833333333333</v>
+        <v>1.794166666666667</v>
       </c>
       <c r="S6">
-        <v>1.794166666666667</v>
+        <v>1.795</v>
       </c>
       <c r="T6">
-        <v>1.795</v>
+        <v>1.488333333333333</v>
       </c>
       <c r="U6">
-        <v>1.488333333333333</v>
+        <v>1.750833333333333</v>
       </c>
       <c r="V6">
-        <v>1.750833333333333</v>
+        <v>2.7525</v>
       </c>
       <c r="W6">
-        <v>2.7525</v>
+        <v>0.4933333333333333</v>
       </c>
       <c r="X6">
-        <v>0.4933333333333333</v>
+        <v>36.59083333333334</v>
       </c>
       <c r="Y6">
-        <v>0.5066666666666667</v>
+        <v>1</v>
       </c>
       <c r="Z6">
-        <v>36.59083333333334</v>
+        <v>2.853211009174312</v>
       </c>
       <c r="AA6">
-        <v>1</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>2.853211009174312</v>
-      </c>
-      <c r="AD6">
         <v>5.615</v>
       </c>
     </row>
@@ -1001,84 +941,75 @@
         <v>0.6122037317196167</v>
       </c>
       <c r="D7">
-        <v>0.3877962682803833</v>
+        <v>4.969046430354468</v>
       </c>
       <c r="E7">
-        <v>4.969046430354468</v>
+        <v>3.962162162162162</v>
       </c>
       <c r="F7">
-        <v>3.962162162162162</v>
+        <v>1.553779069767442</v>
       </c>
       <c r="G7">
-        <v>1.553779069767442</v>
+        <v>2.037745098039216</v>
       </c>
       <c r="H7">
-        <v>2.037745098039216</v>
+        <v>2.045767716535433</v>
       </c>
       <c r="I7">
-        <v>2.045767716535433</v>
+        <v>3.301595744680851</v>
       </c>
       <c r="J7">
-        <v>3.301595744680851</v>
+        <v>2.79938900203666</v>
       </c>
       <c r="K7">
-        <v>2.79938900203666</v>
+        <v>2.270628683693517</v>
       </c>
       <c r="L7">
-        <v>2.270628683693517</v>
+        <v>3.98416625432954</v>
       </c>
       <c r="M7">
-        <v>3.98416625432954</v>
+        <v>3.87871033776868</v>
       </c>
       <c r="N7">
-        <v>3.87871033776868</v>
+        <v>2.156979632389469</v>
       </c>
       <c r="O7">
-        <v>2.156979632389469</v>
+        <v>3.197695573074591</v>
       </c>
       <c r="P7">
-        <v>3.197695573074591</v>
+        <v>1.749027237354086</v>
       </c>
       <c r="Q7">
-        <v>1.749027237354086</v>
+        <v>2.599805258033106</v>
       </c>
       <c r="R7">
-        <v>2.599805258033106</v>
+        <v>2.003424657534246</v>
       </c>
       <c r="S7">
-        <v>2.003424657534246</v>
+        <v>1.923274974253347</v>
       </c>
       <c r="T7">
-        <v>1.923274974253347</v>
+        <v>2.623529411764706</v>
       </c>
       <c r="U7">
-        <v>2.623529411764706</v>
+        <v>2.05873568939771</v>
       </c>
       <c r="V7">
-        <v>2.05873568939771</v>
+        <v>3.649201596806387</v>
       </c>
       <c r="W7">
-        <v>3.649201596806387</v>
+        <v>0.4954039671020803</v>
       </c>
       <c r="X7">
-        <v>0.4954039671020803</v>
+        <v>38.33284954039671</v>
       </c>
       <c r="Y7">
-        <v>0.5045960328979197</v>
+        <v>0.9961259079903148</v>
       </c>
       <c r="Z7">
-        <v>38.33284954039671</v>
+        <v>4.350315380883067</v>
       </c>
       <c r="AA7">
-        <v>0.9961259079903148</v>
-      </c>
-      <c r="AB7">
-        <v>0.00387409200968523</v>
-      </c>
-      <c r="AC7">
-        <v>4.350315380883067</v>
-      </c>
-      <c r="AD7">
         <v>5.013412816691505</v>
       </c>
     </row>
@@ -1097,84 +1028,75 @@
         <v>0.6868437306979617</v>
       </c>
       <c r="D8">
-        <v>0.3131562693020383</v>
+        <v>2.437609841827768</v>
       </c>
       <c r="E8">
-        <v>2.437609841827768</v>
+        <v>3.547912992357437</v>
       </c>
       <c r="F8">
-        <v>3.547912992357437</v>
+        <v>1.521086077411901</v>
       </c>
       <c r="G8">
-        <v>1.521086077411901</v>
+        <v>2.995901639344262</v>
       </c>
       <c r="H8">
-        <v>2.995901639344262</v>
+        <v>1.574739281575898</v>
       </c>
       <c r="I8">
-        <v>1.574739281575898</v>
+        <v>4.946879150066401</v>
       </c>
       <c r="J8">
-        <v>4.946879150066401</v>
+        <v>3.211706102117061</v>
       </c>
       <c r="K8">
-        <v>3.211706102117061</v>
+        <v>2.506261180679785</v>
       </c>
       <c r="L8">
-        <v>2.506261180679785</v>
+        <v>6.221560452650387</v>
       </c>
       <c r="M8">
-        <v>6.221560452650387</v>
+        <v>5.915337423312883</v>
       </c>
       <c r="N8">
-        <v>5.915337423312883</v>
+        <v>2.054198927933294</v>
       </c>
       <c r="O8">
-        <v>2.054198927933294</v>
+        <v>3.196904024767802</v>
       </c>
       <c r="P8">
-        <v>3.196904024767802</v>
+        <v>1.374423963133641</v>
       </c>
       <c r="Q8">
-        <v>1.374423963133641</v>
+        <v>4.384037015615963</v>
       </c>
       <c r="R8">
-        <v>4.384037015615963</v>
+        <v>1.741230592294422</v>
       </c>
       <c r="S8">
-        <v>1.741230592294422</v>
+        <v>1.511255924170616</v>
       </c>
       <c r="T8">
-        <v>1.511255924170616</v>
+        <v>4.484177215189874</v>
       </c>
       <c r="U8">
-        <v>4.484177215189874</v>
+        <v>1.694229625223082</v>
       </c>
       <c r="V8">
-        <v>1.694229625223082</v>
+        <v>4.128801431127012</v>
       </c>
       <c r="W8">
-        <v>4.128801431127012</v>
+        <v>0.4540295119182747</v>
       </c>
       <c r="X8">
-        <v>0.4540295119182747</v>
+        <v>43.55536626916525</v>
       </c>
       <c r="Y8">
-        <v>0.5459704880817253</v>
+        <v>0.9948921679909194</v>
       </c>
       <c r="Z8">
-        <v>43.55536626916525</v>
+        <v>3.777970011534026</v>
       </c>
       <c r="AA8">
-        <v>0.9948921679909194</v>
-      </c>
-      <c r="AB8">
-        <v>0.00510783200908059</v>
-      </c>
-      <c r="AC8">
-        <v>3.777970011534026</v>
-      </c>
-      <c r="AD8">
         <v>4.018270401948842</v>
       </c>
     </row>
@@ -1193,84 +1115,75 @@
         <v>0.3359880537580886</v>
       </c>
       <c r="D9">
-        <v>0.6640119462419114</v>
+        <v>2.335988053758089</v>
       </c>
       <c r="E9">
-        <v>2.335988053758089</v>
+        <v>3.331508213041314</v>
       </c>
       <c r="F9">
-        <v>3.331508213041314</v>
+        <v>2.193130910900946</v>
       </c>
       <c r="G9">
-        <v>2.193130910900946</v>
+        <v>2.584370333499253</v>
       </c>
       <c r="H9">
-        <v>2.584370333499253</v>
+        <v>2.241911398705824</v>
       </c>
       <c r="I9">
-        <v>2.241911398705824</v>
+        <v>7.749128919860627</v>
       </c>
       <c r="J9">
-        <v>7.749128919860627</v>
+        <v>4.976854156296665</v>
       </c>
       <c r="K9">
-        <v>4.976854156296665</v>
+        <v>6.739920358387257</v>
       </c>
       <c r="L9">
-        <v>6.739920358387257</v>
+        <v>7.264310602289696</v>
       </c>
       <c r="M9">
-        <v>7.264310602289696</v>
+        <v>7.835988053758089</v>
       </c>
       <c r="N9">
-        <v>7.835988053758089</v>
+        <v>4.170233947237431</v>
       </c>
       <c r="O9">
-        <v>4.170233947237431</v>
+        <v>6.231956197112992</v>
       </c>
       <c r="P9">
-        <v>6.231956197112992</v>
+        <v>1.630662020905923</v>
       </c>
       <c r="Q9">
-        <v>1.630662020905923</v>
+        <v>2.104280736684918</v>
       </c>
       <c r="R9">
-        <v>2.104280736684918</v>
+        <v>2.422598307615729</v>
       </c>
       <c r="S9">
-        <v>2.422598307615729</v>
+        <v>1.845445495271279</v>
       </c>
       <c r="T9">
-        <v>1.845445495271279</v>
+        <v>6.788949726231956</v>
       </c>
       <c r="U9">
-        <v>6.788949726231956</v>
+        <v>2.539571926331508</v>
       </c>
       <c r="V9">
-        <v>2.539571926331508</v>
+        <v>4.839223494275759</v>
       </c>
       <c r="W9">
-        <v>4.839223494275759</v>
+        <v>0.5124440019910403</v>
       </c>
       <c r="X9">
-        <v>0.5124440019910403</v>
+        <v>46.56470881035341</v>
       </c>
       <c r="Y9">
-        <v>0.4875559980089597</v>
+        <v>0.821304131408661</v>
       </c>
       <c r="Z9">
-        <v>46.56470881035341</v>
+        <v>5.894420815611709</v>
       </c>
       <c r="AA9">
-        <v>0.821304131408661</v>
-      </c>
-      <c r="AB9">
-        <v>0.178695868591339</v>
-      </c>
-      <c r="AC9">
-        <v>5.894420815611709</v>
-      </c>
-      <c r="AD9">
         <v>5.573668491786958</v>
       </c>
     </row>
@@ -1289,84 +1202,75 @@
         <v>0.5189732142857143</v>
       </c>
       <c r="D10">
-        <v>0.4810267857142857</v>
+        <v>4.523908523908524</v>
       </c>
       <c r="E10">
-        <v>4.523908523908524</v>
+        <v>3.172661870503597</v>
       </c>
       <c r="F10">
-        <v>3.172661870503597</v>
+        <v>2.014155712841254</v>
       </c>
       <c r="G10">
-        <v>2.014155712841254</v>
+        <v>2.423350253807107</v>
       </c>
       <c r="H10">
-        <v>2.423350253807107</v>
+        <v>2.282807731434385</v>
       </c>
       <c r="I10">
-        <v>2.282807731434385</v>
+        <v>5.317256162915327</v>
       </c>
       <c r="J10">
-        <v>5.317256162915327</v>
+        <v>3.561965811965812</v>
       </c>
       <c r="K10">
-        <v>3.561965811965812</v>
+        <v>3.869294605809129</v>
       </c>
       <c r="L10">
-        <v>3.869294605809129</v>
+        <v>6.380122950819672</v>
       </c>
       <c r="M10">
-        <v>6.380122950819672</v>
+        <v>6.496304118268215</v>
       </c>
       <c r="N10">
-        <v>6.496304118268215</v>
+        <v>3.154973821989529</v>
       </c>
       <c r="O10">
-        <v>3.154973821989529</v>
+        <v>4.18849840255591</v>
       </c>
       <c r="P10">
-        <v>4.18849840255591</v>
+        <v>1.847715736040609</v>
       </c>
       <c r="Q10">
-        <v>1.847715736040609</v>
+        <v>2.018200202224469</v>
       </c>
       <c r="R10">
-        <v>2.018200202224469</v>
+        <v>2.041456016177957</v>
       </c>
       <c r="S10">
-        <v>2.041456016177957</v>
+        <v>2.053861788617886</v>
       </c>
       <c r="T10">
-        <v>2.053861788617886</v>
+        <v>4.529032258064516</v>
       </c>
       <c r="U10">
-        <v>4.529032258064516</v>
+        <v>2.361593462717058</v>
       </c>
       <c r="V10">
-        <v>2.361593462717058</v>
+        <v>4.25231719876416</v>
       </c>
       <c r="W10">
-        <v>4.25231719876416</v>
+        <v>0.474</v>
       </c>
       <c r="X10">
-        <v>0.474</v>
+        <v>45.271</v>
       </c>
       <c r="Y10">
-        <v>0.526</v>
+        <v>0.983</v>
       </c>
       <c r="Z10">
-        <v>45.271</v>
+        <v>4.821643286573146</v>
       </c>
       <c r="AA10">
-        <v>0.983</v>
-      </c>
-      <c r="AB10">
-        <v>0.017</v>
-      </c>
-      <c r="AC10">
-        <v>4.821643286573146</v>
-      </c>
-      <c r="AD10">
         <v>4.675564681724846</v>
       </c>
     </row>
@@ -1385,84 +1289,75 @@
         <v>0.1089700996677741</v>
       </c>
       <c r="D11">
-        <v>0.891029900332226</v>
+        <v>3.296626984126984</v>
       </c>
       <c r="E11">
-        <v>3.296626984126984</v>
+        <v>1.614394189501486</v>
       </c>
       <c r="F11">
-        <v>1.614394189501486</v>
+        <v>1.287883790029713</v>
       </c>
       <c r="G11">
-        <v>1.287883790029713</v>
+        <v>1.498842209725438</v>
       </c>
       <c r="H11">
-        <v>1.498842209725438</v>
+        <v>1.600331125827815</v>
       </c>
       <c r="I11">
-        <v>1.600331125827815</v>
+        <v>2.31801652892562</v>
       </c>
       <c r="J11">
-        <v>2.31801652892562</v>
+        <v>1.476206212822208</v>
       </c>
       <c r="K11">
-        <v>1.476206212822208</v>
+        <v>2.437230871149387</v>
       </c>
       <c r="L11">
-        <v>2.437230871149387</v>
+        <v>3.750331125827814</v>
       </c>
       <c r="M11">
-        <v>3.750331125827814</v>
+        <v>3.706799336650083</v>
       </c>
       <c r="N11">
-        <v>3.706799336650083</v>
+        <v>1.942091330244871</v>
       </c>
       <c r="O11">
-        <v>1.942091330244871</v>
+        <v>4.002319416832339</v>
       </c>
       <c r="P11">
-        <v>4.002319416832339</v>
+        <v>1.553754548461793</v>
       </c>
       <c r="Q11">
-        <v>1.553754548461793</v>
+        <v>3.339622641509434</v>
       </c>
       <c r="R11">
-        <v>3.339622641509434</v>
+        <v>1.634348113831899</v>
       </c>
       <c r="S11">
-        <v>1.634348113831899</v>
+        <v>1.324834437086093</v>
       </c>
       <c r="T11">
-        <v>1.324834437086093</v>
+        <v>1.511250827266711</v>
       </c>
       <c r="U11">
-        <v>1.511250827266711</v>
+        <v>1.504477611940298</v>
       </c>
       <c r="V11">
-        <v>1.504477611940298</v>
+        <v>5.518028448561032</v>
       </c>
       <c r="W11">
-        <v>5.518028448561032</v>
+        <v>0.4509222661396575</v>
       </c>
       <c r="X11">
-        <v>0.4509222661396575</v>
+        <v>44.58498023715415</v>
       </c>
       <c r="Y11">
-        <v>0.5490777338603425</v>
+        <v>1</v>
       </c>
       <c r="Z11">
-        <v>44.58498023715415</v>
+        <v>3.834331337325349</v>
       </c>
       <c r="AA11">
-        <v>1</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>3.834331337325349</v>
-      </c>
-      <c r="AD11">
         <v>4.147176079734219</v>
       </c>
     </row>
@@ -1481,84 +1376,75 @@
         <v>0.5223684210526316</v>
       </c>
       <c r="D12">
-        <v>0.4776315789473684</v>
+        <v>3.777631578947368</v>
       </c>
       <c r="E12">
-        <v>3.777631578947368</v>
+        <v>3.663815789473684</v>
       </c>
       <c r="F12">
-        <v>3.663815789473684</v>
+        <v>1.586184210526316</v>
       </c>
       <c r="G12">
-        <v>1.586184210526316</v>
+        <v>2.052631578947369</v>
       </c>
       <c r="H12">
-        <v>2.052631578947369</v>
+        <v>1.870394736842105</v>
       </c>
       <c r="I12">
-        <v>1.870394736842105</v>
+        <v>4.061842105263158</v>
       </c>
       <c r="J12">
-        <v>4.061842105263158</v>
+        <v>3.093421052631579</v>
       </c>
       <c r="K12">
-        <v>3.093421052631579</v>
+        <v>2.353289473684211</v>
       </c>
       <c r="L12">
-        <v>2.353289473684211</v>
+        <v>4.705263157894737</v>
       </c>
       <c r="M12">
-        <v>4.705263157894737</v>
+        <v>5.05</v>
       </c>
       <c r="N12">
-        <v>5.05</v>
+        <v>2.123026315789474</v>
       </c>
       <c r="O12">
-        <v>2.123026315789474</v>
+        <v>3.809210526315789</v>
       </c>
       <c r="P12">
-        <v>3.809210526315789</v>
+        <v>1.552631578947368</v>
       </c>
       <c r="Q12">
-        <v>1.552631578947368</v>
+        <v>3.594736842105263</v>
       </c>
       <c r="R12">
-        <v>3.594736842105263</v>
+        <v>1.783552631578947</v>
       </c>
       <c r="S12">
-        <v>1.783552631578947</v>
+        <v>1.744736842105263</v>
       </c>
       <c r="T12">
-        <v>1.744736842105263</v>
+        <v>3.669736842105263</v>
       </c>
       <c r="U12">
-        <v>3.669736842105263</v>
+        <v>1.877631578947368</v>
       </c>
       <c r="V12">
-        <v>1.877631578947368</v>
+        <v>3.9625</v>
       </c>
       <c r="W12">
-        <v>3.9625</v>
+        <v>0.5</v>
       </c>
       <c r="X12">
-        <v>0.5</v>
+        <v>38.84605263157895</v>
       </c>
       <c r="Y12">
-        <v>0.5</v>
+        <v>0.9710526315789474</v>
       </c>
       <c r="Z12">
-        <v>38.84605263157895</v>
+        <v>4.119492656875835</v>
       </c>
       <c r="AA12">
-        <v>0.9710526315789474</v>
-      </c>
-      <c r="AB12">
-        <v>0.02894736842105263</v>
-      </c>
-      <c r="AC12">
-        <v>4.119492656875835</v>
-      </c>
-      <c r="AD12">
         <v>4.442763157894737</v>
       </c>
     </row>
@@ -1577,84 +1463,75 @@
         <v>0.6993939393939393</v>
       </c>
       <c r="D13">
-        <v>0.3006060606060606</v>
+        <v>2.138351983723296</v>
       </c>
       <c r="E13">
-        <v>2.138351983723296</v>
+        <v>2.880081300813008</v>
       </c>
       <c r="F13">
-        <v>2.880081300813008</v>
+        <v>1.454545454545455</v>
       </c>
       <c r="G13">
-        <v>1.454545454545455</v>
+        <v>1.609879032258065</v>
       </c>
       <c r="H13">
-        <v>1.609879032258065</v>
+        <v>1.539393939393939</v>
       </c>
       <c r="I13">
-        <v>1.539393939393939</v>
+        <v>3.725</v>
       </c>
       <c r="J13">
-        <v>3.725</v>
+        <v>2.238805970149254</v>
       </c>
       <c r="K13">
-        <v>2.238805970149254</v>
+        <v>3.016025641025641</v>
       </c>
       <c r="L13">
-        <v>3.016025641025641</v>
+        <v>5.200415368639668</v>
       </c>
       <c r="M13">
-        <v>5.200415368639668</v>
+        <v>5.077753779697624</v>
       </c>
       <c r="N13">
-        <v>5.077753779697624</v>
+        <v>1.757158006362672</v>
       </c>
       <c r="O13">
-        <v>1.757158006362672</v>
+        <v>2.722103004291846</v>
       </c>
       <c r="P13">
-        <v>2.722103004291846</v>
+        <v>1.321536905965622</v>
       </c>
       <c r="Q13">
-        <v>1.321536905965622</v>
+        <v>1.474747474747475</v>
       </c>
       <c r="R13">
-        <v>1.474747474747475</v>
+        <v>1.424547283702213</v>
       </c>
       <c r="S13">
-        <v>1.424547283702213</v>
+        <v>1.252032520325203</v>
       </c>
       <c r="T13">
-        <v>1.252032520325203</v>
+        <v>2.837060702875399</v>
       </c>
       <c r="U13">
-        <v>2.837060702875399</v>
+        <v>1.328600405679513</v>
       </c>
       <c r="V13">
-        <v>1.328600405679513</v>
+        <v>2.674513817809621</v>
       </c>
       <c r="W13">
-        <v>2.674513817809621</v>
+        <v>0.482</v>
       </c>
       <c r="X13">
-        <v>0.482</v>
+        <v>43.539</v>
       </c>
       <c r="Y13">
-        <v>0.518</v>
+        <v>0.78</v>
       </c>
       <c r="Z13">
-        <v>43.539</v>
+        <v>5.449021627188466</v>
       </c>
       <c r="AA13">
-        <v>0.78</v>
-      </c>
-      <c r="AB13">
-        <v>0.22</v>
-      </c>
-      <c r="AC13">
-        <v>5.449021627188466</v>
-      </c>
-      <c r="AD13">
         <v>5.273695420660277</v>
       </c>
     </row>
@@ -1673,84 +1550,75 @@
         <v>0.1201754385964912</v>
       </c>
       <c r="D14">
-        <v>0.8798245614035087</v>
+        <v>3.270657672849916</v>
       </c>
       <c r="E14">
-        <v>3.270657672849916</v>
+        <v>4.354621848739495</v>
       </c>
       <c r="F14">
-        <v>4.354621848739495</v>
+        <v>2.648241206030151</v>
       </c>
       <c r="G14">
-        <v>2.648241206030151</v>
+        <v>3.262626262626263</v>
       </c>
       <c r="H14">
-        <v>3.262626262626263</v>
+        <v>3.02436974789916</v>
       </c>
       <c r="I14">
-        <v>3.02436974789916</v>
+        <v>6.676295666949873</v>
       </c>
       <c r="J14">
-        <v>6.676295666949873</v>
+        <v>5.087542087542087</v>
       </c>
       <c r="K14">
-        <v>5.087542087542087</v>
+        <v>6.133389261744966</v>
       </c>
       <c r="L14">
-        <v>6.133389261744966</v>
+        <v>6.855462184873949</v>
       </c>
       <c r="M14">
-        <v>6.855462184873949</v>
+        <v>7.935185185185185</v>
       </c>
       <c r="N14">
-        <v>7.935185185185185</v>
+        <v>4.785896346644011</v>
       </c>
       <c r="O14">
-        <v>4.785896346644011</v>
+        <v>6.068085106382979</v>
       </c>
       <c r="P14">
-        <v>6.068085106382979</v>
+        <v>2.025125628140704</v>
       </c>
       <c r="Q14">
-        <v>2.025125628140704</v>
+        <v>3.206521739130435</v>
       </c>
       <c r="R14">
-        <v>3.206521739130435</v>
+        <v>2.178242677824268</v>
       </c>
       <c r="S14">
-        <v>2.178242677824268</v>
+        <v>2.006694560669456</v>
       </c>
       <c r="T14">
-        <v>2.006694560669456</v>
+        <v>6.420473773265652</v>
       </c>
       <c r="U14">
-        <v>6.420473773265652</v>
+        <v>2.479359730412805</v>
       </c>
       <c r="V14">
-        <v>2.479359730412805</v>
+        <v>4.815722738799662</v>
       </c>
       <c r="W14">
-        <v>4.815722738799662</v>
+        <v>0.4608333333333333</v>
       </c>
       <c r="X14">
-        <v>0.4608333333333333</v>
+        <v>49.11416666666667</v>
       </c>
       <c r="Y14">
-        <v>0.5391666666666667</v>
+        <v>0.9699749791492911</v>
       </c>
       <c r="Z14">
-        <v>49.11416666666667</v>
+        <v>4.145954962468724</v>
       </c>
       <c r="AA14">
-        <v>0.9699749791492911</v>
-      </c>
-      <c r="AB14">
-        <v>0.03002502085070892</v>
-      </c>
-      <c r="AC14">
-        <v>4.145954962468724</v>
-      </c>
-      <c r="AD14">
         <v>5.233558178752108</v>
       </c>
     </row>
@@ -1769,84 +1637,75 @@
         <v>0.1573426573426573</v>
       </c>
       <c r="D15">
-        <v>0.8426573426573427</v>
+        <v>1.538258575197889</v>
       </c>
       <c r="E15">
-        <v>1.538258575197889</v>
+        <v>1.829508196721311</v>
       </c>
       <c r="F15">
-        <v>1.829508196721311</v>
+        <v>1.162303664921466</v>
       </c>
       <c r="G15">
-        <v>1.162303664921466</v>
+        <v>1.517105263157895</v>
       </c>
       <c r="H15">
-        <v>1.517105263157895</v>
+        <v>1.325459317585302</v>
       </c>
       <c r="I15">
-        <v>1.325459317585302</v>
+        <v>7.855989232839838</v>
       </c>
       <c r="J15">
-        <v>7.855989232839838</v>
+        <v>4.969737726967048</v>
       </c>
       <c r="K15">
-        <v>4.969737726967048</v>
+        <v>5.460810810810811</v>
       </c>
       <c r="L15">
-        <v>5.460810810810811</v>
+        <v>7.397870924817033</v>
       </c>
       <c r="M15">
-        <v>7.397870924817033</v>
+        <v>8.522666666666666</v>
       </c>
       <c r="N15">
-        <v>8.522666666666666</v>
+        <v>4.171864171864172</v>
       </c>
       <c r="O15">
-        <v>4.171864171864172</v>
+        <v>7.128859060402685</v>
       </c>
       <c r="P15">
-        <v>7.128859060402685</v>
+        <v>1.106745252128356</v>
       </c>
       <c r="Q15">
-        <v>1.106745252128356</v>
+        <v>1.508541392904074</v>
       </c>
       <c r="R15">
-        <v>1.508541392904074</v>
+        <v>1.321733420879842</v>
       </c>
       <c r="S15">
-        <v>1.321733420879842</v>
+        <v>1.110819672131148</v>
       </c>
       <c r="T15">
-        <v>1.110819672131148</v>
+        <v>4.57443915703603</v>
       </c>
       <c r="U15">
-        <v>4.57443915703603</v>
+        <v>1.261669953977646</v>
       </c>
       <c r="V15">
-        <v>1.261669953977646</v>
+        <v>2.525793650793651</v>
       </c>
       <c r="W15">
-        <v>2.525793650793651</v>
+        <v>0.4862565445026178</v>
       </c>
       <c r="X15">
-        <v>0.4862565445026178</v>
+        <v>50.79712041884817</v>
       </c>
       <c r="Y15">
-        <v>0.5137434554973822</v>
+        <v>0.8605108055009824</v>
       </c>
       <c r="Z15">
-        <v>50.79712041884817</v>
+        <v>5.078688524590164</v>
       </c>
       <c r="AA15">
-        <v>0.8605108055009824</v>
-      </c>
-      <c r="AB15">
-        <v>0.1394891944990177</v>
-      </c>
-      <c r="AC15">
-        <v>5.078688524590164</v>
-      </c>
-      <c r="AD15">
         <v>5.185888738127544</v>
       </c>
     </row>
@@ -1865,84 +1724,75 @@
         <v>0.5724258289703316</v>
       </c>
       <c r="D16">
-        <v>0.4275741710296684</v>
+        <v>4.440203562340967</v>
       </c>
       <c r="E16">
-        <v>4.440203562340967</v>
+        <v>3.97319932998325</v>
       </c>
       <c r="F16">
-        <v>3.97319932998325</v>
+        <v>1.917922948073702</v>
       </c>
       <c r="G16">
-        <v>1.917922948073702</v>
+        <v>2.335299073294018</v>
       </c>
       <c r="H16">
-        <v>2.335299073294018</v>
+        <v>2.304128053917439</v>
       </c>
       <c r="I16">
-        <v>2.304128053917439</v>
+        <v>3.704604691572546</v>
       </c>
       <c r="J16">
-        <v>3.704604691572546</v>
+        <v>3.467009425878321</v>
       </c>
       <c r="K16">
-        <v>3.467009425878321</v>
+        <v>2.550126368997473</v>
       </c>
       <c r="L16">
-        <v>2.550126368997473</v>
+        <v>4.367932489451476</v>
       </c>
       <c r="M16">
-        <v>4.367932489451476</v>
+        <v>3.994884910485934</v>
       </c>
       <c r="N16">
-        <v>3.994884910485934</v>
+        <v>2.428087986463621</v>
       </c>
       <c r="O16">
-        <v>2.428087986463621</v>
+        <v>3.358278765201122</v>
       </c>
       <c r="P16">
-        <v>3.358278765201122</v>
+        <v>1.870401337792642</v>
       </c>
       <c r="Q16">
-        <v>1.870401337792642</v>
+        <v>3.295397489539749</v>
       </c>
       <c r="R16">
-        <v>3.295397489539749</v>
+        <v>2.176569037656904</v>
       </c>
       <c r="S16">
-        <v>2.176569037656904</v>
+        <v>2.079324894514768</v>
       </c>
       <c r="T16">
-        <v>2.079324894514768</v>
+        <v>3.059574468085106</v>
       </c>
       <c r="U16">
-        <v>3.059574468085106</v>
+        <v>2.415126050420168</v>
       </c>
       <c r="V16">
-        <v>2.415126050420168</v>
+        <v>3.655668358714044</v>
       </c>
       <c r="W16">
-        <v>3.655668358714044</v>
+        <v>0.4775</v>
       </c>
       <c r="X16">
-        <v>0.4775</v>
+        <v>39.48833333333334</v>
       </c>
       <c r="Y16">
-        <v>0.5225</v>
+        <v>0.99</v>
       </c>
       <c r="Z16">
-        <v>39.48833333333334</v>
+        <v>4.214703425229741</v>
       </c>
       <c r="AA16">
-        <v>0.99</v>
-      </c>
-      <c r="AB16">
-        <v>0.01</v>
-      </c>
-      <c r="AC16">
-        <v>4.214703425229741</v>
-      </c>
-      <c r="AD16">
         <v>4.759663865546218</v>
       </c>
     </row>
@@ -1961,72 +1811,63 @@
         <v>0.9983319432860718</v>
       </c>
       <c r="D17">
-        <v>0.001668056713928273</v>
+        <v>1.78915135608049</v>
       </c>
       <c r="E17">
-        <v>1.78915135608049</v>
+        <v>1.592592592592593</v>
       </c>
       <c r="F17">
-        <v>1.592592592592593</v>
+        <v>1.066108786610879</v>
       </c>
       <c r="G17">
-        <v>1.066108786610879</v>
+        <v>1.537351443123939</v>
       </c>
       <c r="H17">
-        <v>1.537351443123939</v>
-      </c>
-      <c r="I17">
         <v>1.177703269069573</v>
       </c>
+      <c r="K17">
+        <v>2.061603375527426</v>
+      </c>
       <c r="L17">
-        <v>2.061603375527426</v>
-      </c>
-      <c r="M17">
         <v>4.984886649874055</v>
       </c>
+      <c r="N17">
+        <v>1.115481171548117</v>
+      </c>
       <c r="O17">
-        <v>1.115481171548117</v>
+        <v>1.5730110775428</v>
       </c>
       <c r="P17">
-        <v>1.5730110775428</v>
+        <v>2.550797649034425</v>
       </c>
       <c r="Q17">
-        <v>2.550797649034425</v>
+        <v>3.874476987447699</v>
       </c>
       <c r="R17">
-        <v>3.874476987447699</v>
+        <v>1.508389261744966</v>
       </c>
       <c r="S17">
-        <v>1.508389261744966</v>
-      </c>
-      <c r="T17">
         <v>1.09419014084507</v>
       </c>
+      <c r="U17">
+        <v>1.115068493150685</v>
+      </c>
       <c r="V17">
-        <v>1.115068493150685</v>
+        <v>6.63855421686747</v>
       </c>
       <c r="W17">
-        <v>6.63855421686747</v>
+        <v>0.5175</v>
       </c>
       <c r="X17">
-        <v>0.5175</v>
+        <v>39.69916666666666</v>
       </c>
       <c r="Y17">
-        <v>0.4825</v>
+        <v>0.9991666666666666</v>
       </c>
       <c r="Z17">
-        <v>39.69916666666666</v>
+        <v>3.5975</v>
       </c>
       <c r="AA17">
-        <v>0.9991666666666666</v>
-      </c>
-      <c r="AB17">
-        <v>0.0008333333333333334</v>
-      </c>
-      <c r="AC17">
-        <v>3.5975</v>
-      </c>
-      <c r="AD17">
         <v>4.991921005385996</v>
       </c>
     </row>
@@ -2045,84 +1886,75 @@
         <v>0.8876127973748975</v>
       </c>
       <c r="D18">
-        <v>0.1123872026251025</v>
+        <v>1.628571428571429</v>
       </c>
       <c r="E18">
-        <v>1.628571428571429</v>
+        <v>2.019607843137255</v>
       </c>
       <c r="F18">
-        <v>2.019607843137255</v>
+        <v>1.472312703583062</v>
       </c>
       <c r="G18">
-        <v>1.472312703583062</v>
+        <v>1.546502057613169</v>
       </c>
       <c r="H18">
-        <v>1.546502057613169</v>
+        <v>1.488562091503268</v>
       </c>
       <c r="I18">
-        <v>1.488562091503268</v>
+        <v>1.640758293838863</v>
       </c>
       <c r="J18">
-        <v>1.640758293838863</v>
+        <v>1.7002457002457</v>
       </c>
       <c r="K18">
-        <v>1.7002457002457</v>
+        <v>1.676734693877551</v>
       </c>
       <c r="L18">
-        <v>1.676734693877551</v>
+        <v>2.590872045639772</v>
       </c>
       <c r="M18">
-        <v>2.590872045639772</v>
+        <v>1.911237785016287</v>
       </c>
       <c r="N18">
-        <v>1.911237785016287</v>
+        <v>1.466992665036675</v>
       </c>
       <c r="O18">
-        <v>1.466992665036675</v>
+        <v>1.713000817661488</v>
       </c>
       <c r="P18">
-        <v>1.713000817661488</v>
+        <v>1.71638141809291</v>
       </c>
       <c r="Q18">
-        <v>1.71638141809291</v>
+        <v>2.929095354523227</v>
       </c>
       <c r="R18">
-        <v>2.929095354523227</v>
+        <v>1.500814332247557</v>
       </c>
       <c r="S18">
-        <v>1.500814332247557</v>
+        <v>1.502852485737571</v>
       </c>
       <c r="T18">
-        <v>1.502852485737571</v>
+        <v>1.521986970684039</v>
       </c>
       <c r="U18">
-        <v>1.521986970684039</v>
+        <v>1.581699346405229</v>
       </c>
       <c r="V18">
-        <v>1.581699346405229</v>
+        <v>2.13121434392828</v>
       </c>
       <c r="W18">
-        <v>2.13121434392828</v>
+        <v>0.5056910569105691</v>
       </c>
       <c r="X18">
-        <v>0.5056910569105691</v>
+        <v>31.92682926829268</v>
       </c>
       <c r="Y18">
-        <v>0.4943089430894309</v>
+        <v>0.9983726606997559</v>
       </c>
       <c r="Z18">
-        <v>31.92682926829268</v>
+        <v>3.024509803921569</v>
       </c>
       <c r="AA18">
-        <v>0.9983726606997559</v>
-      </c>
-      <c r="AB18">
-        <v>0.001627339300244101</v>
-      </c>
-      <c r="AC18">
-        <v>3.024509803921569</v>
-      </c>
-      <c r="AD18">
         <v>4.381107491856677</v>
       </c>
     </row>
@@ -2141,81 +1973,72 @@
         <v>0.258746948738812</v>
       </c>
       <c r="D19">
-        <v>0.741253051261188</v>
+        <v>1.979449398991857</v>
       </c>
       <c r="E19">
-        <v>1.979449398991857</v>
+        <v>2.53046177726038</v>
       </c>
       <c r="F19">
-        <v>2.53046177726038</v>
+        <v>1.48338485316847</v>
       </c>
       <c r="G19">
-        <v>1.48338485316847</v>
+        <v>1.790634674922601</v>
       </c>
       <c r="H19">
-        <v>1.790634674922601</v>
+        <v>1.423833397608947</v>
       </c>
       <c r="I19">
-        <v>1.423833397608947</v>
+        <v>7.838620142743854</v>
       </c>
       <c r="J19">
-        <v>7.838620142743854</v>
+        <v>4.858557844690966</v>
       </c>
       <c r="K19">
-        <v>4.858557844690966</v>
+        <v>6.836142689141513</v>
       </c>
       <c r="L19">
-        <v>6.836142689141513</v>
+        <v>7.928487690504103</v>
       </c>
       <c r="M19">
-        <v>7.928487690504103</v>
+        <v>8.162162162162161</v>
       </c>
       <c r="N19">
-        <v>8.162162162162161</v>
+        <v>4.823743922204214</v>
       </c>
       <c r="O19">
-        <v>4.823743922204214</v>
-      </c>
-      <c r="P19">
         <v>6.742722265932337</v>
       </c>
+      <c r="Q19">
+        <v>1.521604938271605</v>
+      </c>
       <c r="R19">
-        <v>1.521604938271605</v>
+        <v>1.621715610510046</v>
       </c>
       <c r="S19">
-        <v>1.621715610510046</v>
+        <v>1.244590417310665</v>
       </c>
       <c r="T19">
-        <v>1.244590417310665</v>
+        <v>6.387109529458284</v>
       </c>
       <c r="U19">
-        <v>6.387109529458284</v>
+        <v>1.421317829457364</v>
       </c>
       <c r="V19">
-        <v>1.421317829457364</v>
+        <v>4.447100313479623</v>
       </c>
       <c r="W19">
-        <v>4.447100313479623</v>
+        <v>0.4289596273291926</v>
       </c>
       <c r="X19">
-        <v>0.4289596273291926</v>
+        <v>51.81692993114621</v>
       </c>
       <c r="Y19">
-        <v>0.5710403726708074</v>
+        <v>0.8614130434782609</v>
       </c>
       <c r="Z19">
-        <v>51.81692993114621</v>
+        <v>5.25010250102501</v>
       </c>
       <c r="AA19">
-        <v>0.8614130434782609</v>
-      </c>
-      <c r="AB19">
-        <v>0.1385869565217391</v>
-      </c>
-      <c r="AC19">
-        <v>5.25010250102501</v>
-      </c>
-      <c r="AD19">
         <v>5.652475705691809</v>
       </c>
     </row>
@@ -2234,84 +2057,75 @@
         <v>0.4938154138915319</v>
       </c>
       <c r="D20">
-        <v>0.5061845861084682</v>
+        <v>1.586756077116513</v>
       </c>
       <c r="E20">
-        <v>1.586756077116513</v>
+        <v>2.388471177944862</v>
       </c>
       <c r="F20">
-        <v>2.388471177944862</v>
+        <v>1.130543933054393</v>
       </c>
       <c r="G20">
-        <v>1.130543933054393</v>
+        <v>1.678960603520536</v>
       </c>
       <c r="H20">
-        <v>1.678960603520536</v>
+        <v>1.37751677852349</v>
       </c>
       <c r="I20">
-        <v>1.37751677852349</v>
+        <v>4.764909248055315</v>
       </c>
       <c r="J20">
-        <v>4.764909248055315</v>
+        <v>3.981244671781756</v>
       </c>
       <c r="K20">
-        <v>3.981244671781756</v>
+        <v>4.575063613231552</v>
       </c>
       <c r="L20">
-        <v>4.575063613231552</v>
+        <v>6.866161616161616</v>
       </c>
       <c r="M20">
-        <v>6.866161616161616</v>
+        <v>7.41687979539642</v>
       </c>
       <c r="N20">
-        <v>7.41687979539642</v>
+        <v>1.885008517887564</v>
       </c>
       <c r="O20">
-        <v>1.885008517887564</v>
+        <v>3.107047279214987</v>
       </c>
       <c r="P20">
-        <v>3.107047279214987</v>
+        <v>1.131996658312448</v>
       </c>
       <c r="Q20">
-        <v>1.131996658312448</v>
+        <v>1.221202003338898</v>
       </c>
       <c r="R20">
-        <v>1.221202003338898</v>
+        <v>1.190954773869347</v>
       </c>
       <c r="S20">
-        <v>1.190954773869347</v>
+        <v>1.142737195633921</v>
       </c>
       <c r="T20">
-        <v>1.142737195633921</v>
+        <v>5.346973572037511</v>
       </c>
       <c r="U20">
-        <v>5.346973572037511</v>
+        <v>1.451694915254237</v>
       </c>
       <c r="V20">
-        <v>1.451694915254237</v>
+        <v>2.433450087565674</v>
       </c>
       <c r="W20">
-        <v>2.433450087565674</v>
+        <v>0.4691666666666667</v>
       </c>
       <c r="X20">
-        <v>0.4691666666666667</v>
+        <v>50.92916666666667</v>
       </c>
       <c r="Y20">
-        <v>0.5308333333333334</v>
+        <v>0.8941666666666667</v>
       </c>
       <c r="Z20">
-        <v>50.92916666666667</v>
+        <v>4.2325</v>
       </c>
       <c r="AA20">
-        <v>0.8941666666666667</v>
-      </c>
-      <c r="AB20">
-        <v>0.1058333333333333</v>
-      </c>
-      <c r="AC20">
-        <v>4.2325</v>
-      </c>
-      <c r="AD20">
         <v>4.543006081668115</v>
       </c>
     </row>
@@ -2330,84 +2144,75 @@
         <v>0.7933279088689992</v>
       </c>
       <c r="D21">
-        <v>0.2066720911310008</v>
+        <v>4.142384105960265</v>
       </c>
       <c r="E21">
-        <v>4.142384105960265</v>
+        <v>3.698175787728026</v>
       </c>
       <c r="F21">
-        <v>3.698175787728026</v>
+        <v>2.235294117647059</v>
       </c>
       <c r="G21">
-        <v>2.235294117647059</v>
+        <v>2.384808013355593</v>
       </c>
       <c r="H21">
-        <v>2.384808013355593</v>
+        <v>2.30865224625624</v>
       </c>
       <c r="I21">
-        <v>2.30865224625624</v>
+        <v>3.730290456431535</v>
       </c>
       <c r="J21">
-        <v>3.730290456431535</v>
+        <v>3.396825396825397</v>
       </c>
       <c r="K21">
-        <v>3.396825396825397</v>
+        <v>2.959336099585062</v>
       </c>
       <c r="L21">
-        <v>2.959336099585062</v>
+        <v>5.00413564929694</v>
       </c>
       <c r="M21">
-        <v>5.00413564929694</v>
+        <v>4.003319502074689</v>
       </c>
       <c r="N21">
-        <v>4.003319502074689</v>
+        <v>2.603491271820449</v>
       </c>
       <c r="O21">
-        <v>2.603491271820449</v>
+        <v>3.727272727272727</v>
       </c>
       <c r="P21">
-        <v>3.727272727272727</v>
+        <v>1.87986743993372</v>
       </c>
       <c r="Q21">
-        <v>1.87986743993372</v>
+        <v>4.065</v>
       </c>
       <c r="R21">
-        <v>4.065</v>
+        <v>2.210963455149502</v>
       </c>
       <c r="S21">
-        <v>2.210963455149502</v>
+        <v>2.08955223880597</v>
       </c>
       <c r="T21">
-        <v>2.08955223880597</v>
+        <v>3.513647642679901</v>
       </c>
       <c r="U21">
-        <v>3.513647642679901</v>
+        <v>2.069941715237302</v>
       </c>
       <c r="V21">
-        <v>2.069941715237302</v>
+        <v>5.092868988391376</v>
       </c>
       <c r="W21">
-        <v>5.092868988391376</v>
+        <v>0.4703010577705452</v>
       </c>
       <c r="X21">
-        <v>0.4703010577705452</v>
+        <v>33.49877949552481</v>
       </c>
       <c r="Y21">
-        <v>0.5296989422294548</v>
+        <v>0.9926108374384236</v>
       </c>
       <c r="Z21">
-        <v>33.49877949552481</v>
+        <v>5.085376162299239</v>
       </c>
       <c r="AA21">
-        <v>0.9926108374384236</v>
-      </c>
-      <c r="AB21">
-        <v>0.007389162561576354</v>
-      </c>
-      <c r="AC21">
-        <v>5.085376162299239</v>
-      </c>
-      <c r="AD21">
         <v>5.959302325581396</v>
       </c>
     </row>
@@ -2426,84 +2231,75 @@
         <v>0.4708761625061185</v>
       </c>
       <c r="D22">
-        <v>0.5291238374938816</v>
+        <v>3.063376874697629</v>
       </c>
       <c r="E22">
-        <v>3.063376874697629</v>
+        <v>2.474420849420849</v>
       </c>
       <c r="F22">
-        <v>2.474420849420849</v>
+        <v>2.024590163934426</v>
       </c>
       <c r="G22">
-        <v>2.024590163934426</v>
+        <v>2.229357798165138</v>
       </c>
       <c r="H22">
-        <v>2.229357798165138</v>
+        <v>2.010140028971511</v>
       </c>
       <c r="I22">
-        <v>2.010140028971511</v>
+        <v>5.129142300194932</v>
       </c>
       <c r="J22">
-        <v>5.129142300194932</v>
+        <v>3.479398933591856</v>
       </c>
       <c r="K22">
-        <v>3.479398933591856</v>
+        <v>3.920950533462658</v>
       </c>
       <c r="L22">
-        <v>3.920950533462658</v>
+        <v>5.372758119243819</v>
       </c>
       <c r="M22">
-        <v>5.372758119243819</v>
+        <v>5.306013579049466</v>
       </c>
       <c r="N22">
-        <v>5.306013579049466</v>
+        <v>3.384019370460048</v>
       </c>
       <c r="O22">
-        <v>3.384019370460048</v>
+        <v>5.990799031476998</v>
       </c>
       <c r="P22">
-        <v>5.990799031476998</v>
+        <v>2.064158224794983</v>
       </c>
       <c r="Q22">
-        <v>2.064158224794983</v>
+        <v>3.755673587638822</v>
       </c>
       <c r="R22">
-        <v>3.755673587638822</v>
+        <v>2.30327868852459</v>
       </c>
       <c r="S22">
-        <v>2.30327868852459</v>
+        <v>2.017943743937924</v>
       </c>
       <c r="T22">
-        <v>2.017943743937924</v>
+        <v>3.304895782840524</v>
       </c>
       <c r="U22">
-        <v>3.304895782840524</v>
+        <v>2.493946731234867</v>
       </c>
       <c r="V22">
-        <v>2.493946731234867</v>
+        <v>4.478197674418604</v>
       </c>
       <c r="W22">
-        <v>4.478197674418604</v>
+        <v>0.4587951807228915</v>
       </c>
       <c r="X22">
-        <v>0.4587951807228915</v>
+        <v>47.21963070942662</v>
       </c>
       <c r="Y22">
-        <v>0.5412048192771084</v>
+        <v>0.7391513982642237</v>
       </c>
       <c r="Z22">
-        <v>47.21963070942662</v>
+        <v>5.017366136034732</v>
       </c>
       <c r="AA22">
-        <v>0.7391513982642237</v>
-      </c>
-      <c r="AB22">
-        <v>0.2608486017357763</v>
-      </c>
-      <c r="AC22">
-        <v>5.017366136034732</v>
-      </c>
-      <c r="AD22">
         <v>4.792553191489362</v>
       </c>
     </row>
@@ -2522,84 +2318,75 @@
         <v>0.7139731165989371</v>
       </c>
       <c r="D23">
-        <v>0.2860268834010629</v>
+        <v>3.28023876845743</v>
       </c>
       <c r="E23">
-        <v>3.28023876845743</v>
+        <v>2.737864077669903</v>
       </c>
       <c r="F23">
-        <v>2.737864077669903</v>
+        <v>1.556007509386733</v>
       </c>
       <c r="G23">
-        <v>1.556007509386733</v>
+        <v>2.501409332915753</v>
       </c>
       <c r="H23">
-        <v>2.501409332915753</v>
+        <v>1.931326434619003</v>
       </c>
       <c r="I23">
-        <v>1.931326434619003</v>
+        <v>1.610222640326121</v>
       </c>
       <c r="J23">
-        <v>1.610222640326121</v>
+        <v>1.56628016295832</v>
       </c>
       <c r="K23">
-        <v>1.56628016295832</v>
+        <v>1.576260569996868</v>
       </c>
       <c r="L23">
-        <v>1.576260569996868</v>
+        <v>2.690737833594977</v>
       </c>
       <c r="M23">
-        <v>2.690737833594977</v>
+        <v>1.642365456821026</v>
       </c>
       <c r="N23">
-        <v>1.642365456821026</v>
+        <v>1.484507042253521</v>
       </c>
       <c r="O23">
-        <v>1.484507042253521</v>
+        <v>2.190655377861399</v>
       </c>
       <c r="P23">
-        <v>2.190655377861399</v>
+        <v>1.668648310387985</v>
       </c>
       <c r="Q23">
-        <v>1.668648310387985</v>
+        <v>2.436619718309859</v>
       </c>
       <c r="R23">
-        <v>2.436619718309859</v>
+        <v>1.863536776212833</v>
       </c>
       <c r="S23">
-        <v>1.863536776212833</v>
+        <v>1.725496375669713</v>
       </c>
       <c r="T23">
-        <v>1.725496375669713</v>
+        <v>1.520062695924765</v>
       </c>
       <c r="U23">
-        <v>1.520062695924765</v>
+        <v>1.782553729456384</v>
       </c>
       <c r="V23">
-        <v>1.782553729456384</v>
+        <v>3.382111251580278</v>
       </c>
       <c r="W23">
-        <v>3.382111251580278</v>
+        <v>0.451875</v>
       </c>
       <c r="X23">
-        <v>0.451875</v>
+        <v>40.0265625</v>
       </c>
       <c r="Y23">
-        <v>0.548125</v>
+        <v>0.9990625</v>
       </c>
       <c r="Z23">
-        <v>40.0265625</v>
+        <v>3.256642700844014</v>
       </c>
       <c r="AA23">
-        <v>0.9990625</v>
-      </c>
-      <c r="AB23">
-        <v>0.0009375</v>
-      </c>
-      <c r="AC23">
-        <v>3.256642700844014</v>
-      </c>
-      <c r="AD23">
         <v>4.227301189730746</v>
       </c>
     </row>
@@ -2618,84 +2405,75 @@
         <v>0.5748626373626373</v>
       </c>
       <c r="D24">
-        <v>0.4251373626373626</v>
+        <v>2.72259236826166</v>
       </c>
       <c r="E24">
-        <v>2.72259236826166</v>
+        <v>2.313353115727003</v>
       </c>
       <c r="F24">
-        <v>2.313353115727003</v>
+        <v>1.887700534759358</v>
       </c>
       <c r="G24">
-        <v>1.887700534759358</v>
+        <v>2.044296116504854</v>
       </c>
       <c r="H24">
-        <v>2.044296116504854</v>
+        <v>1.926391382405745</v>
       </c>
       <c r="I24">
-        <v>1.926391382405745</v>
+        <v>2.742897727272727</v>
       </c>
       <c r="J24">
-        <v>2.742897727272727</v>
+        <v>2.166040100250627</v>
       </c>
       <c r="K24">
-        <v>2.166040100250627</v>
+        <v>2.784818067754078</v>
       </c>
       <c r="L24">
-        <v>2.784818067754078</v>
+        <v>3.102362204724409</v>
       </c>
       <c r="M24">
-        <v>3.102362204724409</v>
+        <v>2.27819083023544</v>
       </c>
       <c r="N24">
-        <v>2.27819083023544</v>
+        <v>1.906474820143885</v>
       </c>
       <c r="O24">
-        <v>1.906474820143885</v>
+        <v>2.855781448538755</v>
       </c>
       <c r="P24">
-        <v>2.855781448538755</v>
+        <v>2.048838594401429</v>
       </c>
       <c r="Q24">
-        <v>2.048838594401429</v>
+        <v>3.606761565836299</v>
       </c>
       <c r="R24">
-        <v>3.606761565836299</v>
+        <v>1.929383602633154</v>
       </c>
       <c r="S24">
-        <v>1.929383602633154</v>
+        <v>1.892077354959451</v>
       </c>
       <c r="T24">
-        <v>1.892077354959451</v>
+        <v>1.97717184527584</v>
       </c>
       <c r="U24">
-        <v>1.97717184527584</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="V24">
-        <v>1.833333333333333</v>
+        <v>3.852923076923077</v>
       </c>
       <c r="W24">
-        <v>3.852923076923077</v>
+        <v>0.566193853427896</v>
       </c>
       <c r="X24">
-        <v>0.566193853427896</v>
+        <v>35.80378250591016</v>
       </c>
       <c r="Y24">
-        <v>0.433806146572104</v>
+        <v>1</v>
       </c>
       <c r="Z24">
-        <v>35.80378250591016</v>
+        <v>4.202486678507993</v>
       </c>
       <c r="AA24">
-        <v>1</v>
-      </c>
-      <c r="AB24">
-        <v>0</v>
-      </c>
-      <c r="AC24">
-        <v>4.202486678507993</v>
-      </c>
-      <c r="AD24">
         <v>5.43963963963964</v>
       </c>
     </row>
@@ -2714,78 +2492,69 @@
         <v>0.8892617449664429</v>
       </c>
       <c r="D25">
-        <v>0.1107382550335571</v>
+        <v>3.598366235534377</v>
       </c>
       <c r="E25">
-        <v>3.598366235534377</v>
+        <v>2.714093959731544</v>
       </c>
       <c r="F25">
-        <v>2.714093959731544</v>
+        <v>1.459893048128342</v>
       </c>
       <c r="G25">
-        <v>1.459893048128342</v>
+        <v>2.332437877770316</v>
       </c>
       <c r="H25">
-        <v>2.332437877770316</v>
+        <v>1.496662216288384</v>
       </c>
       <c r="I25">
-        <v>1.496662216288384</v>
-      </c>
-      <c r="J25">
         <v>1.602013422818792</v>
       </c>
+      <c r="K25">
+        <v>2.729585006693441</v>
+      </c>
       <c r="L25">
-        <v>2.729585006693441</v>
+        <v>3.652815013404826</v>
       </c>
       <c r="M25">
-        <v>3.652815013404826</v>
+        <v>2.244652406417112</v>
       </c>
       <c r="N25">
-        <v>2.244652406417112</v>
+        <v>1.485981308411215</v>
       </c>
       <c r="O25">
-        <v>1.485981308411215</v>
+        <v>3.074576271186441</v>
       </c>
       <c r="P25">
-        <v>3.074576271186441</v>
+        <v>1.496997998665777</v>
       </c>
       <c r="Q25">
-        <v>1.496997998665777</v>
+        <v>2.205607476635514</v>
       </c>
       <c r="R25">
-        <v>2.205607476635514</v>
+        <v>1.807615230460922</v>
       </c>
       <c r="S25">
-        <v>1.807615230460922</v>
-      </c>
-      <c r="T25">
         <v>1.647058823529412</v>
       </c>
+      <c r="U25">
+        <v>1.974025974025974</v>
+      </c>
       <c r="V25">
-        <v>1.974025974025974</v>
+        <v>6.861859838274933</v>
       </c>
       <c r="W25">
-        <v>6.861859838274933</v>
+        <v>0.5110073382254836</v>
       </c>
       <c r="X25">
-        <v>0.5110073382254836</v>
+        <v>39.47698465643762</v>
       </c>
       <c r="Y25">
-        <v>0.4889926617745163</v>
+        <v>0.9973315543695798</v>
       </c>
       <c r="Z25">
-        <v>39.47698465643762</v>
+        <v>4.991298527443106</v>
       </c>
       <c r="AA25">
-        <v>0.9973315543695798</v>
-      </c>
-      <c r="AB25">
-        <v>0.00266844563042028</v>
-      </c>
-      <c r="AC25">
-        <v>4.991298527443106</v>
-      </c>
-      <c r="AD25">
         <v>3.915483434753212</v>
       </c>
     </row>
@@ -2800,73 +2569,67 @@
           <t>Iraq</t>
         </is>
       </c>
+      <c r="D26">
+        <v>3.565</v>
+      </c>
       <c r="E26">
-        <v>3.565</v>
+        <v>2.986666666666667</v>
       </c>
       <c r="F26">
-        <v>2.986666666666667</v>
+        <v>2.415833333333333</v>
       </c>
       <c r="G26">
-        <v>2.415833333333333</v>
+        <v>2.735</v>
       </c>
       <c r="H26">
-        <v>2.735</v>
+        <v>2.6475</v>
       </c>
       <c r="I26">
-        <v>2.6475</v>
-      </c>
-      <c r="J26">
         <v>2.295808383233533</v>
       </c>
+      <c r="K26">
+        <v>2.781666666666667</v>
+      </c>
       <c r="L26">
-        <v>2.781666666666667</v>
-      </c>
-      <c r="M26">
         <v>3.771666666666667</v>
       </c>
+      <c r="N26">
+        <v>2.28</v>
+      </c>
       <c r="O26">
-        <v>2.28</v>
+        <v>2.3975</v>
       </c>
       <c r="P26">
-        <v>2.3975</v>
+        <v>2.615833333333333</v>
       </c>
       <c r="Q26">
-        <v>2.615833333333333</v>
+        <v>3.340833333333333</v>
       </c>
       <c r="R26">
-        <v>3.340833333333333</v>
+        <v>2.491666666666667</v>
       </c>
       <c r="S26">
-        <v>2.491666666666667</v>
-      </c>
-      <c r="T26">
         <v>2.4625</v>
       </c>
+      <c r="U26">
+        <v>2.651666666666667</v>
+      </c>
       <c r="V26">
-        <v>2.651666666666667</v>
+        <v>4.960833333333333</v>
       </c>
       <c r="W26">
-        <v>4.960833333333333</v>
+        <v>0.5066666666666667</v>
       </c>
       <c r="X26">
-        <v>0.5066666666666667</v>
+        <v>36.6025</v>
       </c>
       <c r="Y26">
-        <v>0.4933333333333333</v>
+        <v>1</v>
       </c>
       <c r="Z26">
-        <v>36.6025</v>
+        <v>3.847953216374269</v>
       </c>
       <c r="AA26">
-        <v>1</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>3.847953216374269</v>
-      </c>
-      <c r="AD26">
         <v>4.454166666666667</v>
       </c>
     </row>
@@ -2885,75 +2648,66 @@
         <v>0.97</v>
       </c>
       <c r="D27">
-        <v>0.03</v>
-      </c>
-      <c r="E27">
         <v>2.994915254237288</v>
       </c>
+      <c r="F27">
+        <v>1.375833333333333</v>
+      </c>
       <c r="G27">
-        <v>1.375833333333333</v>
+        <v>2.105616093880972</v>
       </c>
       <c r="H27">
-        <v>2.105616093880972</v>
+        <v>1.443238731218698</v>
       </c>
       <c r="I27">
-        <v>1.443238731218698</v>
-      </c>
-      <c r="J27">
         <v>1.271129707112971</v>
       </c>
+      <c r="K27">
+        <v>1.913879598662207</v>
+      </c>
       <c r="L27">
-        <v>1.913879598662207</v>
+        <v>3.808688387635756</v>
       </c>
       <c r="M27">
-        <v>3.808688387635756</v>
+        <v>1.253768844221105</v>
       </c>
       <c r="N27">
-        <v>1.253768844221105</v>
+        <v>1.235</v>
       </c>
       <c r="O27">
-        <v>1.235</v>
+        <v>1.5</v>
       </c>
       <c r="P27">
-        <v>1.5</v>
+        <v>1.592839300582848</v>
       </c>
       <c r="Q27">
-        <v>1.592839300582848</v>
+        <v>2.548414023372287</v>
       </c>
       <c r="R27">
-        <v>2.548414023372287</v>
+        <v>1.409658617818485</v>
       </c>
       <c r="S27">
-        <v>1.409658617818485</v>
-      </c>
-      <c r="T27">
         <v>1.276755852842809</v>
       </c>
+      <c r="U27">
+        <v>1.303765690376569</v>
+      </c>
       <c r="V27">
-        <v>1.303765690376569</v>
+        <v>5.33585222502099</v>
       </c>
       <c r="W27">
-        <v>5.33585222502099</v>
+        <v>0.5045719035743973</v>
       </c>
       <c r="X27">
-        <v>0.5045719035743973</v>
+        <v>43.3142144638404</v>
       </c>
       <c r="Y27">
-        <v>0.4954280964256026</v>
+        <v>0.8620116375727348</v>
       </c>
       <c r="Z27">
-        <v>43.3142144638404</v>
+        <v>4.166527893422148</v>
       </c>
       <c r="AA27">
-        <v>0.8620116375727348</v>
-      </c>
-      <c r="AB27">
-        <v>0.1379883624272652</v>
-      </c>
-      <c r="AC27">
-        <v>4.166527893422148</v>
-      </c>
-      <c r="AD27">
         <v>4.03765690376569</v>
       </c>
     </row>
@@ -2972,84 +2726,75 @@
         <v>0.2812858783008036</v>
       </c>
       <c r="D28">
-        <v>0.7187141216991964</v>
+        <v>1.763117283950617</v>
       </c>
       <c r="E28">
-        <v>1.763117283950617</v>
+        <v>1.323795180722892</v>
       </c>
       <c r="F28">
-        <v>1.323795180722892</v>
+        <v>1.106766917293233</v>
       </c>
       <c r="G28">
-        <v>1.106766917293233</v>
+        <v>1.257336343115124</v>
       </c>
       <c r="H28">
-        <v>1.257336343115124</v>
+        <v>1.387169811320755</v>
       </c>
       <c r="I28">
-        <v>1.387169811320755</v>
+        <v>6.710180623973727</v>
       </c>
       <c r="J28">
-        <v>6.710180623973727</v>
+        <v>1.976940814757879</v>
       </c>
       <c r="K28">
-        <v>1.976940814757879</v>
+        <v>4.87037037037037</v>
       </c>
       <c r="L28">
-        <v>4.87037037037037</v>
+        <v>6.802873104549082</v>
       </c>
       <c r="M28">
-        <v>6.802873104549082</v>
+        <v>6.873104549082202</v>
       </c>
       <c r="N28">
-        <v>6.873104549082202</v>
+        <v>2.708466453674121</v>
       </c>
       <c r="O28">
-        <v>2.708466453674121</v>
+        <v>6.183508488278092</v>
       </c>
       <c r="P28">
-        <v>6.183508488278092</v>
+        <v>1.266365688487585</v>
       </c>
       <c r="Q28">
-        <v>1.266365688487585</v>
+        <v>1.300978179082017</v>
       </c>
       <c r="R28">
-        <v>1.300978179082017</v>
+        <v>1.306706857573474</v>
       </c>
       <c r="S28">
-        <v>1.306706857573474</v>
+        <v>1.20763358778626</v>
       </c>
       <c r="T28">
-        <v>1.20763358778626</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="U28">
-        <v>2.666666666666667</v>
+        <v>1.386697602474865</v>
       </c>
       <c r="V28">
-        <v>1.386697602474865</v>
+        <v>6.801646090534979</v>
       </c>
       <c r="W28">
-        <v>6.801646090534979</v>
+        <v>0.4360679970436068</v>
       </c>
       <c r="X28">
-        <v>0.4360679970436068</v>
+        <v>54.78048780487805</v>
       </c>
       <c r="Y28">
-        <v>0.5639320029563932</v>
+        <v>0.9902840059790733</v>
       </c>
       <c r="Z28">
-        <v>54.78048780487805</v>
+        <v>5.380703066566941</v>
       </c>
       <c r="AA28">
-        <v>0.9902840059790733</v>
-      </c>
-      <c r="AB28">
-        <v>0.009715994020926755</v>
-      </c>
-      <c r="AC28">
-        <v>5.380703066566941</v>
-      </c>
-      <c r="AD28">
         <v>4.185892116182573</v>
       </c>
     </row>
@@ -3068,84 +2813,75 @@
         <v>0.5957446808510638</v>
       </c>
       <c r="D29">
-        <v>0.4042553191489361</v>
+        <v>3.402997502081599</v>
       </c>
       <c r="E29">
-        <v>3.402997502081599</v>
+        <v>4.280971659919028</v>
       </c>
       <c r="F29">
-        <v>4.280971659919028</v>
+        <v>2.192058346839546</v>
       </c>
       <c r="G29">
-        <v>2.192058346839546</v>
+        <v>2.946369636963696</v>
       </c>
       <c r="H29">
-        <v>2.946369636963696</v>
+        <v>2.244914564686737</v>
       </c>
       <c r="I29">
-        <v>2.244914564686737</v>
+        <v>2.220677671589922</v>
       </c>
       <c r="J29">
-        <v>2.220677671589922</v>
+        <v>2.478751084128361</v>
       </c>
       <c r="K29">
-        <v>2.478751084128361</v>
+        <v>3.507502206531333</v>
       </c>
       <c r="L29">
-        <v>3.507502206531333</v>
+        <v>4.711775043936731</v>
       </c>
       <c r="M29">
-        <v>4.711775043936731</v>
+        <v>4.538804638715432</v>
       </c>
       <c r="N29">
-        <v>4.538804638715432</v>
+        <v>2.276408450704225</v>
       </c>
       <c r="O29">
-        <v>2.276408450704225</v>
+        <v>3.761248852157943</v>
       </c>
       <c r="P29">
-        <v>3.761248852157943</v>
+        <v>2.380912162162162</v>
       </c>
       <c r="Q29">
-        <v>2.380912162162162</v>
+        <v>2.37344398340249</v>
       </c>
       <c r="R29">
-        <v>2.37344398340249</v>
+        <v>2.046511627906977</v>
       </c>
       <c r="S29">
-        <v>2.046511627906977</v>
+        <v>1.82864238410596</v>
       </c>
       <c r="T29">
-        <v>1.82864238410596</v>
+        <v>3.061418685121107</v>
       </c>
       <c r="U29">
-        <v>3.061418685121107</v>
+        <v>2.01510067114094</v>
       </c>
       <c r="V29">
-        <v>2.01510067114094</v>
+        <v>3.484320557491289</v>
       </c>
       <c r="W29">
-        <v>3.484320557491289</v>
+        <v>0.4521943573667712</v>
       </c>
       <c r="X29">
-        <v>0.4521943573667712</v>
+        <v>41.24529780564264</v>
       </c>
       <c r="Y29">
-        <v>0.5478056426332288</v>
+        <v>0.9528672427336999</v>
       </c>
       <c r="Z29">
-        <v>41.24529780564264</v>
+        <v>5.792176039119805</v>
       </c>
       <c r="AA29">
-        <v>0.9528672427336999</v>
-      </c>
-      <c r="AB29">
-        <v>0.04713275726630008</v>
-      </c>
-      <c r="AC29">
-        <v>5.792176039119805</v>
-      </c>
-      <c r="AD29">
         <v>5.529698942229455</v>
       </c>
     </row>
@@ -3164,84 +2900,75 @@
         <v>0.6636288318144159</v>
       </c>
       <c r="D30">
-        <v>0.3363711681855841</v>
+        <v>3.316343042071197</v>
       </c>
       <c r="E30">
-        <v>3.316343042071197</v>
+        <v>3.583197389885807</v>
       </c>
       <c r="F30">
-        <v>3.583197389885807</v>
+        <v>2.917551020408163</v>
       </c>
       <c r="G30">
-        <v>2.917551020408163</v>
+        <v>3.545085296506905</v>
       </c>
       <c r="H30">
-        <v>3.545085296506905</v>
+        <v>3.190746753246753</v>
       </c>
       <c r="I30">
-        <v>3.190746753246753</v>
+        <v>3.006584362139918</v>
       </c>
       <c r="J30">
-        <v>3.006584362139918</v>
+        <v>3.064860426929393</v>
       </c>
       <c r="K30">
-        <v>3.064860426929393</v>
+        <v>3.657679738562091</v>
       </c>
       <c r="L30">
-        <v>3.657679738562091</v>
+        <v>4.737058340180773</v>
       </c>
       <c r="M30">
-        <v>4.737058340180773</v>
+        <v>4.115918367346938</v>
       </c>
       <c r="N30">
-        <v>4.115918367346938</v>
+        <v>2.990107172300082</v>
       </c>
       <c r="O30">
-        <v>2.990107172300082</v>
+        <v>4.063410454155956</v>
       </c>
       <c r="P30">
-        <v>4.063410454155956</v>
+        <v>3.365415986949429</v>
       </c>
       <c r="Q30">
-        <v>3.365415986949429</v>
+        <v>4.70268074735987</v>
       </c>
       <c r="R30">
-        <v>4.70268074735987</v>
+        <v>3.008203445447088</v>
       </c>
       <c r="S30">
-        <v>3.008203445447088</v>
+        <v>2.88</v>
       </c>
       <c r="T30">
-        <v>2.88</v>
+        <v>3.526487367563162</v>
       </c>
       <c r="U30">
-        <v>3.526487367563162</v>
+        <v>2.983646770237122</v>
       </c>
       <c r="V30">
-        <v>2.983646770237122</v>
+        <v>3.651490066225166</v>
       </c>
       <c r="W30">
-        <v>3.651490066225166</v>
+        <v>0.505957108816521</v>
       </c>
       <c r="X30">
-        <v>0.505957108816521</v>
+        <v>30.74027005559968</v>
       </c>
       <c r="Y30">
-        <v>0.4940428911834789</v>
+        <v>0.9960443037974683</v>
       </c>
       <c r="Z30">
-        <v>30.74027005559968</v>
+        <v>4.31031746031746</v>
       </c>
       <c r="AA30">
-        <v>0.9960443037974683</v>
-      </c>
-      <c r="AB30">
-        <v>0.003955696202531646</v>
-      </c>
-      <c r="AC30">
-        <v>4.31031746031746</v>
-      </c>
-      <c r="AD30">
         <v>4.595813204508857</v>
       </c>
     </row>
@@ -3256,82 +2983,76 @@
           <t>Kyrgyzstan</t>
         </is>
       </c>
+      <c r="D31">
+        <v>3.063829787234043</v>
+      </c>
       <c r="E31">
-        <v>3.063829787234043</v>
+        <v>2.733506944444445</v>
       </c>
       <c r="F31">
-        <v>2.733506944444445</v>
+        <v>1.707797772065124</v>
       </c>
       <c r="G31">
-        <v>1.707797772065124</v>
+        <v>2.202749140893471</v>
       </c>
       <c r="H31">
-        <v>2.202749140893471</v>
+        <v>1.745283018867924</v>
       </c>
       <c r="I31">
-        <v>1.745283018867924</v>
+        <v>1.482394366197183</v>
       </c>
       <c r="J31">
-        <v>1.482394366197183</v>
+        <v>1.490845684394071</v>
       </c>
       <c r="K31">
-        <v>1.490845684394071</v>
+        <v>1.805217391304348</v>
       </c>
       <c r="L31">
-        <v>1.805217391304348</v>
+        <v>2.256476683937824</v>
       </c>
       <c r="M31">
-        <v>2.256476683937824</v>
+        <v>2.001748251748252</v>
       </c>
       <c r="N31">
-        <v>2.001748251748252</v>
+        <v>1.419047619047619</v>
       </c>
       <c r="O31">
-        <v>1.419047619047619</v>
+        <v>1.968225948808473</v>
       </c>
       <c r="P31">
-        <v>1.968225948808473</v>
+        <v>1.87510766580534</v>
       </c>
       <c r="Q31">
-        <v>1.87510766580534</v>
+        <v>2.200343938091144</v>
       </c>
       <c r="R31">
-        <v>2.200343938091144</v>
+        <v>1.602067183462532</v>
       </c>
       <c r="S31">
-        <v>1.602067183462532</v>
+        <v>1.481707317073171</v>
       </c>
       <c r="T31">
-        <v>1.481707317073171</v>
+        <v>1.662587412587412</v>
       </c>
       <c r="U31">
-        <v>1.662587412587412</v>
+        <v>1.533158813263525</v>
       </c>
       <c r="V31">
-        <v>1.533158813263525</v>
+        <v>2.147110332749562</v>
       </c>
       <c r="W31">
-        <v>2.147110332749562</v>
+        <v>0.3808333333333334</v>
       </c>
       <c r="X31">
-        <v>0.3808333333333334</v>
+        <v>41.3025</v>
       </c>
       <c r="Y31">
-        <v>0.6191666666666666</v>
+        <v>0.9441201000834029</v>
       </c>
       <c r="Z31">
-        <v>41.3025</v>
+        <v>5.429524603836531</v>
       </c>
       <c r="AA31">
-        <v>0.9441201000834029</v>
-      </c>
-      <c r="AB31">
-        <v>0.05587989991659716</v>
-      </c>
-      <c r="AC31">
-        <v>5.429524603836531</v>
-      </c>
-      <c r="AD31">
         <v>5.052542372881356</v>
       </c>
     </row>
@@ -3350,84 +3071,75 @@
         <v>0.3156626506024096</v>
       </c>
       <c r="D32">
-        <v>0.6843373493975904</v>
+        <v>3.235341365461847</v>
       </c>
       <c r="E32">
-        <v>3.235341365461847</v>
+        <v>2.970281124497992</v>
       </c>
       <c r="F32">
-        <v>2.970281124497992</v>
+        <v>2.214457831325301</v>
       </c>
       <c r="G32">
-        <v>2.214457831325301</v>
+        <v>2.223293172690763</v>
       </c>
       <c r="H32">
-        <v>2.223293172690763</v>
+        <v>2.219277108433735</v>
       </c>
       <c r="I32">
-        <v>2.219277108433735</v>
+        <v>3.232128514056225</v>
       </c>
       <c r="J32">
-        <v>3.232128514056225</v>
+        <v>2.65140562248996</v>
       </c>
       <c r="K32">
-        <v>2.65140562248996</v>
+        <v>3.911646586345381</v>
       </c>
       <c r="L32">
-        <v>3.911646586345381</v>
+        <v>5.260240963855422</v>
       </c>
       <c r="M32">
-        <v>5.260240963855422</v>
+        <v>4.779919678714859</v>
       </c>
       <c r="N32">
-        <v>4.779919678714859</v>
+        <v>2.682730923694779</v>
       </c>
       <c r="O32">
-        <v>2.682730923694779</v>
+        <v>4.434538152610441</v>
       </c>
       <c r="P32">
-        <v>4.434538152610441</v>
+        <v>2.014457831325301</v>
       </c>
       <c r="Q32">
-        <v>2.014457831325301</v>
+        <v>2.398393574297189</v>
       </c>
       <c r="R32">
-        <v>2.398393574297189</v>
+        <v>2.16144578313253</v>
       </c>
       <c r="S32">
-        <v>2.16144578313253</v>
+        <v>2.255421686746988</v>
       </c>
       <c r="T32">
-        <v>2.255421686746988</v>
+        <v>2.514056224899599</v>
       </c>
       <c r="U32">
-        <v>2.514056224899599</v>
+        <v>2.442570281124498</v>
       </c>
       <c r="V32">
-        <v>2.442570281124498</v>
+        <v>4.339759036144578</v>
       </c>
       <c r="W32">
-        <v>4.339759036144578</v>
+        <v>0.4875502008032129</v>
       </c>
       <c r="X32">
-        <v>0.4875502008032129</v>
+        <v>45.62971887550201</v>
       </c>
       <c r="Y32">
-        <v>0.5124497991967871</v>
+        <v>0.989558232931727</v>
       </c>
       <c r="Z32">
-        <v>45.62971887550201</v>
+        <v>5.118072289156626</v>
       </c>
       <c r="AA32">
-        <v>0.989558232931727</v>
-      </c>
-      <c r="AB32">
-        <v>0.01044176706827309</v>
-      </c>
-      <c r="AC32">
-        <v>5.118072289156626</v>
-      </c>
-      <c r="AD32">
         <v>4.840160642570281</v>
       </c>
     </row>
@@ -3446,78 +3158,69 @@
         <v>0.8583333333333333</v>
       </c>
       <c r="D33">
-        <v>0.1416666666666667</v>
-      </c>
-      <c r="E33">
         <v>3.401023890784983</v>
       </c>
+      <c r="F33">
+        <v>1.971356360572873</v>
+      </c>
       <c r="G33">
-        <v>1.971356360572873</v>
+        <v>2.56140350877193</v>
       </c>
       <c r="H33">
-        <v>2.56140350877193</v>
+        <v>2.644166666666667</v>
       </c>
       <c r="I33">
-        <v>2.644166666666667</v>
-      </c>
-      <c r="J33">
         <v>2.338926174496644</v>
       </c>
+      <c r="K33">
+        <v>2.361666666666667</v>
+      </c>
       <c r="L33">
-        <v>2.361666666666667</v>
+        <v>3.944723618090452</v>
       </c>
       <c r="M33">
-        <v>3.944723618090452</v>
+        <v>2.282845188284519</v>
       </c>
       <c r="N33">
-        <v>2.282845188284519</v>
+        <v>2.090833333333333</v>
       </c>
       <c r="O33">
-        <v>2.090833333333333</v>
+        <v>2.356839422259983</v>
       </c>
       <c r="P33">
-        <v>2.356839422259983</v>
+        <v>2.045986622073579</v>
       </c>
       <c r="Q33">
-        <v>2.045986622073579</v>
+        <v>2.536108751062022</v>
       </c>
       <c r="R33">
-        <v>2.536108751062022</v>
+        <v>2.014166666666667</v>
       </c>
       <c r="S33">
-        <v>2.014166666666667</v>
+        <v>1.824267782426778</v>
       </c>
       <c r="T33">
-        <v>1.824267782426778</v>
+        <v>2.1825</v>
       </c>
       <c r="U33">
-        <v>2.1825</v>
+        <v>1.967391304347826</v>
       </c>
       <c r="V33">
-        <v>1.967391304347826</v>
+        <v>3.835769561478934</v>
       </c>
       <c r="W33">
-        <v>3.835769561478934</v>
+        <v>0.5</v>
       </c>
       <c r="X33">
-        <v>0.5</v>
+        <v>40.82666666666667</v>
       </c>
       <c r="Y33">
-        <v>0.5</v>
+        <v>0.9933333333333333</v>
       </c>
       <c r="Z33">
-        <v>40.82666666666667</v>
+        <v>4.693333333333333</v>
       </c>
       <c r="AA33">
-        <v>0.9933333333333333</v>
-      </c>
-      <c r="AB33">
-        <v>0.006666666666666667</v>
-      </c>
-      <c r="AC33">
-        <v>4.693333333333333</v>
-      </c>
-      <c r="AD33">
         <v>5.5175</v>
       </c>
     </row>
@@ -3536,84 +3239,75 @@
         <v>0.9763713080168777</v>
       </c>
       <c r="D34">
-        <v>0.02362869198312236</v>
+        <v>2.623693379790941</v>
       </c>
       <c r="E34">
-        <v>2.623693379790941</v>
+        <v>1.606113537117904</v>
       </c>
       <c r="F34">
-        <v>1.606113537117904</v>
+        <v>1.158390410958904</v>
       </c>
       <c r="G34">
-        <v>1.158390410958904</v>
+        <v>1.493528904227783</v>
       </c>
       <c r="H34">
-        <v>1.493528904227783</v>
+        <v>1.244386873920553</v>
       </c>
       <c r="I34">
-        <v>1.244386873920553</v>
+        <v>1.117173524150268</v>
       </c>
       <c r="J34">
-        <v>1.117173524150268</v>
+        <v>1.133453561767358</v>
       </c>
       <c r="K34">
-        <v>1.133453561767358</v>
+        <v>1.581705150976909</v>
       </c>
       <c r="L34">
-        <v>1.581705150976909</v>
+        <v>3.682581786030062</v>
       </c>
       <c r="M34">
-        <v>3.682581786030062</v>
+        <v>1.116197183098592</v>
       </c>
       <c r="N34">
-        <v>1.116197183098592</v>
+        <v>1.151009657594381</v>
       </c>
       <c r="O34">
-        <v>1.151009657594381</v>
+        <v>1.209405501330967</v>
       </c>
       <c r="P34">
-        <v>1.209405501330967</v>
+        <v>1.699912510936133</v>
       </c>
       <c r="Q34">
-        <v>1.699912510936133</v>
+        <v>3.048993875765529</v>
       </c>
       <c r="R34">
-        <v>3.048993875765529</v>
+        <v>1.306479859894921</v>
       </c>
       <c r="S34">
-        <v>1.306479859894921</v>
+        <v>1.124778761061947</v>
       </c>
       <c r="T34">
-        <v>1.124778761061947</v>
+        <v>1.064601769911504</v>
       </c>
       <c r="U34">
-        <v>1.064601769911504</v>
+        <v>1.193433895297249</v>
       </c>
       <c r="V34">
-        <v>1.193433895297249</v>
+        <v>4.542039355992844</v>
       </c>
       <c r="W34">
-        <v>4.542039355992844</v>
+        <v>0.5175585284280937</v>
       </c>
       <c r="X34">
-        <v>0.5175585284280937</v>
+        <v>40.21772151898734</v>
       </c>
       <c r="Y34">
-        <v>0.4824414715719064</v>
+        <v>0.9908026755852842</v>
       </c>
       <c r="Z34">
-        <v>40.21772151898734</v>
+        <v>5.334728033472803</v>
       </c>
       <c r="AA34">
-        <v>0.9908026755852842</v>
-      </c>
-      <c r="AB34">
-        <v>0.00919732441471572</v>
-      </c>
-      <c r="AC34">
-        <v>5.334728033472803</v>
-      </c>
-      <c r="AD34">
         <v>5.439407149084569</v>
       </c>
     </row>
@@ -3632,84 +3326,75 @@
         <v>0.3135509396636993</v>
       </c>
       <c r="D35">
-        <v>0.6864490603363007</v>
+        <v>2.793542074363992</v>
       </c>
       <c r="E35">
-        <v>2.793542074363992</v>
+        <v>2.515655577299413</v>
       </c>
       <c r="F35">
-        <v>2.515655577299413</v>
+        <v>2.258317025440313</v>
       </c>
       <c r="G35">
-        <v>2.258317025440313</v>
+        <v>2.292156862745098</v>
       </c>
       <c r="H35">
-        <v>2.292156862745098</v>
+        <v>2.375614552605703</v>
       </c>
       <c r="I35">
-        <v>2.375614552605703</v>
+        <v>5.258570029382958</v>
       </c>
       <c r="J35">
-        <v>5.258570029382958</v>
+        <v>3.306862745098039</v>
       </c>
       <c r="K35">
-        <v>3.306862745098039</v>
+        <v>3.877690802348337</v>
       </c>
       <c r="L35">
-        <v>3.877690802348337</v>
+        <v>5.379547689282203</v>
       </c>
       <c r="M35">
-        <v>5.379547689282203</v>
+        <v>5.672227674190383</v>
       </c>
       <c r="N35">
-        <v>5.672227674190383</v>
+        <v>3.419449901768173</v>
       </c>
       <c r="O35">
-        <v>3.419449901768173</v>
+        <v>5.157016683022571</v>
       </c>
       <c r="P35">
-        <v>5.157016683022571</v>
+        <v>2.225490196078431</v>
       </c>
       <c r="Q35">
-        <v>2.225490196078431</v>
+        <v>3.517173699705594</v>
       </c>
       <c r="R35">
-        <v>3.517173699705594</v>
+        <v>2.314033366045142</v>
       </c>
       <c r="S35">
-        <v>2.314033366045142</v>
+        <v>2.775811209439528</v>
       </c>
       <c r="T35">
-        <v>2.775811209439528</v>
+        <v>3.467059980334317</v>
       </c>
       <c r="U35">
-        <v>3.467059980334317</v>
+        <v>2.557409224730128</v>
       </c>
       <c r="V35">
-        <v>2.557409224730128</v>
+        <v>3.986247544204322</v>
       </c>
       <c r="W35">
-        <v>3.986247544204322</v>
+        <v>0.4403131115459882</v>
       </c>
       <c r="X35">
-        <v>0.4403131115459882</v>
+        <v>40.68880688806888</v>
       </c>
       <c r="Y35">
-        <v>0.5596868884540117</v>
+        <v>0.5827619980411362</v>
       </c>
       <c r="Z35">
-        <v>40.68880688806888</v>
+        <v>4.84984984984985</v>
       </c>
       <c r="AA35">
-        <v>0.5827619980411362</v>
-      </c>
-      <c r="AB35">
-        <v>0.4172380019588638</v>
-      </c>
-      <c r="AC35">
-        <v>4.84984984984985</v>
-      </c>
-      <c r="AD35">
         <v>5.024557956777996</v>
       </c>
     </row>
@@ -3728,84 +3413,75 @@
         <v>0.9766666666666667</v>
       </c>
       <c r="D36">
-        <v>0.02333333333333333</v>
+        <v>3.6775</v>
       </c>
       <c r="E36">
-        <v>3.6775</v>
+        <v>3.13</v>
       </c>
       <c r="F36">
-        <v>3.13</v>
+        <v>2.515833333333333</v>
       </c>
       <c r="G36">
-        <v>2.515833333333333</v>
+        <v>2.830833333333334</v>
       </c>
       <c r="H36">
-        <v>2.830833333333334</v>
+        <v>2.785833333333333</v>
       </c>
       <c r="I36">
-        <v>2.785833333333333</v>
+        <v>2.77</v>
       </c>
       <c r="J36">
-        <v>2.77</v>
+        <v>2.781666666666667</v>
       </c>
       <c r="K36">
-        <v>2.781666666666667</v>
+        <v>3.62</v>
       </c>
       <c r="L36">
-        <v>3.62</v>
+        <v>5.710833333333333</v>
       </c>
       <c r="M36">
-        <v>5.710833333333333</v>
+        <v>3.1425</v>
       </c>
       <c r="N36">
-        <v>3.1425</v>
+        <v>2.940833333333333</v>
       </c>
       <c r="O36">
-        <v>2.940833333333333</v>
+        <v>3.193333333333333</v>
       </c>
       <c r="P36">
-        <v>3.193333333333333</v>
+        <v>3.2725</v>
       </c>
       <c r="Q36">
-        <v>3.2725</v>
+        <v>4.703333333333333</v>
       </c>
       <c r="R36">
-        <v>4.703333333333333</v>
+        <v>2.821666666666667</v>
       </c>
       <c r="S36">
-        <v>2.821666666666667</v>
+        <v>2.345833333333333</v>
       </c>
       <c r="T36">
-        <v>2.345833333333333</v>
+        <v>2.735833333333333</v>
       </c>
       <c r="U36">
-        <v>2.735833333333333</v>
+        <v>2.539166666666667</v>
       </c>
       <c r="V36">
-        <v>2.539166666666667</v>
+        <v>4.303333333333334</v>
       </c>
       <c r="W36">
-        <v>4.303333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="X36">
-        <v>0.5</v>
+        <v>37.22</v>
       </c>
       <c r="Y36">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Z36">
-        <v>37.22</v>
+        <v>3.479166666666667</v>
       </c>
       <c r="AA36">
-        <v>1</v>
-      </c>
-      <c r="AB36">
-        <v>0</v>
-      </c>
-      <c r="AC36">
-        <v>3.479166666666667</v>
-      </c>
-      <c r="AD36">
         <v>5.228333333333333</v>
       </c>
     </row>
@@ -3824,84 +3500,75 @@
         <v>0.995159728944821</v>
       </c>
       <c r="D37">
-        <v>0.00484027105517909</v>
+        <v>1.856316297010608</v>
       </c>
       <c r="E37">
-        <v>1.856316297010608</v>
+        <v>2.423484119345524</v>
       </c>
       <c r="F37">
-        <v>2.423484119345524</v>
+        <v>1.294970986460348</v>
       </c>
       <c r="G37">
-        <v>1.294970986460348</v>
+        <v>1.393822393822394</v>
       </c>
       <c r="H37">
-        <v>1.393822393822394</v>
+        <v>1.28873917228104</v>
       </c>
       <c r="I37">
-        <v>1.28873917228104</v>
+        <v>1.261078998073218</v>
       </c>
       <c r="J37">
-        <v>1.261078998073218</v>
+        <v>1.226615236258438</v>
       </c>
       <c r="K37">
-        <v>1.226615236258438</v>
+        <v>2.530376084860174</v>
       </c>
       <c r="L37">
-        <v>2.530376084860174</v>
+        <v>5.723938223938224</v>
       </c>
       <c r="M37">
-        <v>5.723938223938224</v>
+        <v>1.647683397683398</v>
       </c>
       <c r="N37">
-        <v>1.647683397683398</v>
+        <v>1.411934552454283</v>
       </c>
       <c r="O37">
-        <v>1.411934552454283</v>
+        <v>2.004840271055179</v>
       </c>
       <c r="P37">
-        <v>2.004840271055179</v>
+        <v>1.162970106075217</v>
       </c>
       <c r="Q37">
-        <v>1.162970106075217</v>
+        <v>1.3747591522158</v>
       </c>
       <c r="R37">
-        <v>1.3747591522158</v>
+        <v>1.240115718418515</v>
       </c>
       <c r="S37">
-        <v>1.240115718418515</v>
+        <v>1.216007714561234</v>
       </c>
       <c r="T37">
-        <v>1.216007714561234</v>
+        <v>1.327552986512524</v>
       </c>
       <c r="U37">
-        <v>1.327552986512524</v>
+        <v>1.215458937198068</v>
       </c>
       <c r="V37">
-        <v>1.215458937198068</v>
+        <v>7.185149469623915</v>
       </c>
       <c r="W37">
-        <v>7.185149469623915</v>
+        <v>0.4714975845410628</v>
       </c>
       <c r="X37">
-        <v>0.4714975845410628</v>
+        <v>37.65250965250965</v>
       </c>
       <c r="Y37">
-        <v>0.5285024154589372</v>
+        <v>0.9932627526467758</v>
       </c>
       <c r="Z37">
-        <v>37.65250965250965</v>
+        <v>3.693719806763285</v>
       </c>
       <c r="AA37">
-        <v>0.9932627526467758</v>
-      </c>
-      <c r="AB37">
-        <v>0.006737247353224254</v>
-      </c>
-      <c r="AC37">
-        <v>3.693719806763285</v>
-      </c>
-      <c r="AD37">
         <v>5.944820909970958</v>
       </c>
     </row>
@@ -3920,84 +3587,75 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="D38">
-        <v>0.3888888888888889</v>
+        <v>4.696916812100058</v>
       </c>
       <c r="E38">
-        <v>4.696916812100058</v>
+        <v>4.300987797791981</v>
       </c>
       <c r="F38">
-        <v>4.300987797791981</v>
+        <v>2.33467974610502</v>
       </c>
       <c r="G38">
-        <v>2.33467974610502</v>
+        <v>2.979674796747967</v>
       </c>
       <c r="H38">
-        <v>2.979674796747967</v>
+        <v>2.647469458987783</v>
       </c>
       <c r="I38">
-        <v>2.647469458987783</v>
+        <v>4.338661930136175</v>
       </c>
       <c r="J38">
-        <v>4.338661930136175</v>
+        <v>3.620164126611958</v>
       </c>
       <c r="K38">
-        <v>3.620164126611958</v>
+        <v>3.251168224299065</v>
       </c>
       <c r="L38">
-        <v>3.251168224299065</v>
+        <v>5.040603248259861</v>
       </c>
       <c r="M38">
-        <v>5.040603248259861</v>
+        <v>4.755711775043936</v>
       </c>
       <c r="N38">
-        <v>4.755711775043936</v>
+        <v>2.768782760629004</v>
       </c>
       <c r="O38">
-        <v>2.768782760629004</v>
+        <v>3.767867690490254</v>
       </c>
       <c r="P38">
-        <v>3.767867690490254</v>
+        <v>2.197687861271676</v>
       </c>
       <c r="Q38">
-        <v>2.197687861271676</v>
+        <v>3.085217391304348</v>
       </c>
       <c r="R38">
-        <v>3.085217391304348</v>
+        <v>2.391178177597214</v>
       </c>
       <c r="S38">
-        <v>2.391178177597214</v>
+        <v>2.334701055099648</v>
       </c>
       <c r="T38">
-        <v>2.334701055099648</v>
+        <v>3.320921985815603</v>
       </c>
       <c r="U38">
-        <v>3.320921985815603</v>
+        <v>2.491822429906542</v>
       </c>
       <c r="V38">
-        <v>2.491822429906542</v>
+        <v>3.63785046728972</v>
       </c>
       <c r="W38">
-        <v>3.63785046728972</v>
+        <v>0.5020103388856979</v>
       </c>
       <c r="X38">
-        <v>0.5020103388856979</v>
+        <v>43.35825186889016</v>
       </c>
       <c r="Y38">
-        <v>0.4979896611143022</v>
+        <v>1</v>
       </c>
       <c r="Z38">
-        <v>43.35825186889016</v>
+        <v>4.023081361800346</v>
       </c>
       <c r="AA38">
-        <v>1</v>
-      </c>
-      <c r="AB38">
-        <v>0</v>
-      </c>
-      <c r="AC38">
-        <v>4.023081361800346</v>
-      </c>
-      <c r="AD38">
         <v>4.228621291448516</v>
       </c>
     </row>
@@ -4016,84 +3674,75 @@
         <v>0.9075</v>
       </c>
       <c r="D39">
-        <v>0.0925</v>
+        <v>3.654712260216848</v>
       </c>
       <c r="E39">
-        <v>3.654712260216848</v>
+        <v>3.161236424394319</v>
       </c>
       <c r="F39">
-        <v>3.161236424394319</v>
+        <v>1.488740617180984</v>
       </c>
       <c r="G39">
-        <v>1.488740617180984</v>
+        <v>1.621666666666667</v>
       </c>
       <c r="H39">
-        <v>1.621666666666667</v>
+        <v>1.721666666666667</v>
       </c>
       <c r="I39">
-        <v>1.721666666666667</v>
+        <v>1.721434528773978</v>
       </c>
       <c r="J39">
-        <v>1.721434528773978</v>
+        <v>1.849040867389491</v>
       </c>
       <c r="K39">
-        <v>1.849040867389491</v>
+        <v>1.410341951626355</v>
       </c>
       <c r="L39">
-        <v>1.410341951626355</v>
+        <v>2.448247078464107</v>
       </c>
       <c r="M39">
-        <v>2.448247078464107</v>
+        <v>1.629382303839733</v>
       </c>
       <c r="N39">
-        <v>1.629382303839733</v>
+        <v>1.359466221851543</v>
       </c>
       <c r="O39">
-        <v>1.359466221851543</v>
+        <v>1.946577629382304</v>
       </c>
       <c r="P39">
-        <v>1.946577629382304</v>
+        <v>1.533778148457048</v>
       </c>
       <c r="Q39">
-        <v>1.533778148457048</v>
+        <v>5.039166666666667</v>
       </c>
       <c r="R39">
-        <v>5.039166666666667</v>
+        <v>1.438698915763136</v>
       </c>
       <c r="S39">
-        <v>1.438698915763136</v>
+        <v>1.549624687239366</v>
       </c>
       <c r="T39">
-        <v>1.549624687239366</v>
+        <v>1.386155129274395</v>
       </c>
       <c r="U39">
-        <v>1.386155129274395</v>
+        <v>1.433694745621351</v>
       </c>
       <c r="V39">
-        <v>1.433694745621351</v>
+        <v>3.932330827067669</v>
       </c>
       <c r="W39">
-        <v>3.932330827067669</v>
+        <v>0.5008333333333334</v>
       </c>
       <c r="X39">
-        <v>0.5008333333333334</v>
+        <v>40.43166666666666</v>
       </c>
       <c r="Y39">
-        <v>0.4991666666666666</v>
+        <v>1</v>
       </c>
       <c r="Z39">
-        <v>40.43166666666666</v>
+        <v>3.377295492487479</v>
       </c>
       <c r="AA39">
-        <v>1</v>
-      </c>
-      <c r="AB39">
-        <v>0</v>
-      </c>
-      <c r="AC39">
-        <v>3.377295492487479</v>
-      </c>
-      <c r="AD39">
         <v>4.7025</v>
       </c>
     </row>
@@ -4112,84 +3761,75 @@
         <v>0.4334554334554335</v>
       </c>
       <c r="D40">
-        <v>0.5665445665445665</v>
+        <v>3.83302752293578</v>
       </c>
       <c r="E40">
-        <v>3.83302752293578</v>
+        <v>3.964590964590965</v>
       </c>
       <c r="F40">
-        <v>3.964590964590965</v>
+        <v>3.29059829059829</v>
       </c>
       <c r="G40">
-        <v>3.29059829059829</v>
+        <v>3.592796092796093</v>
       </c>
       <c r="H40">
-        <v>3.592796092796093</v>
+        <v>3.427960927960928</v>
       </c>
       <c r="I40">
-        <v>3.427960927960928</v>
+        <v>3.874236874236874</v>
       </c>
       <c r="J40">
-        <v>3.874236874236874</v>
+        <v>3.39010989010989</v>
       </c>
       <c r="K40">
-        <v>3.39010989010989</v>
+        <v>4.178876678876679</v>
       </c>
       <c r="L40">
-        <v>4.178876678876679</v>
+        <v>4.509157509157509</v>
       </c>
       <c r="M40">
-        <v>4.509157509157509</v>
+        <v>4.535409035409035</v>
       </c>
       <c r="N40">
-        <v>4.535409035409035</v>
+        <v>3.273504273504273</v>
       </c>
       <c r="O40">
-        <v>3.273504273504273</v>
+        <v>3.927350427350427</v>
       </c>
       <c r="P40">
-        <v>3.927350427350427</v>
+        <v>3.337606837606838</v>
       </c>
       <c r="Q40">
-        <v>3.337606837606838</v>
+        <v>3.664835164835165</v>
       </c>
       <c r="R40">
-        <v>3.664835164835165</v>
+        <v>3.190476190476191</v>
       </c>
       <c r="S40">
-        <v>3.190476190476191</v>
+        <v>3.182539682539682</v>
       </c>
       <c r="T40">
-        <v>3.182539682539682</v>
+        <v>3.832722832722833</v>
       </c>
       <c r="U40">
-        <v>3.832722832722833</v>
+        <v>3.297313797313797</v>
       </c>
       <c r="V40">
-        <v>3.297313797313797</v>
+        <v>5.177045177045177</v>
       </c>
       <c r="W40">
-        <v>5.177045177045177</v>
+        <v>0.4835164835164835</v>
       </c>
       <c r="X40">
-        <v>0.4835164835164835</v>
+        <v>38.7985347985348</v>
       </c>
       <c r="Y40">
-        <v>0.5164835164835165</v>
+        <v>1</v>
       </c>
       <c r="Z40">
-        <v>38.7985347985348</v>
+        <v>5.645299145299146</v>
       </c>
       <c r="AA40">
-        <v>1</v>
-      </c>
-      <c r="AB40">
-        <v>0</v>
-      </c>
-      <c r="AC40">
-        <v>5.645299145299146</v>
-      </c>
-      <c r="AD40">
         <v>5.493894993894994</v>
       </c>
     </row>
@@ -4208,84 +3848,75 @@
         <v>0.8773800456968773</v>
       </c>
       <c r="D41">
-        <v>0.1226199543031226</v>
+        <v>4.395277989337395</v>
       </c>
       <c r="E41">
-        <v>4.395277989337395</v>
+        <v>3.979436405178979</v>
       </c>
       <c r="F41">
-        <v>3.979436405178979</v>
+        <v>3.0997715156131</v>
       </c>
       <c r="G41">
-        <v>3.0997715156131</v>
+        <v>3.408987052551409</v>
       </c>
       <c r="H41">
-        <v>3.408987052551409</v>
+        <v>3.084539223153084</v>
       </c>
       <c r="I41">
-        <v>3.084539223153084</v>
+        <v>3.594059405940594</v>
       </c>
       <c r="J41">
+        <v>3.387661843107387</v>
+      </c>
+      <c r="K41">
+        <v>3.524752475247525</v>
+      </c>
+      <c r="L41">
+        <v>4.642802741812643</v>
+      </c>
+      <c r="M41">
+        <v>3.821020563594821</v>
+      </c>
+      <c r="N41">
+        <v>3.15003808073115</v>
+      </c>
+      <c r="O41">
+        <v>3.953541507996953</v>
+      </c>
+      <c r="P41">
+        <v>3.134805788271135</v>
+      </c>
+      <c r="Q41">
+        <v>4.466108149276466</v>
+      </c>
+      <c r="R41">
+        <v>3.276466108149276</v>
+      </c>
+      <c r="S41">
+        <v>3.104341203351104</v>
+      </c>
+      <c r="T41">
         <v>3.594059405940594</v>
       </c>
-      <c r="K41">
-        <v>3.387661843107387</v>
-      </c>
-      <c r="L41">
-        <v>3.524752475247525</v>
-      </c>
-      <c r="M41">
-        <v>4.642802741812643</v>
-      </c>
-      <c r="N41">
-        <v>3.821020563594821</v>
-      </c>
-      <c r="O41">
-        <v>3.15003808073115</v>
-      </c>
-      <c r="P41">
-        <v>3.953541507996953</v>
-      </c>
-      <c r="Q41">
-        <v>3.134805788271135</v>
-      </c>
-      <c r="R41">
-        <v>4.466108149276466</v>
-      </c>
-      <c r="S41">
-        <v>3.276466108149276</v>
-      </c>
-      <c r="T41">
-        <v>3.104341203351104</v>
-      </c>
       <c r="U41">
-        <v>3.594059405940594</v>
+        <v>3.148514851485149</v>
       </c>
       <c r="V41">
-        <v>3.148514851485149</v>
+        <v>4.575019040365575</v>
       </c>
       <c r="W41">
-        <v>4.575019040365575</v>
+        <v>0.5003808073115004</v>
       </c>
       <c r="X41">
-        <v>0.5003808073115004</v>
+        <v>38.32977913175933</v>
       </c>
       <c r="Y41">
-        <v>0.4996191926884996</v>
+        <v>0.9885757806549885</v>
       </c>
       <c r="Z41">
-        <v>38.32977913175933</v>
+        <v>4.344249809596344</v>
       </c>
       <c r="AA41">
-        <v>0.9885757806549885</v>
-      </c>
-      <c r="AB41">
-        <v>0.01142421934501143</v>
-      </c>
-      <c r="AC41">
-        <v>4.344249809596344</v>
-      </c>
-      <c r="AD41">
         <v>4.601675552170602</v>
       </c>
     </row>
@@ -4304,84 +3935,75 @@
         <v>0.8528698464025869</v>
       </c>
       <c r="D42">
-        <v>0.1471301535974131</v>
+        <v>2.0032414910859</v>
       </c>
       <c r="E42">
-        <v>2.0032414910859</v>
+        <v>2.016220600162206</v>
       </c>
       <c r="F42">
-        <v>2.016220600162206</v>
+        <v>1.679352226720648</v>
       </c>
       <c r="G42">
-        <v>1.679352226720648</v>
+        <v>1.789303079416532</v>
       </c>
       <c r="H42">
-        <v>1.789303079416532</v>
+        <v>1.71417004048583</v>
       </c>
       <c r="I42">
-        <v>1.71417004048583</v>
+        <v>1.5</v>
       </c>
       <c r="J42">
-        <v>1.5</v>
+        <v>1.635036496350365</v>
       </c>
       <c r="K42">
-        <v>1.635036496350365</v>
+        <v>1.708706265256306</v>
       </c>
       <c r="L42">
-        <v>1.708706265256306</v>
+        <v>2.475609756097561</v>
       </c>
       <c r="M42">
-        <v>2.475609756097561</v>
+        <v>2.690923957481603</v>
       </c>
       <c r="N42">
-        <v>2.690923957481603</v>
+        <v>1.552588996763754</v>
       </c>
       <c r="O42">
-        <v>1.552588996763754</v>
+        <v>1.647506339814032</v>
       </c>
       <c r="P42">
-        <v>1.647506339814032</v>
+        <v>1.944939271255061</v>
       </c>
       <c r="Q42">
-        <v>1.944939271255061</v>
+        <v>6.049352750809062</v>
       </c>
       <c r="R42">
-        <v>6.049352750809062</v>
+        <v>1.854486661277284</v>
       </c>
       <c r="S42">
-        <v>1.854486661277284</v>
+        <v>1.661003236245955</v>
       </c>
       <c r="T42">
-        <v>1.661003236245955</v>
+        <v>2.559902200488998</v>
       </c>
       <c r="U42">
-        <v>2.559902200488998</v>
+        <v>1.704692556634304</v>
       </c>
       <c r="V42">
-        <v>1.704692556634304</v>
+        <v>2.621311475409836</v>
       </c>
       <c r="W42">
-        <v>2.621311475409836</v>
+        <v>0.5117219078415521</v>
       </c>
       <c r="X42">
-        <v>0.5117219078415521</v>
+        <v>32.56345998383185</v>
       </c>
       <c r="Y42">
-        <v>0.4882780921584479</v>
+        <v>0.9967663702506063</v>
       </c>
       <c r="Z42">
-        <v>32.56345998383185</v>
+        <v>3.588762214983714</v>
       </c>
       <c r="AA42">
-        <v>0.9967663702506063</v>
-      </c>
-      <c r="AB42">
-        <v>0.003233629749393694</v>
-      </c>
-      <c r="AC42">
-        <v>3.588762214983714</v>
-      </c>
-      <c r="AD42">
         <v>4.411908646003263</v>
       </c>
     </row>
@@ -4400,84 +4022,75 @@
         <v>0.2583333333333334</v>
       </c>
       <c r="D43">
-        <v>0.7416666666666667</v>
+        <v>4.038333333333333</v>
       </c>
       <c r="E43">
-        <v>4.038333333333333</v>
+        <v>3.65</v>
       </c>
       <c r="F43">
-        <v>3.65</v>
+        <v>1.66</v>
       </c>
       <c r="G43">
-        <v>1.66</v>
+        <v>2.19</v>
       </c>
       <c r="H43">
-        <v>2.19</v>
+        <v>2.134166666666667</v>
       </c>
       <c r="I43">
-        <v>2.134166666666667</v>
+        <v>3.264166666666667</v>
       </c>
       <c r="J43">
-        <v>3.264166666666667</v>
+        <v>2.703333333333333</v>
       </c>
       <c r="K43">
-        <v>2.703333333333333</v>
+        <v>2.0525</v>
       </c>
       <c r="L43">
-        <v>2.0525</v>
+        <v>4.48</v>
       </c>
       <c r="M43">
-        <v>4.48</v>
+        <v>4.088333333333333</v>
       </c>
       <c r="N43">
-        <v>4.088333333333333</v>
+        <v>1.800833333333333</v>
       </c>
       <c r="O43">
-        <v>1.800833333333333</v>
+        <v>2.47</v>
       </c>
       <c r="P43">
-        <v>2.47</v>
+        <v>1.585833333333333</v>
       </c>
       <c r="Q43">
-        <v>1.585833333333333</v>
+        <v>4.3525</v>
       </c>
       <c r="R43">
-        <v>4.3525</v>
+        <v>1.975</v>
       </c>
       <c r="S43">
-        <v>1.975</v>
+        <v>1.995833333333333</v>
       </c>
       <c r="T43">
-        <v>1.995833333333333</v>
+        <v>3.425</v>
       </c>
       <c r="U43">
-        <v>3.425</v>
+        <v>2.076666666666667</v>
       </c>
       <c r="V43">
-        <v>2.076666666666667</v>
+        <v>2.313333333333333</v>
       </c>
       <c r="W43">
-        <v>2.313333333333333</v>
+        <v>0.4908333333333333</v>
       </c>
       <c r="X43">
-        <v>0.4908333333333333</v>
+        <v>35.1325</v>
       </c>
       <c r="Y43">
-        <v>0.5091666666666667</v>
+        <v>0.9983333333333333</v>
       </c>
       <c r="Z43">
-        <v>35.1325</v>
+        <v>3.735613010842369</v>
       </c>
       <c r="AA43">
-        <v>0.9983333333333333</v>
-      </c>
-      <c r="AB43">
-        <v>0.001666666666666667</v>
-      </c>
-      <c r="AC43">
-        <v>3.735613010842369</v>
-      </c>
-      <c r="AD43">
         <v>4.579166666666667</v>
       </c>
     </row>
@@ -4496,81 +4109,72 @@
         <v>0.4797136038186158</v>
       </c>
       <c r="D44">
-        <v>0.5202863961813843</v>
+        <v>2.173033707865168</v>
       </c>
       <c r="E44">
-        <v>2.173033707865168</v>
+        <v>2.531531531531531</v>
       </c>
       <c r="F44">
-        <v>2.531531531531531</v>
+        <v>1.307174887892377</v>
       </c>
       <c r="G44">
-        <v>1.307174887892377</v>
+        <v>1.954954954954955</v>
       </c>
       <c r="H44">
-        <v>1.954954954954955</v>
+        <v>1.349775784753363</v>
       </c>
       <c r="I44">
-        <v>1.349775784753363</v>
+        <v>6.593533487297922</v>
       </c>
       <c r="J44">
-        <v>6.593533487297922</v>
+        <v>3.850917431192661</v>
       </c>
       <c r="K44">
-        <v>3.850917431192661</v>
+        <v>4.867579908675799</v>
       </c>
       <c r="L44">
-        <v>4.867579908675799</v>
+        <v>6.930022573363432</v>
       </c>
       <c r="M44">
-        <v>6.930022573363432</v>
+        <v>7.091324200913242</v>
       </c>
       <c r="N44">
-        <v>7.091324200913242</v>
+        <v>3.267281105990783</v>
       </c>
       <c r="O44">
-        <v>3.267281105990783</v>
-      </c>
-      <c r="P44">
         <v>5.619047619047619</v>
       </c>
+      <c r="Q44">
+        <v>1.910112359550562</v>
+      </c>
       <c r="R44">
-        <v>1.910112359550562</v>
+        <v>1.677130044843049</v>
       </c>
       <c r="S44">
-        <v>1.677130044843049</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="T44">
-        <v>1.416666666666667</v>
+        <v>5.401805869074492</v>
       </c>
       <c r="U44">
-        <v>5.401805869074492</v>
+        <v>1.556306306306306</v>
       </c>
       <c r="V44">
-        <v>1.556306306306306</v>
+        <v>4.13963963963964</v>
       </c>
       <c r="W44">
-        <v>4.13963963963964</v>
+        <v>0.4988814317673378</v>
       </c>
       <c r="X44">
-        <v>0.4988814317673378</v>
+        <v>52.07451923076923</v>
       </c>
       <c r="Y44">
-        <v>0.5011185682326622</v>
+        <v>0.916289592760181</v>
       </c>
       <c r="Z44">
-        <v>52.07451923076923</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="AA44">
-        <v>0.916289592760181</v>
-      </c>
-      <c r="AB44">
-        <v>0.083710407239819</v>
-      </c>
-      <c r="AC44">
-        <v>4.833333333333333</v>
-      </c>
-      <c r="AD44">
         <v>5.377049180327869</v>
       </c>
     </row>
@@ -4589,84 +4193,75 @@
         <v>0.1370558375634518</v>
       </c>
       <c r="D45">
-        <v>0.8629441624365483</v>
+        <v>1.569387755102041</v>
       </c>
       <c r="E45">
-        <v>1.569387755102041</v>
+        <v>2.095383054287164</v>
       </c>
       <c r="F45">
-        <v>2.095383054287164</v>
+        <v>1.347145022738757</v>
       </c>
       <c r="G45">
-        <v>1.347145022738757</v>
+        <v>1.857432775240994</v>
       </c>
       <c r="H45">
-        <v>1.857432775240994</v>
+        <v>1.462259239979178</v>
       </c>
       <c r="I45">
-        <v>1.462259239979178</v>
+        <v>9.03134962805526</v>
       </c>
       <c r="J45">
-        <v>9.03134962805526</v>
+        <v>6.227717391304348</v>
       </c>
       <c r="K45">
-        <v>6.227717391304348</v>
+        <v>7.637894736842105</v>
       </c>
       <c r="L45">
-        <v>7.637894736842105</v>
+        <v>8.193850964043772</v>
       </c>
       <c r="M45">
-        <v>8.193850964043772</v>
+        <v>8.82712215320911</v>
       </c>
       <c r="N45">
-        <v>8.82712215320911</v>
+        <v>5.38557637705849</v>
       </c>
       <c r="O45">
-        <v>5.38557637705849</v>
+        <v>7.562043795620438</v>
       </c>
       <c r="P45">
-        <v>7.562043795620438</v>
+        <v>1.282542885973764</v>
       </c>
       <c r="Q45">
-        <v>1.282542885973764</v>
+        <v>1.72970247100353</v>
       </c>
       <c r="R45">
-        <v>1.72970247100353</v>
+        <v>1.713853904282116</v>
       </c>
       <c r="S45">
-        <v>1.713853904282116</v>
+        <v>1.192991366175724</v>
       </c>
       <c r="T45">
-        <v>1.192991366175724</v>
+        <v>7.179295624332978</v>
       </c>
       <c r="U45">
-        <v>7.179295624332978</v>
+        <v>1.551706308169597</v>
       </c>
       <c r="V45">
-        <v>1.551706308169597</v>
+        <v>3.401566579634465</v>
       </c>
       <c r="W45">
-        <v>3.401566579634465</v>
+        <v>0.4629370629370629</v>
       </c>
       <c r="X45">
-        <v>0.4629370629370629</v>
+        <v>53.35990675990676</v>
       </c>
       <c r="Y45">
-        <v>0.5370629370629371</v>
+        <v>0.8905698436712053</v>
       </c>
       <c r="Z45">
-        <v>53.35990675990676</v>
+        <v>5.732451678535097</v>
       </c>
       <c r="AA45">
-        <v>0.8905698436712053</v>
-      </c>
-      <c r="AB45">
-        <v>0.1094301563287948</v>
-      </c>
-      <c r="AC45">
-        <v>5.732451678535097</v>
-      </c>
-      <c r="AD45">
         <v>5.78134284016637</v>
       </c>
     </row>
@@ -4685,84 +4280,75 @@
         <v>0.2370637785800241</v>
       </c>
       <c r="D46">
-        <v>0.762936221419976</v>
+        <v>1.986247544204322</v>
       </c>
       <c r="E46">
-        <v>1.986247544204322</v>
+        <v>2.148003894839338</v>
       </c>
       <c r="F46">
-        <v>2.148003894839338</v>
+        <v>1.385436893203883</v>
       </c>
       <c r="G46">
-        <v>1.385436893203883</v>
+        <v>1.792801556420234</v>
       </c>
       <c r="H46">
-        <v>1.792801556420234</v>
+        <v>1.343719571567673</v>
       </c>
       <c r="I46">
-        <v>1.343719571567673</v>
+        <v>7.327922077922078</v>
       </c>
       <c r="J46">
-        <v>7.327922077922078</v>
+        <v>5.346356916578669</v>
       </c>
       <c r="K46">
-        <v>5.346356916578669</v>
+        <v>6.809766022380468</v>
       </c>
       <c r="L46">
-        <v>6.809766022380468</v>
+        <v>7.790322580645161</v>
       </c>
       <c r="M46">
-        <v>7.790322580645161</v>
+        <v>7.899897854954035</v>
       </c>
       <c r="N46">
-        <v>7.899897854954035</v>
+        <v>3.305194805194805</v>
       </c>
       <c r="O46">
-        <v>3.305194805194805</v>
+        <v>7.105858170606372</v>
       </c>
       <c r="P46">
-        <v>7.105858170606372</v>
+        <v>1.136319376825706</v>
       </c>
       <c r="Q46">
-        <v>1.136319376825706</v>
+        <v>1.472195121951219</v>
       </c>
       <c r="R46">
-        <v>1.472195121951219</v>
+        <v>1.650048875855328</v>
       </c>
       <c r="S46">
-        <v>1.650048875855328</v>
+        <v>1.190569744597249</v>
       </c>
       <c r="T46">
-        <v>1.190569744597249</v>
+        <v>5.724173553719008</v>
       </c>
       <c r="U46">
-        <v>5.724173553719008</v>
+        <v>1.792964824120603</v>
       </c>
       <c r="V46">
-        <v>1.792964824120603</v>
+        <v>4.270298047276465</v>
       </c>
       <c r="W46">
-        <v>4.270298047276465</v>
+        <v>0.425531914893617</v>
       </c>
       <c r="X46">
-        <v>0.425531914893617</v>
+        <v>57.8511673151751</v>
       </c>
       <c r="Y46">
-        <v>0.574468085106383</v>
+        <v>0.7730358874878759</v>
       </c>
       <c r="Z46">
-        <v>57.8511673151751</v>
+        <v>5.442495126705653</v>
       </c>
       <c r="AA46">
-        <v>0.7730358874878759</v>
-      </c>
-      <c r="AB46">
-        <v>0.2269641125121241</v>
-      </c>
-      <c r="AC46">
-        <v>5.442495126705653</v>
-      </c>
-      <c r="AD46">
         <v>5.692954784437434</v>
       </c>
     </row>
@@ -4781,84 +4367,75 @@
         <v>0.9221770091556459</v>
       </c>
       <c r="D47">
-        <v>0.07782299084435401</v>
+        <v>2.737789203084833</v>
       </c>
       <c r="E47">
-        <v>2.737789203084833</v>
+        <v>2.04251012145749</v>
       </c>
       <c r="F47">
-        <v>2.04251012145749</v>
+        <v>1.786707882534776</v>
       </c>
       <c r="G47">
-        <v>1.786707882534776</v>
+        <v>1.967808930425753</v>
       </c>
       <c r="H47">
-        <v>1.967808930425753</v>
+        <v>1.659090909090909</v>
       </c>
       <c r="I47">
-        <v>1.659090909090909</v>
+        <v>1.582417582417582</v>
       </c>
       <c r="J47">
-        <v>1.582417582417582</v>
+        <v>1.5539090444558</v>
       </c>
       <c r="K47">
-        <v>1.5539090444558</v>
+        <v>1.789727126805778</v>
       </c>
       <c r="L47">
-        <v>1.789727126805778</v>
+        <v>2.329781836631152</v>
       </c>
       <c r="M47">
-        <v>2.329781836631152</v>
+        <v>1.57324516785351</v>
       </c>
       <c r="N47">
-        <v>1.57324516785351</v>
+        <v>1.554545454545454</v>
       </c>
       <c r="O47">
-        <v>1.554545454545454</v>
+        <v>1.640776699029126</v>
       </c>
       <c r="P47">
-        <v>1.640776699029126</v>
+        <v>1.939425051334702</v>
       </c>
       <c r="Q47">
-        <v>1.939425051334702</v>
+        <v>3.341513292433538</v>
       </c>
       <c r="R47">
-        <v>3.341513292433538</v>
+        <v>1.72177009155646</v>
       </c>
       <c r="S47">
-        <v>1.72177009155646</v>
+        <v>1.652555498193082</v>
       </c>
       <c r="T47">
-        <v>1.652555498193082</v>
+        <v>1.665128205128205</v>
       </c>
       <c r="U47">
-        <v>1.665128205128205</v>
+        <v>1.559875583203733</v>
       </c>
       <c r="V47">
-        <v>1.559875583203733</v>
+        <v>3.701345755693582</v>
       </c>
       <c r="W47">
-        <v>3.701345755693582</v>
+        <v>0.5197994987468672</v>
       </c>
       <c r="X47">
-        <v>0.5197994987468672</v>
+        <v>35.64551863041289</v>
       </c>
       <c r="Y47">
-        <v>0.4802005012531328</v>
+        <v>0.9969924812030075</v>
       </c>
       <c r="Z47">
-        <v>35.64551863041289</v>
+        <v>3.16214859437751</v>
       </c>
       <c r="AA47">
-        <v>0.9969924812030075</v>
-      </c>
-      <c r="AB47">
-        <v>0.003007518796992481</v>
-      </c>
-      <c r="AC47">
-        <v>3.16214859437751</v>
-      </c>
-      <c r="AD47">
         <v>4.418703506907545</v>
       </c>
     </row>
@@ -4877,84 +4454,75 @@
         <v>0.661608497723824</v>
       </c>
       <c r="D48">
-        <v>0.338391502276176</v>
+        <v>3.489283074648928</v>
       </c>
       <c r="E48">
-        <v>3.489283074648928</v>
+        <v>2.772628530050688</v>
       </c>
       <c r="F48">
-        <v>2.772628530050688</v>
+        <v>1.558106169296987</v>
       </c>
       <c r="G48">
-        <v>1.558106169296987</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="H48">
-        <v>1.857142857142857</v>
+        <v>1.715010877447426</v>
       </c>
       <c r="I48">
-        <v>1.715010877447426</v>
+        <v>2.845864661654135</v>
       </c>
       <c r="J48">
-        <v>2.845864661654135</v>
+        <v>2.316983894582723</v>
       </c>
       <c r="K48">
-        <v>2.316983894582723</v>
+        <v>2.325072886297376</v>
       </c>
       <c r="L48">
-        <v>2.325072886297376</v>
+        <v>4.327761627906977</v>
       </c>
       <c r="M48">
-        <v>4.327761627906977</v>
+        <v>4.368070953436807</v>
       </c>
       <c r="N48">
-        <v>4.368070953436807</v>
+        <v>1.912472647702407</v>
       </c>
       <c r="O48">
-        <v>1.912472647702407</v>
+        <v>3.454198473282443</v>
       </c>
       <c r="P48">
-        <v>3.454198473282443</v>
+        <v>1.480286738351255</v>
       </c>
       <c r="Q48">
-        <v>1.480286738351255</v>
+        <v>1.90050107372942</v>
       </c>
       <c r="R48">
-        <v>1.90050107372942</v>
+        <v>1.608914450035945</v>
       </c>
       <c r="S48">
-        <v>1.608914450035945</v>
+        <v>1.638313609467456</v>
       </c>
       <c r="T48">
-        <v>1.638313609467456</v>
+        <v>2.687167805618831</v>
       </c>
       <c r="U48">
-        <v>2.687167805618831</v>
+        <v>1.729948491537896</v>
       </c>
       <c r="V48">
-        <v>1.729948491537896</v>
+        <v>3.955571740713765</v>
       </c>
       <c r="W48">
-        <v>3.955571740713765</v>
+        <v>0.5014285714285714</v>
       </c>
       <c r="X48">
-        <v>0.5014285714285714</v>
+        <v>40.15857142857143</v>
       </c>
       <c r="Y48">
-        <v>0.4985714285714286</v>
+        <v>0.9957142857142857</v>
       </c>
       <c r="Z48">
-        <v>40.15857142857143</v>
+        <v>4.309285714285714</v>
       </c>
       <c r="AA48">
-        <v>0.9957142857142857</v>
-      </c>
-      <c r="AB48">
-        <v>0.004285714285714286</v>
-      </c>
-      <c r="AC48">
-        <v>4.309285714285714</v>
-      </c>
-      <c r="AD48">
         <v>4.949385394070861</v>
       </c>
     </row>
@@ -4973,84 +4541,75 @@
         <v>0.6549707602339181</v>
       </c>
       <c r="D49">
-        <v>0.3450292397660819</v>
+        <v>5.284166666666667</v>
       </c>
       <c r="E49">
-        <v>5.284166666666667</v>
+        <v>4.811509591326105</v>
       </c>
       <c r="F49">
-        <v>4.811509591326105</v>
+        <v>3.640768588137009</v>
       </c>
       <c r="G49">
-        <v>3.640768588137009</v>
+        <v>4.079298831385643</v>
       </c>
       <c r="H49">
-        <v>4.079298831385643</v>
+        <v>4.216666666666667</v>
       </c>
       <c r="I49">
-        <v>4.216666666666667</v>
+        <v>4.57</v>
       </c>
       <c r="J49">
-        <v>4.57</v>
+        <v>3.773978315262719</v>
       </c>
       <c r="K49">
-        <v>3.773978315262719</v>
+        <v>3.018333333333334</v>
       </c>
       <c r="L49">
-        <v>3.018333333333334</v>
+        <v>4.205</v>
       </c>
       <c r="M49">
-        <v>4.205</v>
+        <v>4.314691151919867</v>
       </c>
       <c r="N49">
-        <v>4.314691151919867</v>
+        <v>3.125104253544621</v>
       </c>
       <c r="O49">
-        <v>3.125104253544621</v>
+        <v>3.625</v>
       </c>
       <c r="P49">
-        <v>3.625</v>
+        <v>3.437864887406172</v>
       </c>
       <c r="Q49">
-        <v>3.437864887406172</v>
+        <v>3.964166666666667</v>
       </c>
       <c r="R49">
-        <v>3.964166666666667</v>
+        <v>3.729166666666667</v>
       </c>
       <c r="S49">
-        <v>3.729166666666667</v>
+        <v>4.176814011676397</v>
       </c>
       <c r="T49">
-        <v>4.176814011676397</v>
+        <v>3.870617696160267</v>
       </c>
       <c r="U49">
-        <v>3.870617696160267</v>
+        <v>3.994166666666667</v>
       </c>
       <c r="V49">
-        <v>3.994166666666667</v>
+        <v>4.12510425354462</v>
       </c>
       <c r="W49">
-        <v>4.12510425354462</v>
+        <v>0.5</v>
       </c>
       <c r="X49">
-        <v>0.5</v>
+        <v>43.71416666666666</v>
       </c>
       <c r="Y49">
-        <v>0.5</v>
+        <v>0.9983333333333333</v>
       </c>
       <c r="Z49">
-        <v>43.71416666666666</v>
+        <v>3.340833333333333</v>
       </c>
       <c r="AA49">
-        <v>0.9983333333333333</v>
-      </c>
-      <c r="AB49">
-        <v>0.001666666666666667</v>
-      </c>
-      <c r="AC49">
-        <v>3.340833333333333</v>
-      </c>
-      <c r="AD49">
         <v>4.393333333333334</v>
       </c>
     </row>
@@ -5069,84 +4628,75 @@
         <v>0.6158701532912534</v>
       </c>
       <c r="D50">
-        <v>0.3841298467087466</v>
+        <v>2.465949820788531</v>
       </c>
       <c r="E50">
-        <v>2.465949820788531</v>
+        <v>2.129811996418979</v>
       </c>
       <c r="F50">
-        <v>2.129811996418979</v>
+        <v>1.360787824529991</v>
       </c>
       <c r="G50">
-        <v>1.360787824529991</v>
+        <v>1.519247985675918</v>
       </c>
       <c r="H50">
-        <v>1.519247985675918</v>
+        <v>1.372866127583109</v>
       </c>
       <c r="I50">
-        <v>1.372866127583109</v>
+        <v>5.578707916287534</v>
       </c>
       <c r="J50">
-        <v>5.578707916287534</v>
+        <v>3.079964061096137</v>
       </c>
       <c r="K50">
-        <v>3.079964061096137</v>
+        <v>2.805729632945389</v>
       </c>
       <c r="L50">
-        <v>2.805729632945389</v>
+        <v>6.06618962432916</v>
       </c>
       <c r="M50">
-        <v>6.06618962432916</v>
+        <v>5.12017937219731</v>
       </c>
       <c r="N50">
-        <v>5.12017937219731</v>
+        <v>1.804659498207885</v>
       </c>
       <c r="O50">
-        <v>1.804659498207885</v>
+        <v>3.339928057553957</v>
       </c>
       <c r="P50">
-        <v>3.339928057553957</v>
+        <v>1.258728737690242</v>
       </c>
       <c r="Q50">
-        <v>1.258728737690242</v>
+        <v>2.637992831541219</v>
       </c>
       <c r="R50">
-        <v>2.637992831541219</v>
+        <v>1.50762331838565</v>
       </c>
       <c r="S50">
-        <v>1.50762331838565</v>
+        <v>1.343525179856115</v>
       </c>
       <c r="T50">
-        <v>1.343525179856115</v>
+        <v>4.028776978417266</v>
       </c>
       <c r="U50">
-        <v>4.028776978417266</v>
+        <v>1.461883408071749</v>
       </c>
       <c r="V50">
-        <v>1.461883408071749</v>
+        <v>2.744394618834081</v>
       </c>
       <c r="W50">
-        <v>2.744394618834081</v>
+        <v>0.3928888888888889</v>
       </c>
       <c r="X50">
-        <v>0.3928888888888889</v>
+        <v>49.78222222222222</v>
       </c>
       <c r="Y50">
-        <v>0.6071111111111112</v>
+        <v>0.9381165919282511</v>
       </c>
       <c r="Z50">
-        <v>49.78222222222222</v>
+        <v>5.476486246672582</v>
       </c>
       <c r="AA50">
-        <v>0.9381165919282511</v>
-      </c>
-      <c r="AB50">
-        <v>0.06188340807174888</v>
-      </c>
-      <c r="AC50">
-        <v>5.476486246672582</v>
-      </c>
-      <c r="AD50">
         <v>5.135623869801085</v>
       </c>
     </row>
@@ -5165,84 +4715,75 @@
         <v>0.7462845010615711</v>
       </c>
       <c r="D51">
-        <v>0.2537154989384289</v>
+        <v>2.162675474814203</v>
       </c>
       <c r="E51">
-        <v>2.162675474814203</v>
+        <v>1.911382113821138</v>
       </c>
       <c r="F51">
-        <v>1.911382113821138</v>
+        <v>1.471636952998379</v>
       </c>
       <c r="G51">
-        <v>1.471636952998379</v>
+        <v>2.108218063466233</v>
       </c>
       <c r="H51">
-        <v>2.108218063466233</v>
+        <v>1.621533442088091</v>
       </c>
       <c r="I51">
-        <v>1.621533442088091</v>
+        <v>2.342442356959864</v>
       </c>
       <c r="J51">
-        <v>2.342442356959864</v>
+        <v>1.964046822742475</v>
       </c>
       <c r="K51">
-        <v>1.964046822742475</v>
+        <v>3.089225589225589</v>
       </c>
       <c r="L51">
-        <v>3.089225589225589</v>
+        <v>4.53628023352794</v>
       </c>
       <c r="M51">
-        <v>4.53628023352794</v>
+        <v>4.746153846153846</v>
       </c>
       <c r="N51">
-        <v>4.746153846153846</v>
+        <v>1.667493796526055</v>
       </c>
       <c r="O51">
-        <v>1.667493796526055</v>
+        <v>2.131979695431472</v>
       </c>
       <c r="P51">
-        <v>2.131979695431472</v>
+        <v>1.389789303079417</v>
       </c>
       <c r="Q51">
-        <v>1.389789303079417</v>
+        <v>1.765991902834008</v>
       </c>
       <c r="R51">
-        <v>1.765991902834008</v>
+        <v>1.386363636363636</v>
       </c>
       <c r="S51">
-        <v>1.386363636363636</v>
+        <v>1.323481116584565</v>
       </c>
       <c r="T51">
-        <v>1.323481116584565</v>
+        <v>2.631623212783852</v>
       </c>
       <c r="U51">
-        <v>2.631623212783852</v>
+        <v>1.512884455527847</v>
       </c>
       <c r="V51">
-        <v>1.512884455527847</v>
+        <v>2.355874894336433</v>
       </c>
       <c r="W51">
-        <v>2.355874894336433</v>
+        <v>0.3953858392999204</v>
       </c>
       <c r="X51">
-        <v>0.3953858392999204</v>
+        <v>48.05483870967742</v>
       </c>
       <c r="Y51">
-        <v>0.6046141607000796</v>
+        <v>0.9984089101034208</v>
       </c>
       <c r="Z51">
-        <v>48.05483870967742</v>
+        <v>4.204149377593361</v>
       </c>
       <c r="AA51">
-        <v>0.9984089101034208</v>
-      </c>
-      <c r="AB51">
-        <v>0.001591089896579157</v>
-      </c>
-      <c r="AC51">
-        <v>4.204149377593361</v>
-      </c>
-      <c r="AD51">
         <v>5.389221556886228</v>
       </c>
     </row>
@@ -5261,84 +4802,75 @@
         <v>0.4496330887258172</v>
       </c>
       <c r="D52">
-        <v>0.5503669112741828</v>
+        <v>3.890307603017992</v>
       </c>
       <c r="E52">
-        <v>3.890307603017992</v>
+        <v>4.896338028169014</v>
       </c>
       <c r="F52">
-        <v>4.896338028169014</v>
+        <v>2.272574312955693</v>
       </c>
       <c r="G52">
-        <v>2.272574312955693</v>
+        <v>3.64121699196326</v>
       </c>
       <c r="H52">
-        <v>3.64121699196326</v>
+        <v>2.425652667423383</v>
       </c>
       <c r="I52">
-        <v>2.425652667423383</v>
+        <v>2.604513064133017</v>
       </c>
       <c r="J52">
-        <v>2.604513064133017</v>
+        <v>2.952769679300292</v>
       </c>
       <c r="K52">
-        <v>2.952769679300292</v>
+        <v>4.576855639976622</v>
       </c>
       <c r="L52">
-        <v>4.576855639976622</v>
+        <v>6.095921883974727</v>
       </c>
       <c r="M52">
-        <v>6.095921883974727</v>
+        <v>6.062969381860197</v>
       </c>
       <c r="N52">
-        <v>6.062969381860197</v>
+        <v>2.708432304038005</v>
       </c>
       <c r="O52">
-        <v>2.708432304038005</v>
+        <v>4.658566221142163</v>
       </c>
       <c r="P52">
-        <v>4.658566221142163</v>
+        <v>2.133600917431193</v>
       </c>
       <c r="Q52">
-        <v>2.133600917431193</v>
+        <v>2.336358479863868</v>
       </c>
       <c r="R52">
-        <v>2.336358479863868</v>
+        <v>2.077141236528644</v>
       </c>
       <c r="S52">
-        <v>2.077141236528644</v>
+        <v>1.886621315192744</v>
       </c>
       <c r="T52">
-        <v>1.886621315192744</v>
+        <v>4.20986920332937</v>
       </c>
       <c r="U52">
-        <v>4.20986920332937</v>
+        <v>2.416374269005848</v>
       </c>
       <c r="V52">
-        <v>2.416374269005848</v>
+        <v>4.562613430127041</v>
       </c>
       <c r="W52">
-        <v>4.562613430127041</v>
+        <v>0.4121546961325967</v>
       </c>
       <c r="X52">
-        <v>0.4121546961325967</v>
+        <v>45.40662983425414</v>
       </c>
       <c r="Y52">
-        <v>0.5878453038674033</v>
+        <v>0.9618573797678275</v>
       </c>
       <c r="Z52">
-        <v>45.40662983425414</v>
+        <v>5.873333333333333</v>
       </c>
       <c r="AA52">
-        <v>0.9618573797678275</v>
-      </c>
-      <c r="AB52">
-        <v>0.03814262023217247</v>
-      </c>
-      <c r="AC52">
-        <v>5.873333333333333</v>
-      </c>
-      <c r="AD52">
         <v>4.773325701202061</v>
       </c>
     </row>
@@ -5357,84 +4889,75 @@
         <v>0.7000518941359626</v>
       </c>
       <c r="D53">
-        <v>0.2999481058640374</v>
+        <v>2.542</v>
       </c>
       <c r="E53">
-        <v>2.542</v>
+        <v>1.819909954977489</v>
       </c>
       <c r="F53">
-        <v>1.819909954977489</v>
+        <v>1.350175087543772</v>
       </c>
       <c r="G53">
-        <v>1.350175087543772</v>
+        <v>1.532532532532533</v>
       </c>
       <c r="H53">
-        <v>1.532532532532533</v>
+        <v>1.408908908908909</v>
       </c>
       <c r="I53">
-        <v>1.408908908908909</v>
+        <v>3.447686116700201</v>
       </c>
       <c r="J53">
-        <v>3.447686116700201</v>
+        <v>2.776494224008036</v>
       </c>
       <c r="K53">
-        <v>2.776494224008036</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="L53">
-        <v>3.285714285714286</v>
+        <v>4.205025125628141</v>
       </c>
       <c r="M53">
-        <v>4.205025125628141</v>
+        <v>4.035732259687972</v>
       </c>
       <c r="N53">
-        <v>4.035732259687972</v>
+        <v>2.462079357106981</v>
       </c>
       <c r="O53">
-        <v>2.462079357106981</v>
+        <v>4.188928390045708</v>
       </c>
       <c r="P53">
-        <v>4.188928390045708</v>
+        <v>1.321178821178821</v>
       </c>
       <c r="Q53">
-        <v>1.321178821178821</v>
+        <v>3.361</v>
       </c>
       <c r="R53">
-        <v>3.361</v>
+        <v>1.584123814278582</v>
       </c>
       <c r="S53">
-        <v>1.584123814278582</v>
+        <v>1.304347826086957</v>
       </c>
       <c r="T53">
-        <v>1.304347826086957</v>
+        <v>2.867203219315895</v>
       </c>
       <c r="U53">
-        <v>2.867203219315895</v>
+        <v>1.550275137568784</v>
       </c>
       <c r="V53">
-        <v>1.550275137568784</v>
+        <v>4.779175050301811</v>
       </c>
       <c r="W53">
-        <v>4.779175050301811</v>
+        <v>0.4592445328031809</v>
       </c>
       <c r="X53">
-        <v>0.4592445328031809</v>
+        <v>47.78330019880715</v>
       </c>
       <c r="Y53">
-        <v>0.5407554671968191</v>
+        <v>0.8026838966202783</v>
       </c>
       <c r="Z53">
-        <v>47.78330019880715</v>
+        <v>5.218127490039841</v>
       </c>
       <c r="AA53">
-        <v>0.8026838966202783</v>
-      </c>
-      <c r="AB53">
-        <v>0.1973161033797217</v>
-      </c>
-      <c r="AC53">
-        <v>5.218127490039841</v>
-      </c>
-      <c r="AD53">
         <v>4.979038854805726</v>
       </c>
     </row>
@@ -5453,84 +4976,75 @@
         <v>0.3133047210300429</v>
       </c>
       <c r="D54">
-        <v>0.6866952789699571</v>
+        <v>3.895325203252033</v>
       </c>
       <c r="E54">
-        <v>3.895325203252033</v>
+        <v>3.939024390243902</v>
       </c>
       <c r="F54">
-        <v>3.939024390243902</v>
+        <v>3.081</v>
       </c>
       <c r="G54">
-        <v>3.081</v>
+        <v>3.440320962888666</v>
       </c>
       <c r="H54">
-        <v>3.440320962888666</v>
+        <v>3.176113360323887</v>
       </c>
       <c r="I54">
-        <v>3.176113360323887</v>
+        <v>3.855544252288912</v>
       </c>
       <c r="J54">
-        <v>3.855544252288912</v>
+        <v>3.671779141104294</v>
       </c>
       <c r="K54">
-        <v>3.671779141104294</v>
+        <v>4.469262295081967</v>
       </c>
       <c r="L54">
-        <v>4.469262295081967</v>
+        <v>5.527439024390244</v>
       </c>
       <c r="M54">
-        <v>5.527439024390244</v>
+        <v>5.891752577319588</v>
       </c>
       <c r="N54">
-        <v>5.891752577319588</v>
+        <v>3.269113149847095</v>
       </c>
       <c r="O54">
-        <v>3.269113149847095</v>
+        <v>3.804979253112033</v>
       </c>
       <c r="P54">
-        <v>3.804979253112033</v>
+        <v>3.114228456913827</v>
       </c>
       <c r="Q54">
-        <v>3.114228456913827</v>
+        <v>3.539235412474849</v>
       </c>
       <c r="R54">
-        <v>3.539235412474849</v>
+        <v>3.049098196392785</v>
       </c>
       <c r="S54">
-        <v>3.049098196392785</v>
+        <v>3.038076152304609</v>
       </c>
       <c r="T54">
-        <v>3.038076152304609</v>
+        <v>5.141675284384695</v>
       </c>
       <c r="U54">
-        <v>5.141675284384695</v>
+        <v>3.085714285714286</v>
       </c>
       <c r="V54">
-        <v>3.085714285714286</v>
+        <v>4.739572736520855</v>
       </c>
       <c r="W54">
-        <v>4.739572736520855</v>
+        <v>0.4780114722753346</v>
       </c>
       <c r="X54">
-        <v>0.4780114722753346</v>
+        <v>46.13710450623202</v>
       </c>
       <c r="Y54">
-        <v>0.5219885277246654</v>
+        <v>0.9164265129682997</v>
       </c>
       <c r="Z54">
-        <v>46.13710450623202</v>
+        <v>6.134634146341464</v>
       </c>
       <c r="AA54">
-        <v>0.9164265129682997</v>
-      </c>
-      <c r="AB54">
-        <v>0.08357348703170028</v>
-      </c>
-      <c r="AC54">
-        <v>6.134634146341464</v>
-      </c>
-      <c r="AD54">
         <v>4.786004056795131</v>
       </c>
     </row>
@@ -5549,84 +5063,75 @@
         <v>0.4608778625954199</v>
       </c>
       <c r="D55">
-        <v>0.5391221374045801</v>
+        <v>3.664690939881456</v>
       </c>
       <c r="E55">
-        <v>3.664690939881456</v>
+        <v>3.58972198820556</v>
       </c>
       <c r="F55">
-        <v>3.58972198820556</v>
+        <v>2.353484466834593</v>
       </c>
       <c r="G55">
-        <v>2.353484466834593</v>
+        <v>2.609612141652614</v>
       </c>
       <c r="H55">
-        <v>2.609612141652614</v>
+        <v>2.874894336432798</v>
       </c>
       <c r="I55">
-        <v>2.874894336432798</v>
+        <v>4.909498207885305</v>
       </c>
       <c r="J55">
-        <v>4.909498207885305</v>
+        <v>3.662020905923345</v>
       </c>
       <c r="K55">
-        <v>3.662020905923345</v>
+        <v>4.824500434404865</v>
       </c>
       <c r="L55">
-        <v>4.824500434404865</v>
+        <v>6.241525423728813</v>
       </c>
       <c r="M55">
-        <v>6.241525423728813</v>
+        <v>6.75968992248062</v>
       </c>
       <c r="N55">
-        <v>6.75968992248062</v>
+        <v>3.132340052585451</v>
       </c>
       <c r="O55">
-        <v>3.132340052585451</v>
+        <v>3.59265890778872</v>
       </c>
       <c r="P55">
-        <v>3.59265890778872</v>
+        <v>1.986463620981388</v>
       </c>
       <c r="Q55">
-        <v>1.986463620981388</v>
+        <v>2.653198653198653</v>
       </c>
       <c r="R55">
-        <v>2.653198653198653</v>
+        <v>2.010906040268456</v>
       </c>
       <c r="S55">
-        <v>2.010906040268456</v>
+        <v>1.946655376799323</v>
       </c>
       <c r="T55">
-        <v>1.946655376799323</v>
+        <v>5.140474100087796</v>
       </c>
       <c r="U55">
-        <v>5.140474100087796</v>
+        <v>2.228813559322034</v>
       </c>
       <c r="V55">
-        <v>2.228813559322034</v>
+        <v>3.170925110132158</v>
       </c>
       <c r="W55">
-        <v>3.170925110132158</v>
+        <v>0.46</v>
       </c>
       <c r="X55">
-        <v>0.46</v>
+        <v>52.65583333333333</v>
       </c>
       <c r="Y55">
-        <v>0.54</v>
+        <v>0.9925</v>
       </c>
       <c r="Z55">
-        <v>52.65583333333333</v>
+        <v>4.324166666666667</v>
       </c>
       <c r="AA55">
-        <v>0.9925</v>
-      </c>
-      <c r="AB55">
-        <v>0.0075</v>
-      </c>
-      <c r="AC55">
-        <v>4.324166666666667</v>
-      </c>
-      <c r="AD55">
         <v>5.183290707587383</v>
       </c>
     </row>
@@ -5645,84 +5150,75 @@
         <v>0.7792823290453622</v>
       </c>
       <c r="D56">
-        <v>0.2207176709546378</v>
+        <v>2.216362407031778</v>
       </c>
       <c r="E56">
-        <v>2.216362407031778</v>
+        <v>2.216307277628032</v>
       </c>
       <c r="F56">
-        <v>2.216307277628032</v>
+        <v>1.833109017496635</v>
       </c>
       <c r="G56">
-        <v>1.833109017496635</v>
+        <v>1.748317631224765</v>
       </c>
       <c r="H56">
-        <v>1.748317631224765</v>
+        <v>1.767160161507402</v>
       </c>
       <c r="I56">
-        <v>1.767160161507402</v>
+        <v>4.208080808080808</v>
       </c>
       <c r="J56">
-        <v>4.208080808080808</v>
+        <v>2.4949358541526</v>
       </c>
       <c r="K56">
-        <v>2.4949358541526</v>
+        <v>2.394878706199461</v>
       </c>
       <c r="L56">
-        <v>2.394878706199461</v>
+        <v>4.584511784511784</v>
       </c>
       <c r="M56">
-        <v>4.584511784511784</v>
+        <v>4.478378378378379</v>
       </c>
       <c r="N56">
-        <v>4.478378378378379</v>
+        <v>2.488888888888889</v>
       </c>
       <c r="O56">
-        <v>2.488888888888889</v>
+        <v>2.757596218771101</v>
       </c>
       <c r="P56">
-        <v>2.757596218771101</v>
+        <v>1.997983870967742</v>
       </c>
       <c r="Q56">
-        <v>1.997983870967742</v>
+        <v>2.319435104236718</v>
       </c>
       <c r="R56">
-        <v>2.319435104236718</v>
+        <v>1.895763281775387</v>
       </c>
       <c r="S56">
-        <v>1.895763281775387</v>
+        <v>1.85464333781965</v>
       </c>
       <c r="T56">
-        <v>1.85464333781965</v>
+        <v>2.464959568733154</v>
       </c>
       <c r="U56">
-        <v>2.464959568733154</v>
+        <v>2.289172831203766</v>
       </c>
       <c r="V56">
-        <v>2.289172831203766</v>
+        <v>4.5</v>
       </c>
       <c r="W56">
-        <v>4.5</v>
+        <v>0.4681421864520456</v>
       </c>
       <c r="X56">
-        <v>0.4681421864520456</v>
+        <v>46.21814543028686</v>
       </c>
       <c r="Y56">
-        <v>0.5318578135479544</v>
+        <v>1</v>
       </c>
       <c r="Z56">
-        <v>46.21814543028686</v>
+        <v>3.159783344617468</v>
       </c>
       <c r="AA56">
-        <v>1</v>
-      </c>
-      <c r="AB56">
-        <v>0</v>
-      </c>
-      <c r="AC56">
-        <v>3.159783344617468</v>
-      </c>
-      <c r="AD56">
         <v>4.735823882588392</v>
       </c>
     </row>
@@ -5741,81 +5237,72 @@
         <v>0.7933333333333333</v>
       </c>
       <c r="D57">
-        <v>0.2066666666666667</v>
+        <v>3.098333333333333</v>
       </c>
       <c r="E57">
-        <v>3.098333333333333</v>
+        <v>2.599166666666667</v>
       </c>
       <c r="F57">
-        <v>2.599166666666667</v>
+        <v>2.190833333333333</v>
       </c>
       <c r="G57">
-        <v>2.190833333333333</v>
+        <v>2.4225</v>
       </c>
       <c r="H57">
-        <v>2.4225</v>
-      </c>
-      <c r="I57">
         <v>2.255833333333333</v>
       </c>
+      <c r="J57">
+        <v>2.106666666666666</v>
+      </c>
       <c r="K57">
-        <v>2.106666666666666</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="L57">
-        <v>2.333333333333333</v>
+        <v>2.365833333333333</v>
       </c>
       <c r="M57">
-        <v>2.365833333333333</v>
+        <v>2.130833333333333</v>
       </c>
       <c r="N57">
-        <v>2.130833333333333</v>
+        <v>2.0825</v>
       </c>
       <c r="O57">
-        <v>2.0825</v>
+        <v>2.353333333333333</v>
       </c>
       <c r="P57">
-        <v>2.353333333333333</v>
+        <v>2.296666666666667</v>
       </c>
       <c r="Q57">
-        <v>2.296666666666667</v>
+        <v>2.29</v>
       </c>
       <c r="R57">
-        <v>2.29</v>
+        <v>2.249166666666667</v>
       </c>
       <c r="S57">
-        <v>2.249166666666667</v>
+        <v>2.228333333333333</v>
       </c>
       <c r="T57">
-        <v>2.228333333333333</v>
+        <v>2.163333333333334</v>
       </c>
       <c r="U57">
-        <v>2.163333333333334</v>
+        <v>2.215</v>
       </c>
       <c r="V57">
-        <v>2.215</v>
+        <v>2.463333333333333</v>
       </c>
       <c r="W57">
-        <v>2.463333333333333</v>
+        <v>0.495</v>
       </c>
       <c r="X57">
-        <v>0.495</v>
+        <v>41.065</v>
       </c>
       <c r="Y57">
-        <v>0.505</v>
+        <v>0.995</v>
       </c>
       <c r="Z57">
-        <v>41.065</v>
+        <v>5.252312867956266</v>
       </c>
       <c r="AA57">
-        <v>0.995</v>
-      </c>
-      <c r="AB57">
-        <v>0.005</v>
-      </c>
-      <c r="AC57">
-        <v>5.252312867956266</v>
-      </c>
-      <c r="AD57">
         <v>5.644166666666667</v>
       </c>
     </row>
@@ -5834,84 +5321,75 @@
         <v>0.9842061512884456</v>
       </c>
       <c r="D58">
-        <v>0.01579384871155445</v>
+        <v>2.763135946622185</v>
       </c>
       <c r="E58">
-        <v>2.763135946622185</v>
+        <v>2.120532003325021</v>
       </c>
       <c r="F58">
-        <v>2.120532003325021</v>
+        <v>1.530340814630091</v>
       </c>
       <c r="G58">
-        <v>1.530340814630091</v>
+        <v>1.920965058236273</v>
       </c>
       <c r="H58">
-        <v>1.920965058236273</v>
+        <v>1.738154613466334</v>
       </c>
       <c r="I58">
-        <v>1.738154613466334</v>
+        <v>1.412010008340284</v>
       </c>
       <c r="J58">
-        <v>1.412010008340284</v>
+        <v>1.671654197838736</v>
       </c>
       <c r="K58">
-        <v>1.671654197838736</v>
+        <v>2.667776852622814</v>
       </c>
       <c r="L58">
-        <v>2.667776852622814</v>
+        <v>4.140365448504983</v>
       </c>
       <c r="M58">
-        <v>4.140365448504983</v>
+        <v>1.537052456286428</v>
       </c>
       <c r="N58">
-        <v>1.537052456286428</v>
+        <v>1.435215946843854</v>
       </c>
       <c r="O58">
-        <v>1.435215946843854</v>
+        <v>1.848459616985845</v>
       </c>
       <c r="P58">
-        <v>1.848459616985845</v>
+        <v>1.936046511627907</v>
       </c>
       <c r="Q58">
-        <v>1.936046511627907</v>
+        <v>3.004983388704319</v>
       </c>
       <c r="R58">
-        <v>3.004983388704319</v>
+        <v>1.487136929460581</v>
       </c>
       <c r="S58">
-        <v>1.487136929460581</v>
+        <v>1.348585690515807</v>
       </c>
       <c r="T58">
-        <v>1.348585690515807</v>
+        <v>1.369908561928512</v>
       </c>
       <c r="U58">
-        <v>1.369908561928512</v>
+        <v>1.349708576186511</v>
       </c>
       <c r="V58">
-        <v>1.349708576186511</v>
+        <v>3.355241264559068</v>
       </c>
       <c r="W58">
-        <v>3.355241264559068</v>
+        <v>0.4626865671641791</v>
       </c>
       <c r="X58">
-        <v>0.4626865671641791</v>
+        <v>43.16348547717843</v>
       </c>
       <c r="Y58">
-        <v>0.5373134328358209</v>
+        <v>0.9883817427385893</v>
       </c>
       <c r="Z58">
-        <v>43.16348547717843</v>
+        <v>3.555369127516779</v>
       </c>
       <c r="AA58">
-        <v>0.9883817427385893</v>
-      </c>
-      <c r="AB58">
-        <v>0.01161825726141079</v>
-      </c>
-      <c r="AC58">
-        <v>3.555369127516779</v>
-      </c>
-      <c r="AD58">
         <v>4.706766917293233</v>
       </c>
     </row>
@@ -5930,78 +5408,69 @@
         <v>0.919714165615805</v>
       </c>
       <c r="D59">
-        <v>0.08028583438419504</v>
+        <v>1.89194826866917</v>
       </c>
       <c r="E59">
-        <v>1.89194826866917</v>
+        <v>2.096733668341709</v>
       </c>
       <c r="F59">
-        <v>2.096733668341709</v>
+        <v>1.610648918469218</v>
       </c>
       <c r="G59">
-        <v>1.610648918469218</v>
+        <v>1.686847599164927</v>
       </c>
       <c r="H59">
-        <v>1.686847599164927</v>
+        <v>1.650667779632721</v>
       </c>
       <c r="I59">
-        <v>1.650667779632721</v>
+        <v>2.077020736352095</v>
       </c>
       <c r="J59">
-        <v>2.077020736352095</v>
+        <v>1.853002939941201</v>
       </c>
       <c r="K59">
-        <v>1.853002939941201</v>
+        <v>2.572696534234996</v>
       </c>
       <c r="L59">
-        <v>2.572696534234996</v>
+        <v>4.402206194314807</v>
       </c>
       <c r="M59">
-        <v>4.402206194314807</v>
+        <v>2.349576271186441</v>
       </c>
       <c r="N59">
-        <v>2.349576271186441</v>
+        <v>1.800501882057716</v>
       </c>
       <c r="O59">
-        <v>1.800501882057716</v>
+        <v>2.530322580645161</v>
       </c>
       <c r="P59">
-        <v>2.530322580645161</v>
+        <v>1.803831736776343</v>
       </c>
       <c r="Q59">
-        <v>1.803831736776343</v>
+        <v>2.093333333333333</v>
       </c>
       <c r="R59">
-        <v>2.093333333333333</v>
-      </c>
-      <c r="S59">
         <v>1.954962468723937</v>
       </c>
-      <c r="U59">
+      <c r="T59">
         <v>2.346137610806247</v>
       </c>
+      <c r="V59">
+        <v>3.293967714528462</v>
+      </c>
       <c r="W59">
-        <v>3.293967714528462</v>
+        <v>0.4997929606625259</v>
       </c>
       <c r="X59">
-        <v>0.4997929606625259</v>
+        <v>38.83181441590721</v>
       </c>
       <c r="Y59">
-        <v>0.5002070393374741</v>
+        <v>0.9966873706004141</v>
       </c>
       <c r="Z59">
-        <v>38.83181441590721</v>
+        <v>3.333748960931006</v>
       </c>
       <c r="AA59">
-        <v>0.9966873706004141</v>
-      </c>
-      <c r="AB59">
-        <v>0.003312629399585921</v>
-      </c>
-      <c r="AC59">
-        <v>3.333748960931006</v>
-      </c>
-      <c r="AD59">
         <v>5.34349506225848</v>
       </c>
     </row>
@@ -6020,84 +5489,75 @@
         <v>0.6153846153846154</v>
       </c>
       <c r="D60">
-        <v>0.3846153846153846</v>
+        <v>3.001635322976288</v>
       </c>
       <c r="E60">
-        <v>3.001635322976288</v>
+        <v>2.239574816026165</v>
       </c>
       <c r="F60">
-        <v>2.239574816026165</v>
+        <v>1.423548650858545</v>
       </c>
       <c r="G60">
-        <v>1.423548650858545</v>
+        <v>1.748160261651676</v>
       </c>
       <c r="H60">
-        <v>1.748160261651676</v>
+        <v>1.573998364677024</v>
       </c>
       <c r="I60">
-        <v>1.573998364677024</v>
+        <v>4.351594439901881</v>
       </c>
       <c r="J60">
-        <v>4.351594439901881</v>
+        <v>3.159443990188062</v>
       </c>
       <c r="K60">
-        <v>3.159443990188062</v>
+        <v>3.395748160261652</v>
       </c>
       <c r="L60">
-        <v>3.395748160261652</v>
+        <v>5.014717906786591</v>
       </c>
       <c r="M60">
-        <v>5.014717906786591</v>
+        <v>5.174161896974653</v>
       </c>
       <c r="N60">
-        <v>5.174161896974653</v>
+        <v>2.807849550286182</v>
       </c>
       <c r="O60">
-        <v>2.807849550286182</v>
+        <v>6.090760425183974</v>
       </c>
       <c r="P60">
-        <v>6.090760425183974</v>
+        <v>1.589533932951758</v>
       </c>
       <c r="Q60">
-        <v>1.589533932951758</v>
+        <v>4.247751430907604</v>
       </c>
       <c r="R60">
-        <v>4.247751430907604</v>
+        <v>1.626328699918234</v>
       </c>
       <c r="S60">
-        <v>1.626328699918234</v>
+        <v>1.364677023712183</v>
       </c>
       <c r="T60">
-        <v>1.364677023712183</v>
+        <v>3.335241210139003</v>
       </c>
       <c r="U60">
-        <v>3.335241210139003</v>
+        <v>1.654946852003271</v>
       </c>
       <c r="V60">
-        <v>1.654946852003271</v>
+        <v>6.963175122749591</v>
       </c>
       <c r="W60">
-        <v>6.963175122749591</v>
+        <v>0.4856909239574816</v>
       </c>
       <c r="X60">
-        <v>0.4856909239574816</v>
+        <v>48.28887070376432</v>
       </c>
       <c r="Y60">
-        <v>0.5143090760425184</v>
+        <v>0.9697465249386754</v>
       </c>
       <c r="Z60">
-        <v>48.28887070376432</v>
+        <v>5.165302782324058</v>
       </c>
       <c r="AA60">
-        <v>0.9697465249386754</v>
-      </c>
-      <c r="AB60">
-        <v>0.03025347506132461</v>
-      </c>
-      <c r="AC60">
-        <v>5.165302782324058</v>
-      </c>
-      <c r="AD60">
         <v>4.502861815208504</v>
       </c>
     </row>
@@ -6116,84 +5576,75 @@
         <v>0.5512953367875648</v>
       </c>
       <c r="D61">
-        <v>0.4487046632124352</v>
+        <v>3.402308326463314</v>
       </c>
       <c r="E61">
-        <v>3.402308326463314</v>
+        <v>3.614891913530825</v>
       </c>
       <c r="F61">
-        <v>3.614891913530825</v>
+        <v>1.955520254169976</v>
       </c>
       <c r="G61">
-        <v>1.955520254169976</v>
+        <v>3.088356729975227</v>
       </c>
       <c r="H61">
-        <v>3.088356729975227</v>
+        <v>2.465964343598055</v>
       </c>
       <c r="I61">
-        <v>2.465964343598055</v>
+        <v>2.732245681381958</v>
       </c>
       <c r="J61">
-        <v>2.732245681381958</v>
+        <v>2.945584299732382</v>
       </c>
       <c r="K61">
-        <v>2.945584299732382</v>
+        <v>4.055702917771884</v>
       </c>
       <c r="L61">
-        <v>4.055702917771884</v>
+        <v>5.682023486901536</v>
       </c>
       <c r="M61">
-        <v>5.682023486901536</v>
+        <v>5.945420906567993</v>
       </c>
       <c r="N61">
-        <v>5.945420906567993</v>
+        <v>2.237931034482759</v>
       </c>
       <c r="O61">
-        <v>2.237931034482759</v>
+        <v>4.683778234086242</v>
       </c>
       <c r="P61">
-        <v>4.683778234086242</v>
+        <v>1.991967871485944</v>
       </c>
       <c r="Q61">
-        <v>1.991967871485944</v>
+        <v>2.448136142625608</v>
       </c>
       <c r="R61">
-        <v>2.448136142625608</v>
+        <v>2.097991967871486</v>
       </c>
       <c r="S61">
-        <v>2.097991967871486</v>
+        <v>1.821630347054076</v>
       </c>
       <c r="T61">
-        <v>1.821630347054076</v>
+        <v>3.801675977653631</v>
       </c>
       <c r="U61">
-        <v>3.801675977653631</v>
+        <v>2.165400843881856</v>
       </c>
       <c r="V61">
-        <v>2.165400843881856</v>
+        <v>4.460727969348659</v>
       </c>
       <c r="W61">
-        <v>4.460727969348659</v>
+        <v>0.4065166795965865</v>
       </c>
       <c r="X61">
-        <v>0.4065166795965865</v>
+        <v>47.57253685027153</v>
       </c>
       <c r="Y61">
-        <v>0.5934833204034135</v>
+        <v>0.9572317262830482</v>
       </c>
       <c r="Z61">
-        <v>47.57253685027153</v>
+        <v>5.897496087636933</v>
       </c>
       <c r="AA61">
-        <v>0.9572317262830482</v>
-      </c>
-      <c r="AB61">
-        <v>0.04276827371695179</v>
-      </c>
-      <c r="AC61">
-        <v>5.897496087636933</v>
-      </c>
-      <c r="AD61">
         <v>4.480971659919028</v>
       </c>
     </row>
@@ -6212,84 +5663,75 @@
         <v>0.2805005213764338</v>
       </c>
       <c r="D62">
-        <v>0.7194994786235662</v>
+        <v>2.638232271325796</v>
       </c>
       <c r="E62">
-        <v>2.638232271325796</v>
+        <v>2.509297520661157</v>
       </c>
       <c r="F62">
-        <v>2.509297520661157</v>
+        <v>1.770475227502528</v>
       </c>
       <c r="G62">
-        <v>1.770475227502528</v>
+        <v>2.03763987792472</v>
       </c>
       <c r="H62">
-        <v>2.03763987792472</v>
+        <v>1.594262295081967</v>
       </c>
       <c r="I62">
-        <v>1.594262295081967</v>
+        <v>6.831154684095861</v>
       </c>
       <c r="J62">
-        <v>6.831154684095861</v>
+        <v>4.452554744525547</v>
       </c>
       <c r="K62">
-        <v>4.452554744525547</v>
+        <v>4.81139896373057</v>
       </c>
       <c r="L62">
-        <v>4.81139896373057</v>
+        <v>7.312108559498956</v>
       </c>
       <c r="M62">
-        <v>7.312108559498956</v>
+        <v>7.201047120418848</v>
       </c>
       <c r="N62">
-        <v>7.201047120418848</v>
+        <v>3.180873180873181</v>
       </c>
       <c r="O62">
-        <v>3.180873180873181</v>
+        <v>5.467941507311586</v>
       </c>
       <c r="P62">
-        <v>5.467941507311586</v>
+        <v>1.393969849246231</v>
       </c>
       <c r="Q62">
-        <v>1.393969849246231</v>
+        <v>2.284561049445005</v>
       </c>
       <c r="R62">
-        <v>2.284561049445005</v>
+        <v>1.783838383838384</v>
       </c>
       <c r="S62">
-        <v>1.783838383838384</v>
+        <v>1.623601220752798</v>
       </c>
       <c r="T62">
-        <v>1.623601220752798</v>
+        <v>5.239704329461457</v>
       </c>
       <c r="U62">
-        <v>5.239704329461457</v>
+        <v>1.927477017364658</v>
       </c>
       <c r="V62">
-        <v>1.927477017364658</v>
+        <v>3.749488752556237</v>
       </c>
       <c r="W62">
-        <v>3.749488752556237</v>
+        <v>0.316</v>
       </c>
       <c r="X62">
-        <v>0.316</v>
+        <v>49.83</v>
       </c>
       <c r="Y62">
-        <v>0.6840000000000001</v>
+        <v>0.970970970970971</v>
       </c>
       <c r="Z62">
-        <v>49.83</v>
+        <v>4.342685370741483</v>
       </c>
       <c r="AA62">
-        <v>0.970970970970971</v>
-      </c>
-      <c r="AB62">
-        <v>0.02902902902902903</v>
-      </c>
-      <c r="AC62">
-        <v>4.342685370741483</v>
-      </c>
-      <c r="AD62">
         <v>5.007201646090535</v>
       </c>
     </row>
@@ -6308,84 +5750,75 @@
         <v>0.6603250099088387</v>
       </c>
       <c r="D63">
-        <v>0.3396749900911613</v>
+        <v>2.530763239875389</v>
       </c>
       <c r="E63">
-        <v>2.530763239875389</v>
+        <v>2.932632398753894</v>
       </c>
       <c r="F63">
-        <v>2.932632398753894</v>
+        <v>1.892133956386293</v>
       </c>
       <c r="G63">
-        <v>1.892133956386293</v>
+        <v>2.110031104199067</v>
       </c>
       <c r="H63">
-        <v>2.110031104199067</v>
+        <v>1.771206225680934</v>
       </c>
       <c r="I63">
-        <v>1.771206225680934</v>
+        <v>6.496865203761756</v>
       </c>
       <c r="J63">
-        <v>6.496865203761756</v>
+        <v>3.835216205687573</v>
       </c>
       <c r="K63">
-        <v>3.835216205687573</v>
+        <v>5.067004285157772</v>
       </c>
       <c r="L63">
-        <v>5.067004285157772</v>
+        <v>6.597432905484247</v>
       </c>
       <c r="M63">
-        <v>6.597432905484247</v>
+        <v>6.715009746588694</v>
       </c>
       <c r="N63">
-        <v>6.715009746588694</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="O63">
-        <v>3.333333333333333</v>
+        <v>5.384315255559891</v>
       </c>
       <c r="P63">
-        <v>5.384315255559891</v>
+        <v>1.414396887159533</v>
       </c>
       <c r="Q63">
-        <v>1.414396887159533</v>
+        <v>1.991054064566317</v>
       </c>
       <c r="R63">
-        <v>1.991054064566317</v>
+        <v>2.406152647975078</v>
       </c>
       <c r="S63">
-        <v>2.406152647975078</v>
+        <v>1.556420233463035</v>
       </c>
       <c r="T63">
-        <v>1.556420233463035</v>
+        <v>5.77561355668095</v>
       </c>
       <c r="U63">
-        <v>5.77561355668095</v>
+        <v>2.221269964939618</v>
       </c>
       <c r="V63">
-        <v>2.221269964939618</v>
+        <v>5.511301636788776</v>
       </c>
       <c r="W63">
-        <v>5.511301636788776</v>
+        <v>0.5354391371340523</v>
       </c>
       <c r="X63">
-        <v>0.5354391371340523</v>
+        <v>43.42218798151001</v>
       </c>
       <c r="Y63">
-        <v>0.4645608628659476</v>
+        <v>0.8943217665615142</v>
       </c>
       <c r="Z63">
-        <v>43.42218798151001</v>
+        <v>5.882123341139734</v>
       </c>
       <c r="AA63">
-        <v>0.8943217665615142</v>
-      </c>
-      <c r="AB63">
-        <v>0.1056782334384858</v>
-      </c>
-      <c r="AC63">
-        <v>5.882123341139734</v>
-      </c>
-      <c r="AD63">
         <v>5.051221434200158</v>
       </c>
     </row>
@@ -6404,81 +5837,72 @@
         <v>0.900523560209424</v>
       </c>
       <c r="D64">
-        <v>0.09947643979057591</v>
+        <v>3.133671742808799</v>
       </c>
       <c r="E64">
-        <v>3.133671742808799</v>
+        <v>5.57189811010682</v>
       </c>
       <c r="F64">
-        <v>5.57189811010682</v>
+        <v>1.992628992628993</v>
       </c>
       <c r="G64">
-        <v>1.992628992628993</v>
+        <v>3.284426229508197</v>
       </c>
       <c r="H64">
-        <v>3.284426229508197</v>
-      </c>
-      <c r="I64">
         <v>2.068908941755538</v>
       </c>
+      <c r="J64">
+        <v>1.984387838948233</v>
+      </c>
       <c r="K64">
-        <v>1.984387838948233</v>
+        <v>2.88934764657308</v>
       </c>
       <c r="L64">
-        <v>2.88934764657308</v>
+        <v>3.408381265406738</v>
       </c>
       <c r="M64">
-        <v>3.408381265406738</v>
+        <v>2.329166666666667</v>
       </c>
       <c r="N64">
-        <v>2.329166666666667</v>
+        <v>2.099337748344371</v>
       </c>
       <c r="O64">
-        <v>2.099337748344371</v>
+        <v>2.711489361702128</v>
       </c>
       <c r="P64">
-        <v>2.711489361702128</v>
+        <v>2.435177539223782</v>
       </c>
       <c r="Q64">
-        <v>2.435177539223782</v>
+        <v>2.66885784716516</v>
       </c>
       <c r="R64">
-        <v>2.66885784716516</v>
+        <v>2.038587848932676</v>
       </c>
       <c r="S64">
-        <v>2.038587848932676</v>
+        <v>1.809958506224066</v>
       </c>
       <c r="T64">
-        <v>1.809958506224066</v>
+        <v>1.909991742361685</v>
       </c>
       <c r="U64">
-        <v>1.909991742361685</v>
+        <v>1.813798836242726</v>
       </c>
       <c r="V64">
-        <v>1.813798836242726</v>
+        <v>2.710570469798658</v>
       </c>
       <c r="W64">
-        <v>2.710570469798658</v>
+        <v>0.5072</v>
       </c>
       <c r="X64">
-        <v>0.5072</v>
+        <v>35.9031224979984</v>
       </c>
       <c r="Y64">
-        <v>0.4928</v>
+        <v>0.9888</v>
       </c>
       <c r="Z64">
-        <v>35.9031224979984</v>
+        <v>5.800670016750419</v>
       </c>
       <c r="AA64">
-        <v>0.9888</v>
-      </c>
-      <c r="AB64">
-        <v>0.0112</v>
-      </c>
-      <c r="AC64">
-        <v>5.800670016750419</v>
-      </c>
-      <c r="AD64">
         <v>5.642282958199357</v>
       </c>
     </row>
@@ -6497,84 +5921,75 @@
         <v>0.5798319327731093</v>
       </c>
       <c r="D65">
-        <v>0.4201680672268908</v>
+        <v>4.169747899159664</v>
       </c>
       <c r="E65">
-        <v>4.169747899159664</v>
+        <v>3.08655462184874</v>
       </c>
       <c r="F65">
-        <v>3.08655462184874</v>
+        <v>1.899159663865546</v>
       </c>
       <c r="G65">
-        <v>1.899159663865546</v>
+        <v>2.214285714285714</v>
       </c>
       <c r="H65">
-        <v>2.214285714285714</v>
+        <v>2.112605042016807</v>
       </c>
       <c r="I65">
-        <v>2.112605042016807</v>
+        <v>4.180672268907563</v>
       </c>
       <c r="J65">
-        <v>4.180672268907563</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="K65">
-        <v>3.285714285714286</v>
+        <v>2.842016806722689</v>
       </c>
       <c r="L65">
-        <v>2.842016806722689</v>
+        <v>5.526890756302521</v>
       </c>
       <c r="M65">
-        <v>5.526890756302521</v>
+        <v>5.226050420168067</v>
       </c>
       <c r="N65">
-        <v>5.226050420168067</v>
+        <v>2.404201680672269</v>
       </c>
       <c r="O65">
-        <v>2.404201680672269</v>
+        <v>3.332197614991482</v>
       </c>
       <c r="P65">
-        <v>3.332197614991482</v>
+        <v>2.099159663865546</v>
       </c>
       <c r="Q65">
-        <v>2.099159663865546</v>
+        <v>3.576470588235294</v>
       </c>
       <c r="R65">
-        <v>3.576470588235294</v>
+        <v>2.37563025210084</v>
       </c>
       <c r="S65">
-        <v>2.37563025210084</v>
+        <v>2.10672268907563</v>
       </c>
       <c r="T65">
-        <v>2.10672268907563</v>
+        <v>4.530252100840336</v>
       </c>
       <c r="U65">
-        <v>4.530252100840336</v>
+        <v>2.378991596638655</v>
       </c>
       <c r="V65">
-        <v>2.378991596638655</v>
+        <v>3.33109243697479</v>
       </c>
       <c r="W65">
-        <v>3.33109243697479</v>
+        <v>0.4798319327731093</v>
       </c>
       <c r="X65">
-        <v>0.4798319327731093</v>
+        <v>38.30924369747899</v>
       </c>
       <c r="Y65">
-        <v>0.5201680672268908</v>
+        <v>0.9882352941176471</v>
       </c>
       <c r="Z65">
-        <v>38.30924369747899</v>
+        <v>4.111858704793945</v>
       </c>
       <c r="AA65">
-        <v>0.9882352941176471</v>
-      </c>
-      <c r="AB65">
-        <v>0.01176470588235294</v>
-      </c>
-      <c r="AC65">
-        <v>4.111858704793945</v>
-      </c>
-      <c r="AD65">
         <v>4.478991596638656</v>
       </c>
     </row>
@@ -6593,84 +6008,75 @@
         <v>0.2983333333333333</v>
       </c>
       <c r="D66">
-        <v>0.7016666666666667</v>
+        <v>4.524166666666667</v>
       </c>
       <c r="E66">
-        <v>4.524166666666667</v>
+        <v>3.424166666666667</v>
       </c>
       <c r="F66">
-        <v>3.424166666666667</v>
+        <v>2.495</v>
       </c>
       <c r="G66">
-        <v>2.495</v>
+        <v>2.8325</v>
       </c>
       <c r="H66">
-        <v>2.8325</v>
+        <v>2.8975</v>
       </c>
       <c r="I66">
-        <v>2.8975</v>
+        <v>5.6425</v>
       </c>
       <c r="J66">
-        <v>5.6425</v>
+        <v>3.946666666666667</v>
       </c>
       <c r="K66">
-        <v>3.946666666666667</v>
+        <v>4.1675</v>
       </c>
       <c r="L66">
-        <v>4.1675</v>
+        <v>5.233333333333333</v>
       </c>
       <c r="M66">
-        <v>5.233333333333333</v>
+        <v>5.526666666666666</v>
       </c>
       <c r="N66">
-        <v>5.526666666666666</v>
+        <v>4.469166666666666</v>
       </c>
       <c r="O66">
-        <v>4.469166666666666</v>
+        <v>4.883333333333334</v>
       </c>
       <c r="P66">
-        <v>4.883333333333334</v>
+        <v>2.801666666666667</v>
       </c>
       <c r="Q66">
-        <v>2.801666666666667</v>
+        <v>4.541666666666667</v>
       </c>
       <c r="R66">
-        <v>4.541666666666667</v>
+        <v>3.0475</v>
       </c>
       <c r="S66">
-        <v>3.0475</v>
+        <v>3.095</v>
       </c>
       <c r="T66">
-        <v>3.095</v>
+        <v>4.900833333333333</v>
       </c>
       <c r="U66">
-        <v>4.900833333333333</v>
+        <v>3.336666666666666</v>
       </c>
       <c r="V66">
-        <v>3.336666666666666</v>
+        <v>4.1725</v>
       </c>
       <c r="W66">
-        <v>4.1725</v>
+        <v>0.4541666666666667</v>
       </c>
       <c r="X66">
-        <v>0.4541666666666667</v>
+        <v>37.8925</v>
       </c>
       <c r="Y66">
-        <v>0.5458333333333333</v>
+        <v>1</v>
       </c>
       <c r="Z66">
-        <v>37.8925</v>
+        <v>4.234166666666667</v>
       </c>
       <c r="AA66">
-        <v>1</v>
-      </c>
-      <c r="AB66">
-        <v>0</v>
-      </c>
-      <c r="AC66">
-        <v>4.234166666666667</v>
-      </c>
-      <c r="AD66">
         <v>5.105833333333333</v>
       </c>
     </row>
@@ -6689,84 +6095,75 @@
         <v>0.7035803497085762</v>
       </c>
       <c r="D67">
-        <v>0.2964196502914238</v>
+        <v>2.216171617161716</v>
       </c>
       <c r="E67">
-        <v>2.216171617161716</v>
+        <v>2.099752679307502</v>
       </c>
       <c r="F67">
-        <v>2.099752679307502</v>
+        <v>1.679571663920923</v>
       </c>
       <c r="G67">
-        <v>1.679571663920923</v>
+        <v>1.855144032921811</v>
       </c>
       <c r="H67">
-        <v>1.855144032921811</v>
+        <v>1.915156507413509</v>
       </c>
       <c r="I67">
-        <v>1.915156507413509</v>
+        <v>1.716996699669967</v>
       </c>
       <c r="J67">
-        <v>1.716996699669967</v>
+        <v>1.797530864197531</v>
       </c>
       <c r="K67">
-        <v>1.797530864197531</v>
+        <v>1.769991755976917</v>
       </c>
       <c r="L67">
-        <v>1.769991755976917</v>
+        <v>2.714756801319044</v>
       </c>
       <c r="M67">
-        <v>2.714756801319044</v>
+        <v>2.360628618693135</v>
       </c>
       <c r="N67">
-        <v>2.360628618693135</v>
+        <v>1.647155812036274</v>
       </c>
       <c r="O67">
-        <v>1.647155812036274</v>
+        <v>1.887510339123242</v>
       </c>
       <c r="P67">
-        <v>1.887510339123242</v>
+        <v>1.903465346534653</v>
       </c>
       <c r="Q67">
-        <v>1.903465346534653</v>
+        <v>4.328073089700997</v>
       </c>
       <c r="R67">
-        <v>4.328073089700997</v>
+        <v>1.738664468260511</v>
       </c>
       <c r="S67">
-        <v>1.738664468260511</v>
+        <v>1.776218001651528</v>
       </c>
       <c r="T67">
-        <v>1.776218001651528</v>
+        <v>1.964550700741962</v>
       </c>
       <c r="U67">
-        <v>1.964550700741962</v>
+        <v>1.703305785123967</v>
       </c>
       <c r="V67">
-        <v>1.703305785123967</v>
+        <v>2.473118279569892</v>
       </c>
       <c r="W67">
-        <v>2.473118279569892</v>
+        <v>0.4938271604938271</v>
       </c>
       <c r="X67">
-        <v>0.4938271604938271</v>
+        <v>39.1494632535095</v>
       </c>
       <c r="Y67">
-        <v>0.5061728395061729</v>
+        <v>0.9934102141680395</v>
       </c>
       <c r="Z67">
-        <v>39.1494632535095</v>
+        <v>3.452596867271228</v>
       </c>
       <c r="AA67">
-        <v>0.9934102141680395</v>
-      </c>
-      <c r="AB67">
-        <v>0.006589785831960461</v>
-      </c>
-      <c r="AC67">
-        <v>3.452596867271228</v>
-      </c>
-      <c r="AD67">
         <v>3.462489694971146</v>
       </c>
     </row>

--- a/WVS_Dataset/WVS7_Country.xlsx
+++ b/WVS_Dataset/WVS7_Country.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA67"/>
+  <dimension ref="A1:AE67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,127 +367,147 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Q165</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Q166</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Q167</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q168</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Q177</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Q178</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Q179</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Q180</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Q181</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Q182</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Q183</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Q184</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Q185</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Q186</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Q187</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Q188</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Q189</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Q190</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Q191</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Q192</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Q193</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Q194</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Q195</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Q260</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Q262</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Q263</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Q275</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Q288</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Q289</t>
         </is>
       </c>
     </row>
@@ -503,79 +523,91 @@
         </is>
       </c>
       <c r="C2">
+        <v>0.641</v>
+      </c>
+      <c r="D2">
+        <v>0.450050454086781</v>
+      </c>
+      <c r="E2">
         <v>0.2678751258811682</v>
       </c>
-      <c r="D2">
+      <c r="F2">
+        <v>0.3279678068410463</v>
+      </c>
+      <c r="G2">
         <v>1.998996990972919</v>
       </c>
-      <c r="E2">
+      <c r="H2">
         <v>1.888223552894212</v>
       </c>
-      <c r="F2">
+      <c r="I2">
         <v>1.505483549351944</v>
       </c>
-      <c r="G2">
+      <c r="J2">
         <v>1.676323676323676</v>
       </c>
-      <c r="H2">
+      <c r="K2">
         <v>1.305694305694306</v>
       </c>
-      <c r="I2">
+      <c r="L2">
         <v>8.025025025025025</v>
       </c>
-      <c r="J2">
+      <c r="M2">
         <v>4.734939759036145</v>
       </c>
-      <c r="K2">
+      <c r="N2">
         <v>6.074074074074074</v>
       </c>
-      <c r="L2">
+      <c r="O2">
         <v>8.244</v>
       </c>
-      <c r="M2">
+      <c r="P2">
         <v>8.191767068273093</v>
       </c>
-      <c r="N2">
+      <c r="Q2">
         <v>3.638</v>
       </c>
-      <c r="O2">
+      <c r="R2">
         <v>6.186304128902316</v>
       </c>
-      <c r="P2">
+      <c r="S2">
         <v>1.203796203796204</v>
       </c>
-      <c r="Q2">
+      <c r="T2">
         <v>1.690927218344965</v>
       </c>
-      <c r="R2">
+      <c r="U2">
         <v>1.296407185628742</v>
       </c>
-      <c r="S2">
+      <c r="V2">
         <v>1.124</v>
       </c>
-      <c r="T2">
+      <c r="W2">
         <v>5.68505516549649</v>
       </c>
-      <c r="U2">
+      <c r="X2">
         <v>1.337662337662338</v>
       </c>
-      <c r="V2">
+      <c r="Y2">
         <v>3.396603396603397</v>
       </c>
-      <c r="W2">
+      <c r="Z2">
         <v>0.5069721115537849</v>
       </c>
-      <c r="X2">
+      <c r="AA2">
         <v>46.82569721115538</v>
       </c>
-      <c r="Y2">
+      <c r="AB2">
         <v>0.2768924302788844</v>
       </c>
-      <c r="Z2">
+      <c r="AC2">
         <v>4.856430707876371</v>
       </c>
-      <c r="AA2">
+      <c r="AD2">
         <v>5.355605889014723</v>
+      </c>
+      <c r="AE2">
+        <v>8.089820359281438</v>
       </c>
     </row>
     <row r="3">
@@ -590,79 +622,91 @@
         </is>
       </c>
       <c r="C3">
+        <v>0.9109311740890689</v>
+      </c>
+      <c r="D3">
+        <v>0.6341730558598029</v>
+      </c>
+      <c r="E3">
         <v>0.5277185501066098</v>
       </c>
-      <c r="D3">
+      <c r="F3">
+        <v>0.7034700315457413</v>
+      </c>
+      <c r="G3">
         <v>4.559877175025589</v>
       </c>
-      <c r="E3">
+      <c r="H3">
         <v>3.049645390070922</v>
       </c>
-      <c r="F3">
+      <c r="I3">
         <v>1.7293997965412</v>
       </c>
-      <c r="G3">
+      <c r="J3">
         <v>2.141116751269036</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>1.875757575757576</v>
       </c>
-      <c r="I3">
+      <c r="L3">
         <v>6.023411371237458</v>
       </c>
-      <c r="J3">
+      <c r="M3">
         <v>3.919477693144723</v>
       </c>
-      <c r="K3">
+      <c r="N3">
         <v>3.630252100840336</v>
       </c>
-      <c r="L3">
+      <c r="O3">
         <v>6.530590717299578</v>
       </c>
-      <c r="M3">
+      <c r="P3">
         <v>6.739084132055378</v>
       </c>
-      <c r="N3">
+      <c r="Q3">
         <v>2.662740899357602</v>
       </c>
-      <c r="O3">
+      <c r="R3">
         <v>3.857634902411022</v>
       </c>
-      <c r="P3">
+      <c r="S3">
         <v>1.440320962888666</v>
       </c>
-      <c r="Q3">
+      <c r="T3">
         <v>1.944723618090452</v>
       </c>
-      <c r="R3">
+      <c r="U3">
         <v>1.725806451612903</v>
       </c>
-      <c r="S3">
+      <c r="V3">
         <v>1.606924643584521</v>
       </c>
-      <c r="T3">
+      <c r="W3">
         <v>5.269602577873255</v>
       </c>
-      <c r="U3">
+      <c r="X3">
         <v>1.858617131062952</v>
       </c>
-      <c r="V3">
+      <c r="Y3">
         <v>3.383575883575884</v>
       </c>
-      <c r="W3">
+      <c r="Z3">
         <v>0.4835493519441675</v>
       </c>
-      <c r="X3">
+      <c r="AA3">
         <v>42.55134596211366</v>
       </c>
-      <c r="Y3">
+      <c r="AB3">
         <v>0.9790628115653041</v>
       </c>
-      <c r="Z3">
+      <c r="AC3">
         <v>3.735792622133599</v>
       </c>
-      <c r="AA3">
+      <c r="AD3">
         <v>5.078616352201258</v>
+      </c>
+      <c r="AE3">
+        <v>7.502004008016032</v>
       </c>
     </row>
     <row r="4">
@@ -677,79 +721,91 @@
         </is>
       </c>
       <c r="C4">
+        <v>0.9495033112582781</v>
+      </c>
+      <c r="D4">
+        <v>0.4391582799634035</v>
+      </c>
+      <c r="E4">
         <v>0.4286995515695067</v>
       </c>
-      <c r="D4">
+      <c r="F4">
+        <v>0.482078853046595</v>
+      </c>
+      <c r="G4">
         <v>1.863523573200992</v>
       </c>
-      <c r="E4">
+      <c r="H4">
         <v>1.408230452674897</v>
       </c>
-      <c r="F4">
+      <c r="I4">
         <v>1.136288998357964</v>
       </c>
-      <c r="G4">
+      <c r="J4">
         <v>1.665296052631579</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>1.281481481481481</v>
       </c>
-      <c r="I4">
+      <c r="L4">
         <v>1.372937293729373</v>
       </c>
-      <c r="J4">
+      <c r="M4">
         <v>1.360561056105611</v>
       </c>
-      <c r="K4">
+      <c r="N4">
         <v>2.485762144053601</v>
       </c>
-      <c r="L4">
+      <c r="O4">
         <v>3.611433305716653</v>
       </c>
-      <c r="M4">
+      <c r="P4">
         <v>2.494176372712146</v>
       </c>
-      <c r="N4">
+      <c r="Q4">
         <v>1.313886606409203</v>
       </c>
-      <c r="O4">
+      <c r="R4">
         <v>2.460492778249788</v>
       </c>
-      <c r="P4">
+      <c r="S4">
         <v>1.246103363412633</v>
       </c>
-      <c r="Q4">
+      <c r="T4">
         <v>1.911330049261084</v>
       </c>
-      <c r="R4">
+      <c r="U4">
         <v>1.270114942528736</v>
       </c>
-      <c r="S4">
+      <c r="V4">
         <v>1.239202657807309</v>
       </c>
-      <c r="T4">
+      <c r="W4">
         <v>1.684297520661157</v>
       </c>
-      <c r="U4">
+      <c r="X4">
         <v>1.184755592377796</v>
       </c>
-      <c r="V4">
+      <c r="Y4">
         <v>2.664739884393064</v>
       </c>
-      <c r="W4">
+      <c r="Z4">
         <v>0.3139820114472608</v>
       </c>
-      <c r="X4">
+      <c r="AA4">
         <v>49.04415372035977</v>
       </c>
-      <c r="Y4">
+      <c r="AB4">
         <v>0.9351395730706076</v>
       </c>
-      <c r="Z4">
+      <c r="AC4">
         <v>5.438683127572016</v>
       </c>
-      <c r="AA4">
+      <c r="AD4">
         <v>4.702145214521452</v>
+      </c>
+      <c r="AE4">
+        <v>6.085036794766967</v>
       </c>
     </row>
     <row r="5">
@@ -764,79 +820,91 @@
         </is>
       </c>
       <c r="C5">
+        <v>0.5858187957231289</v>
+      </c>
+      <c r="D5">
+        <v>0.5331820760068066</v>
+      </c>
+      <c r="E5">
         <v>0.2846674182638106</v>
       </c>
-      <c r="D5">
+      <c r="F5">
+        <v>0.4906726964386659</v>
+      </c>
+      <c r="G5">
         <v>1.778953229398664</v>
       </c>
-      <c r="E5">
+      <c r="H5">
         <v>2.205701509223029</v>
       </c>
-      <c r="F5">
+      <c r="I5">
         <v>1.40133779264214</v>
       </c>
-      <c r="G5">
+      <c r="J5">
         <v>1.848687883863763</v>
       </c>
-      <c r="H5">
+      <c r="K5">
         <v>1.435025097601785</v>
       </c>
-      <c r="I5">
+      <c r="L5">
         <v>7.387720295622513</v>
       </c>
-      <c r="J5">
+      <c r="M5">
         <v>5.173371104815864</v>
       </c>
-      <c r="K5">
+      <c r="N5">
         <v>6.562323745064861</v>
       </c>
-      <c r="L5">
+      <c r="O5">
         <v>7.738270209157716</v>
       </c>
-      <c r="M5">
+      <c r="P5">
         <v>7.884659090909091</v>
       </c>
-      <c r="N5">
+      <c r="Q5">
         <v>4.038439796495195</v>
       </c>
-      <c r="O5">
+      <c r="R5">
         <v>6.688775510204081</v>
       </c>
-      <c r="P5">
+      <c r="S5">
         <v>1.241340782122905</v>
       </c>
-      <c r="Q5">
+      <c r="T5">
         <v>1.608040201005025</v>
       </c>
-      <c r="R5">
+      <c r="U5">
         <v>1.595637583892617</v>
       </c>
-      <c r="S5">
+      <c r="V5">
         <v>1.321967579653438</v>
       </c>
-      <c r="T5">
+      <c r="W5">
         <v>6.078753541076487</v>
       </c>
-      <c r="U5">
+      <c r="X5">
         <v>1.711160964666293</v>
       </c>
-      <c r="V5">
+      <c r="Y5">
         <v>4.453168816601234</v>
       </c>
-      <c r="W5">
+      <c r="Z5">
         <v>0.3913285158421345</v>
       </c>
-      <c r="X5">
+      <c r="AA5">
         <v>54.2958217270195</v>
       </c>
-      <c r="Y5">
+      <c r="AB5">
         <v>0.9284525790349417</v>
       </c>
-      <c r="Z5">
+      <c r="AC5">
         <v>5.655192197360872</v>
       </c>
-      <c r="AA5">
+      <c r="AD5">
         <v>5.127574370709382</v>
+      </c>
+      <c r="AE5">
+        <v>6.842760180995475</v>
       </c>
     </row>
     <row r="6">
@@ -851,79 +919,91 @@
         </is>
       </c>
       <c r="C6">
+        <v>0.9983333333333333</v>
+      </c>
+      <c r="D6">
+        <v>0.9891576313594662</v>
+      </c>
+      <c r="E6">
         <v>0.9933166248955723</v>
       </c>
-      <c r="D6">
+      <c r="F6">
+        <v>0.9941520467836257</v>
+      </c>
+      <c r="G6">
         <v>2.024166666666666</v>
       </c>
-      <c r="E6">
+      <c r="H6">
         <v>1.800833333333333</v>
       </c>
-      <c r="F6">
+      <c r="I6">
         <v>1.554166666666667</v>
       </c>
-      <c r="G6">
+      <c r="J6">
         <v>1.700833333333333</v>
       </c>
-      <c r="H6">
+      <c r="K6">
         <v>1.6075</v>
       </c>
-      <c r="I6">
+      <c r="L6">
         <v>1.6875</v>
       </c>
-      <c r="J6">
+      <c r="M6">
         <v>1.6</v>
       </c>
-      <c r="K6">
+      <c r="N6">
         <v>2.021666666666667</v>
       </c>
-      <c r="L6">
+      <c r="O6">
         <v>2.17</v>
       </c>
-      <c r="M6">
+      <c r="P6">
         <v>1.505</v>
       </c>
-      <c r="N6">
+      <c r="Q6">
         <v>1.9</v>
       </c>
-      <c r="O6">
+      <c r="R6">
         <v>2.7775</v>
       </c>
-      <c r="P6">
+      <c r="S6">
         <v>1.915</v>
       </c>
-      <c r="Q6">
+      <c r="T6">
         <v>2.155833333333333</v>
       </c>
-      <c r="R6">
+      <c r="U6">
         <v>1.794166666666667</v>
       </c>
-      <c r="S6">
+      <c r="V6">
         <v>1.795</v>
       </c>
-      <c r="T6">
+      <c r="W6">
         <v>1.488333333333333</v>
       </c>
-      <c r="U6">
+      <c r="X6">
         <v>1.750833333333333</v>
       </c>
-      <c r="V6">
+      <c r="Y6">
         <v>2.7525</v>
       </c>
-      <c r="W6">
+      <c r="Z6">
         <v>0.4933333333333333</v>
       </c>
-      <c r="X6">
+      <c r="AA6">
         <v>36.59083333333334</v>
       </c>
-      <c r="Y6">
+      <c r="AB6">
         <v>1</v>
       </c>
-      <c r="Z6">
+      <c r="AC6">
         <v>2.853211009174312</v>
       </c>
-      <c r="AA6">
+      <c r="AD6">
         <v>5.615</v>
+      </c>
+      <c r="AE6">
+        <v>3.8925</v>
       </c>
     </row>
     <row r="7">
@@ -938,79 +1018,91 @@
         </is>
       </c>
       <c r="C7">
+        <v>0.9776699029126213</v>
+      </c>
+      <c r="D7">
+        <v>0.7485832045337455</v>
+      </c>
+      <c r="E7">
         <v>0.6122037317196167</v>
       </c>
-      <c r="D7">
+      <c r="F7">
+        <v>0.8684470820969338</v>
+      </c>
+      <c r="G7">
         <v>4.969046430354468</v>
       </c>
-      <c r="E7">
+      <c r="H7">
         <v>3.962162162162162</v>
       </c>
-      <c r="F7">
+      <c r="I7">
         <v>1.553779069767442</v>
       </c>
-      <c r="G7">
+      <c r="J7">
         <v>2.037745098039216</v>
       </c>
-      <c r="H7">
+      <c r="K7">
         <v>2.045767716535433</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>3.301595744680851</v>
       </c>
-      <c r="J7">
+      <c r="M7">
         <v>2.79938900203666</v>
       </c>
-      <c r="K7">
+      <c r="N7">
         <v>2.270628683693517</v>
       </c>
-      <c r="L7">
+      <c r="O7">
         <v>3.98416625432954</v>
       </c>
-      <c r="M7">
+      <c r="P7">
         <v>3.87871033776868</v>
       </c>
-      <c r="N7">
+      <c r="Q7">
         <v>2.156979632389469</v>
       </c>
-      <c r="O7">
+      <c r="R7">
         <v>3.197695573074591</v>
       </c>
-      <c r="P7">
+      <c r="S7">
         <v>1.749027237354086</v>
       </c>
-      <c r="Q7">
+      <c r="T7">
         <v>2.599805258033106</v>
       </c>
-      <c r="R7">
+      <c r="U7">
         <v>2.003424657534246</v>
       </c>
-      <c r="S7">
+      <c r="V7">
         <v>1.923274974253347</v>
       </c>
-      <c r="T7">
+      <c r="W7">
         <v>2.623529411764706</v>
       </c>
-      <c r="U7">
+      <c r="X7">
         <v>2.05873568939771</v>
       </c>
-      <c r="V7">
+      <c r="Y7">
         <v>3.649201596806387</v>
       </c>
-      <c r="W7">
+      <c r="Z7">
         <v>0.4954039671020803</v>
       </c>
-      <c r="X7">
+      <c r="AA7">
         <v>38.33284954039671</v>
       </c>
-      <c r="Y7">
+      <c r="AB7">
         <v>0.9961259079903148</v>
       </c>
-      <c r="Z7">
+      <c r="AC7">
         <v>4.350315380883067</v>
       </c>
-      <c r="AA7">
+      <c r="AD7">
         <v>5.013412816691505</v>
+      </c>
+      <c r="AE7">
+        <v>7.585873246250605</v>
       </c>
     </row>
     <row r="8">
@@ -1025,79 +1117,91 @@
         </is>
       </c>
       <c r="C8">
+        <v>0.975792507204611</v>
+      </c>
+      <c r="D8">
+        <v>0.6371173469387755</v>
+      </c>
+      <c r="E8">
         <v>0.6868437306979617</v>
       </c>
-      <c r="D8">
+      <c r="F8">
+        <v>0.8067278287461773</v>
+      </c>
+      <c r="G8">
         <v>2.437609841827768</v>
       </c>
-      <c r="E8">
+      <c r="H8">
         <v>3.547912992357437</v>
       </c>
-      <c r="F8">
+      <c r="I8">
         <v>1.521086077411901</v>
       </c>
-      <c r="G8">
+      <c r="J8">
         <v>2.995901639344262</v>
       </c>
-      <c r="H8">
+      <c r="K8">
         <v>1.574739281575898</v>
       </c>
-      <c r="I8">
+      <c r="L8">
         <v>4.946879150066401</v>
       </c>
-      <c r="J8">
+      <c r="M8">
         <v>3.211706102117061</v>
       </c>
-      <c r="K8">
+      <c r="N8">
         <v>2.506261180679785</v>
       </c>
-      <c r="L8">
+      <c r="O8">
         <v>6.221560452650387</v>
       </c>
-      <c r="M8">
+      <c r="P8">
         <v>5.915337423312883</v>
       </c>
-      <c r="N8">
+      <c r="Q8">
         <v>2.054198927933294</v>
       </c>
-      <c r="O8">
+      <c r="R8">
         <v>3.196904024767802</v>
       </c>
-      <c r="P8">
+      <c r="S8">
         <v>1.374423963133641</v>
       </c>
-      <c r="Q8">
+      <c r="T8">
         <v>4.384037015615963</v>
       </c>
-      <c r="R8">
+      <c r="U8">
         <v>1.741230592294422</v>
       </c>
-      <c r="S8">
+      <c r="V8">
         <v>1.511255924170616</v>
       </c>
-      <c r="T8">
+      <c r="W8">
         <v>4.484177215189874</v>
       </c>
-      <c r="U8">
+      <c r="X8">
         <v>1.694229625223082</v>
       </c>
-      <c r="V8">
+      <c r="Y8">
         <v>4.128801431127012</v>
       </c>
-      <c r="W8">
+      <c r="Z8">
         <v>0.4540295119182747</v>
       </c>
-      <c r="X8">
+      <c r="AA8">
         <v>43.55536626916525</v>
       </c>
-      <c r="Y8">
+      <c r="AB8">
         <v>0.9948921679909194</v>
       </c>
-      <c r="Z8">
+      <c r="AC8">
         <v>3.777970011534026</v>
       </c>
-      <c r="AA8">
+      <c r="AD8">
         <v>4.018270401948842</v>
+      </c>
+      <c r="AE8">
+        <v>7.357515960533952</v>
       </c>
     </row>
     <row r="9">
@@ -1112,79 +1216,91 @@
         </is>
       </c>
       <c r="C9">
+        <v>0.5532603285216525</v>
+      </c>
+      <c r="D9">
+        <v>0.5525136884021902</v>
+      </c>
+      <c r="E9">
         <v>0.3359880537580886</v>
       </c>
-      <c r="D9">
+      <c r="F9">
+        <v>0.4554504728720757</v>
+      </c>
+      <c r="G9">
         <v>2.335988053758089</v>
       </c>
-      <c r="E9">
+      <c r="H9">
         <v>3.331508213041314</v>
       </c>
-      <c r="F9">
+      <c r="I9">
         <v>2.193130910900946</v>
       </c>
-      <c r="G9">
+      <c r="J9">
         <v>2.584370333499253</v>
       </c>
-      <c r="H9">
+      <c r="K9">
         <v>2.241911398705824</v>
       </c>
-      <c r="I9">
+      <c r="L9">
         <v>7.749128919860627</v>
       </c>
-      <c r="J9">
+      <c r="M9">
         <v>4.976854156296665</v>
       </c>
-      <c r="K9">
+      <c r="N9">
         <v>6.739920358387257</v>
       </c>
-      <c r="L9">
+      <c r="O9">
         <v>7.264310602289696</v>
       </c>
-      <c r="M9">
+      <c r="P9">
         <v>7.835988053758089</v>
       </c>
-      <c r="N9">
+      <c r="Q9">
         <v>4.170233947237431</v>
       </c>
-      <c r="O9">
+      <c r="R9">
         <v>6.231956197112992</v>
       </c>
-      <c r="P9">
+      <c r="S9">
         <v>1.630662020905923</v>
       </c>
-      <c r="Q9">
+      <c r="T9">
         <v>2.104280736684918</v>
       </c>
-      <c r="R9">
+      <c r="U9">
         <v>2.422598307615729</v>
       </c>
-      <c r="S9">
+      <c r="V9">
         <v>1.845445495271279</v>
       </c>
-      <c r="T9">
+      <c r="W9">
         <v>6.788949726231956</v>
       </c>
-      <c r="U9">
+      <c r="X9">
         <v>2.539571926331508</v>
       </c>
-      <c r="V9">
+      <c r="Y9">
         <v>4.839223494275759</v>
       </c>
-      <c r="W9">
+      <c r="Z9">
         <v>0.5124440019910403</v>
       </c>
-      <c r="X9">
+      <c r="AA9">
         <v>46.56470881035341</v>
       </c>
-      <c r="Y9">
+      <c r="AB9">
         <v>0.821304131408661</v>
       </c>
-      <c r="Z9">
+      <c r="AC9">
         <v>5.894420815611709</v>
       </c>
-      <c r="AA9">
+      <c r="AD9">
         <v>5.573668491786958</v>
+      </c>
+      <c r="AE9">
+        <v>7.629417620706819</v>
       </c>
     </row>
     <row r="10">
@@ -1199,79 +1315,91 @@
         </is>
       </c>
       <c r="C10">
+        <v>0.8609958506224067</v>
+      </c>
+      <c r="D10">
+        <v>0.6970720720720721</v>
+      </c>
+      <c r="E10">
         <v>0.5189732142857143</v>
       </c>
-      <c r="D10">
+      <c r="F10">
+        <v>0.6481687014428413</v>
+      </c>
+      <c r="G10">
         <v>4.523908523908524</v>
       </c>
-      <c r="E10">
+      <c r="H10">
         <v>3.172661870503597</v>
       </c>
-      <c r="F10">
+      <c r="I10">
         <v>2.014155712841254</v>
       </c>
-      <c r="G10">
+      <c r="J10">
         <v>2.423350253807107</v>
       </c>
-      <c r="H10">
+      <c r="K10">
         <v>2.282807731434385</v>
       </c>
-      <c r="I10">
+      <c r="L10">
         <v>5.317256162915327</v>
       </c>
-      <c r="J10">
+      <c r="M10">
         <v>3.561965811965812</v>
       </c>
-      <c r="K10">
+      <c r="N10">
         <v>3.869294605809129</v>
       </c>
-      <c r="L10">
+      <c r="O10">
         <v>6.380122950819672</v>
       </c>
-      <c r="M10">
+      <c r="P10">
         <v>6.496304118268215</v>
       </c>
-      <c r="N10">
+      <c r="Q10">
         <v>3.154973821989529</v>
       </c>
-      <c r="O10">
+      <c r="R10">
         <v>4.18849840255591</v>
       </c>
-      <c r="P10">
+      <c r="S10">
         <v>1.847715736040609</v>
       </c>
-      <c r="Q10">
+      <c r="T10">
         <v>2.018200202224469</v>
       </c>
-      <c r="R10">
+      <c r="U10">
         <v>2.041456016177957</v>
       </c>
-      <c r="S10">
+      <c r="V10">
         <v>2.053861788617886</v>
       </c>
-      <c r="T10">
+      <c r="W10">
         <v>4.529032258064516</v>
       </c>
-      <c r="U10">
+      <c r="X10">
         <v>2.361593462717058</v>
       </c>
-      <c r="V10">
+      <c r="Y10">
         <v>4.25231719876416</v>
       </c>
-      <c r="W10">
+      <c r="Z10">
         <v>0.474</v>
       </c>
-      <c r="X10">
+      <c r="AA10">
         <v>45.271</v>
       </c>
-      <c r="Y10">
+      <c r="AB10">
         <v>0.983</v>
       </c>
-      <c r="Z10">
+      <c r="AC10">
         <v>4.821643286573146</v>
       </c>
-      <c r="AA10">
+      <c r="AD10">
         <v>4.675564681724846</v>
+      </c>
+      <c r="AE10">
+        <v>7.800829875518672</v>
       </c>
     </row>
     <row r="11">
@@ -1286,79 +1414,91 @@
         </is>
       </c>
       <c r="C11">
+        <v>0.1747765640516385</v>
+      </c>
+      <c r="D11">
+        <v>0.1161247511612475</v>
+      </c>
+      <c r="E11">
         <v>0.1089700996677741</v>
       </c>
-      <c r="D11">
+      <c r="F11">
+        <v>0.1204258150365935</v>
+      </c>
+      <c r="G11">
         <v>3.296626984126984</v>
       </c>
-      <c r="E11">
+      <c r="H11">
         <v>1.614394189501486</v>
       </c>
-      <c r="F11">
+      <c r="I11">
         <v>1.287883790029713</v>
       </c>
-      <c r="G11">
+      <c r="J11">
         <v>1.498842209725438</v>
       </c>
-      <c r="H11">
+      <c r="K11">
         <v>1.600331125827815</v>
       </c>
-      <c r="I11">
+      <c r="L11">
         <v>2.31801652892562</v>
       </c>
-      <c r="J11">
+      <c r="M11">
         <v>1.476206212822208</v>
       </c>
-      <c r="K11">
+      <c r="N11">
         <v>2.437230871149387</v>
       </c>
-      <c r="L11">
+      <c r="O11">
         <v>3.750331125827814</v>
       </c>
-      <c r="M11">
+      <c r="P11">
         <v>3.706799336650083</v>
       </c>
-      <c r="N11">
+      <c r="Q11">
         <v>1.942091330244871</v>
       </c>
-      <c r="O11">
+      <c r="R11">
         <v>4.002319416832339</v>
       </c>
-      <c r="P11">
+      <c r="S11">
         <v>1.553754548461793</v>
       </c>
-      <c r="Q11">
+      <c r="T11">
         <v>3.339622641509434</v>
       </c>
-      <c r="R11">
+      <c r="U11">
         <v>1.634348113831899</v>
       </c>
-      <c r="S11">
+      <c r="V11">
         <v>1.324834437086093</v>
       </c>
-      <c r="T11">
+      <c r="W11">
         <v>1.511250827266711</v>
       </c>
-      <c r="U11">
+      <c r="X11">
         <v>1.504477611940298</v>
       </c>
-      <c r="V11">
+      <c r="Y11">
         <v>5.518028448561032</v>
       </c>
-      <c r="W11">
+      <c r="Z11">
         <v>0.4509222661396575</v>
       </c>
-      <c r="X11">
+      <c r="AA11">
         <v>44.58498023715415</v>
       </c>
-      <c r="Y11">
+      <c r="AB11">
         <v>1</v>
       </c>
-      <c r="Z11">
+      <c r="AC11">
         <v>3.834331337325349</v>
       </c>
-      <c r="AA11">
+      <c r="AD11">
         <v>4.147176079734219</v>
+      </c>
+      <c r="AE11">
+        <v>8.229923358880374</v>
       </c>
     </row>
     <row r="12">
@@ -1373,79 +1513,91 @@
         </is>
       </c>
       <c r="C12">
+        <v>0.9638157894736842</v>
+      </c>
+      <c r="D12">
+        <v>0.6164473684210526</v>
+      </c>
+      <c r="E12">
         <v>0.5223684210526316</v>
       </c>
-      <c r="D12">
+      <c r="F12">
+        <v>0.8052631578947368</v>
+      </c>
+      <c r="G12">
         <v>3.777631578947368</v>
       </c>
-      <c r="E12">
+      <c r="H12">
         <v>3.663815789473684</v>
       </c>
-      <c r="F12">
+      <c r="I12">
         <v>1.586184210526316</v>
       </c>
-      <c r="G12">
+      <c r="J12">
         <v>2.052631578947369</v>
       </c>
-      <c r="H12">
+      <c r="K12">
         <v>1.870394736842105</v>
       </c>
-      <c r="I12">
+      <c r="L12">
         <v>4.061842105263158</v>
       </c>
-      <c r="J12">
+      <c r="M12">
         <v>3.093421052631579</v>
       </c>
-      <c r="K12">
+      <c r="N12">
         <v>2.353289473684211</v>
       </c>
-      <c r="L12">
+      <c r="O12">
         <v>4.705263157894737</v>
       </c>
-      <c r="M12">
+      <c r="P12">
         <v>5.05</v>
       </c>
-      <c r="N12">
+      <c r="Q12">
         <v>2.123026315789474</v>
       </c>
-      <c r="O12">
+      <c r="R12">
         <v>3.809210526315789</v>
       </c>
-      <c r="P12">
+      <c r="S12">
         <v>1.552631578947368</v>
       </c>
-      <c r="Q12">
+      <c r="T12">
         <v>3.594736842105263</v>
       </c>
-      <c r="R12">
+      <c r="U12">
         <v>1.783552631578947</v>
       </c>
-      <c r="S12">
+      <c r="V12">
         <v>1.744736842105263</v>
       </c>
-      <c r="T12">
+      <c r="W12">
         <v>3.669736842105263</v>
       </c>
-      <c r="U12">
+      <c r="X12">
         <v>1.877631578947368</v>
       </c>
-      <c r="V12">
+      <c r="Y12">
         <v>3.9625</v>
       </c>
-      <c r="W12">
+      <c r="Z12">
         <v>0.5</v>
       </c>
-      <c r="X12">
+      <c r="AA12">
         <v>38.84605263157895</v>
       </c>
-      <c r="Y12">
+      <c r="AB12">
         <v>0.9710526315789474</v>
       </c>
-      <c r="Z12">
+      <c r="AC12">
         <v>4.119492656875835</v>
       </c>
-      <c r="AA12">
+      <c r="AD12">
         <v>4.442763157894737</v>
+      </c>
+      <c r="AE12">
+        <v>7.660526315789474</v>
       </c>
     </row>
     <row r="13">
@@ -1460,79 +1612,91 @@
         </is>
       </c>
       <c r="C13">
+        <v>0.9490986214209968</v>
+      </c>
+      <c r="D13">
+        <v>0.7234299516908212</v>
+      </c>
+      <c r="E13">
         <v>0.6993939393939393</v>
       </c>
-      <c r="D13">
+      <c r="F13">
+        <v>0.7322074788902292</v>
+      </c>
+      <c r="G13">
         <v>2.138351983723296</v>
       </c>
-      <c r="E13">
+      <c r="H13">
         <v>2.880081300813008</v>
       </c>
-      <c r="F13">
+      <c r="I13">
         <v>1.454545454545455</v>
       </c>
-      <c r="G13">
+      <c r="J13">
         <v>1.609879032258065</v>
       </c>
-      <c r="H13">
+      <c r="K13">
         <v>1.539393939393939</v>
       </c>
-      <c r="I13">
+      <c r="L13">
         <v>3.725</v>
       </c>
-      <c r="J13">
+      <c r="M13">
         <v>2.238805970149254</v>
       </c>
-      <c r="K13">
+      <c r="N13">
         <v>3.016025641025641</v>
       </c>
-      <c r="L13">
+      <c r="O13">
         <v>5.200415368639668</v>
       </c>
-      <c r="M13">
+      <c r="P13">
         <v>5.077753779697624</v>
       </c>
-      <c r="N13">
+      <c r="Q13">
         <v>1.757158006362672</v>
       </c>
-      <c r="O13">
+      <c r="R13">
         <v>2.722103004291846</v>
       </c>
-      <c r="P13">
+      <c r="S13">
         <v>1.321536905965622</v>
       </c>
-      <c r="Q13">
+      <c r="T13">
         <v>1.474747474747475</v>
       </c>
-      <c r="R13">
+      <c r="U13">
         <v>1.424547283702213</v>
       </c>
-      <c r="S13">
+      <c r="V13">
         <v>1.252032520325203</v>
       </c>
-      <c r="T13">
+      <c r="W13">
         <v>2.837060702875399</v>
       </c>
-      <c r="U13">
+      <c r="X13">
         <v>1.328600405679513</v>
       </c>
-      <c r="V13">
+      <c r="Y13">
         <v>2.674513817809621</v>
       </c>
-      <c r="W13">
+      <c r="Z13">
         <v>0.482</v>
       </c>
-      <c r="X13">
+      <c r="AA13">
         <v>43.539</v>
       </c>
-      <c r="Y13">
+      <c r="AB13">
         <v>0.78</v>
       </c>
-      <c r="Z13">
+      <c r="AC13">
         <v>5.449021627188466</v>
       </c>
-      <c r="AA13">
+      <c r="AD13">
         <v>5.273695420660277</v>
+      </c>
+      <c r="AE13">
+        <v>5.031093279839519</v>
       </c>
     </row>
     <row r="14">
@@ -1547,79 +1711,91 @@
         </is>
       </c>
       <c r="C14">
+        <v>0.2600349040139616</v>
+      </c>
+      <c r="D14">
+        <v>0.2574955908289241</v>
+      </c>
+      <c r="E14">
         <v>0.1201754385964912</v>
       </c>
-      <c r="D14">
+      <c r="F14">
+        <v>0.2230971128608924</v>
+      </c>
+      <c r="G14">
         <v>3.270657672849916</v>
       </c>
-      <c r="E14">
+      <c r="H14">
         <v>4.354621848739495</v>
       </c>
-      <c r="F14">
+      <c r="I14">
         <v>2.648241206030151</v>
       </c>
-      <c r="G14">
+      <c r="J14">
         <v>3.262626262626263</v>
       </c>
-      <c r="H14">
+      <c r="K14">
         <v>3.02436974789916</v>
       </c>
-      <c r="I14">
+      <c r="L14">
         <v>6.676295666949873</v>
       </c>
-      <c r="J14">
+      <c r="M14">
         <v>5.087542087542087</v>
       </c>
-      <c r="K14">
+      <c r="N14">
         <v>6.133389261744966</v>
       </c>
-      <c r="L14">
+      <c r="O14">
         <v>6.855462184873949</v>
       </c>
-      <c r="M14">
+      <c r="P14">
         <v>7.935185185185185</v>
       </c>
-      <c r="N14">
+      <c r="Q14">
         <v>4.785896346644011</v>
       </c>
-      <c r="O14">
+      <c r="R14">
         <v>6.068085106382979</v>
       </c>
-      <c r="P14">
+      <c r="S14">
         <v>2.025125628140704</v>
       </c>
-      <c r="Q14">
+      <c r="T14">
         <v>3.206521739130435</v>
       </c>
-      <c r="R14">
+      <c r="U14">
         <v>2.178242677824268</v>
       </c>
-      <c r="S14">
+      <c r="V14">
         <v>2.006694560669456</v>
       </c>
-      <c r="T14">
+      <c r="W14">
         <v>6.420473773265652</v>
       </c>
-      <c r="U14">
+      <c r="X14">
         <v>2.479359730412805</v>
       </c>
-      <c r="V14">
+      <c r="Y14">
         <v>4.815722738799662</v>
       </c>
-      <c r="W14">
+      <c r="Z14">
         <v>0.4608333333333333</v>
       </c>
-      <c r="X14">
+      <c r="AA14">
         <v>49.11416666666667</v>
       </c>
-      <c r="Y14">
+      <c r="AB14">
         <v>0.9699749791492911</v>
       </c>
-      <c r="Z14">
+      <c r="AC14">
         <v>4.145954962468724</v>
       </c>
-      <c r="AA14">
+      <c r="AD14">
         <v>5.233558178752108</v>
+      </c>
+      <c r="AE14">
+        <v>8.689597315436242</v>
       </c>
     </row>
     <row r="15">
@@ -1634,79 +1810,91 @@
         </is>
       </c>
       <c r="C15">
+        <v>0.5930313588850175</v>
+      </c>
+      <c r="D15">
+        <v>0.4344322344322344</v>
+      </c>
+      <c r="E15">
         <v>0.1573426573426573</v>
       </c>
-      <c r="D15">
+      <c r="F15">
+        <v>0.3291050035236082</v>
+      </c>
+      <c r="G15">
         <v>1.538258575197889</v>
       </c>
-      <c r="E15">
+      <c r="H15">
         <v>1.829508196721311</v>
       </c>
-      <c r="F15">
+      <c r="I15">
         <v>1.162303664921466</v>
       </c>
-      <c r="G15">
+      <c r="J15">
         <v>1.517105263157895</v>
       </c>
-      <c r="H15">
+      <c r="K15">
         <v>1.325459317585302</v>
       </c>
-      <c r="I15">
+      <c r="L15">
         <v>7.855989232839838</v>
       </c>
-      <c r="J15">
+      <c r="M15">
         <v>4.969737726967048</v>
       </c>
-      <c r="K15">
+      <c r="N15">
         <v>5.460810810810811</v>
       </c>
-      <c r="L15">
+      <c r="O15">
         <v>7.397870924817033</v>
       </c>
-      <c r="M15">
+      <c r="P15">
         <v>8.522666666666666</v>
       </c>
-      <c r="N15">
+      <c r="Q15">
         <v>4.171864171864172</v>
       </c>
-      <c r="O15">
+      <c r="R15">
         <v>7.128859060402685</v>
       </c>
-      <c r="P15">
+      <c r="S15">
         <v>1.106745252128356</v>
       </c>
-      <c r="Q15">
+      <c r="T15">
         <v>1.508541392904074</v>
       </c>
-      <c r="R15">
+      <c r="U15">
         <v>1.321733420879842</v>
       </c>
-      <c r="S15">
+      <c r="V15">
         <v>1.110819672131148</v>
       </c>
-      <c r="T15">
+      <c r="W15">
         <v>4.57443915703603</v>
       </c>
-      <c r="U15">
+      <c r="X15">
         <v>1.261669953977646</v>
       </c>
-      <c r="V15">
+      <c r="Y15">
         <v>2.525793650793651</v>
       </c>
-      <c r="W15">
+      <c r="Z15">
         <v>0.4862565445026178</v>
       </c>
-      <c r="X15">
+      <c r="AA15">
         <v>50.79712041884817</v>
       </c>
-      <c r="Y15">
+      <c r="AB15">
         <v>0.8605108055009824</v>
       </c>
-      <c r="Z15">
+      <c r="AC15">
         <v>5.078688524590164</v>
       </c>
-      <c r="AA15">
+      <c r="AD15">
         <v>5.185888738127544</v>
+      </c>
+      <c r="AE15">
+        <v>7.761341222879684</v>
       </c>
     </row>
     <row r="16">
@@ -1721,79 +1909,91 @@
         </is>
       </c>
       <c r="C16">
+        <v>0.9791318864774624</v>
+      </c>
+      <c r="D16">
+        <v>0.7034120734908137</v>
+      </c>
+      <c r="E16">
         <v>0.5724258289703316</v>
       </c>
-      <c r="D16">
+      <c r="F16">
+        <v>0.8460877042132416</v>
+      </c>
+      <c r="G16">
         <v>4.440203562340967</v>
       </c>
-      <c r="E16">
+      <c r="H16">
         <v>3.97319932998325</v>
       </c>
-      <c r="F16">
+      <c r="I16">
         <v>1.917922948073702</v>
       </c>
-      <c r="G16">
+      <c r="J16">
         <v>2.335299073294018</v>
       </c>
-      <c r="H16">
+      <c r="K16">
         <v>2.304128053917439</v>
       </c>
-      <c r="I16">
+      <c r="L16">
         <v>3.704604691572546</v>
       </c>
-      <c r="J16">
+      <c r="M16">
         <v>3.467009425878321</v>
       </c>
-      <c r="K16">
+      <c r="N16">
         <v>2.550126368997473</v>
       </c>
-      <c r="L16">
+      <c r="O16">
         <v>4.367932489451476</v>
       </c>
-      <c r="M16">
+      <c r="P16">
         <v>3.994884910485934</v>
       </c>
-      <c r="N16">
+      <c r="Q16">
         <v>2.428087986463621</v>
       </c>
-      <c r="O16">
+      <c r="R16">
         <v>3.358278765201122</v>
       </c>
-      <c r="P16">
+      <c r="S16">
         <v>1.870401337792642</v>
       </c>
-      <c r="Q16">
+      <c r="T16">
         <v>3.295397489539749</v>
       </c>
-      <c r="R16">
+      <c r="U16">
         <v>2.176569037656904</v>
       </c>
-      <c r="S16">
+      <c r="V16">
         <v>2.079324894514768</v>
       </c>
-      <c r="T16">
+      <c r="W16">
         <v>3.059574468085106</v>
       </c>
-      <c r="U16">
+      <c r="X16">
         <v>2.415126050420168</v>
       </c>
-      <c r="V16">
+      <c r="Y16">
         <v>3.655668358714044</v>
       </c>
-      <c r="W16">
+      <c r="Z16">
         <v>0.4775</v>
       </c>
-      <c r="X16">
+      <c r="AA16">
         <v>39.48833333333334</v>
       </c>
-      <c r="Y16">
+      <c r="AB16">
         <v>0.99</v>
       </c>
-      <c r="Z16">
+      <c r="AC16">
         <v>4.214703425229741</v>
       </c>
-      <c r="AA16">
+      <c r="AD16">
         <v>4.759663865546218</v>
+      </c>
+      <c r="AE16">
+        <v>8.107718405428329</v>
       </c>
     </row>
     <row r="17">
@@ -1807,68 +2007,77 @@
           <t>Egypt</t>
         </is>
       </c>
-      <c r="C17">
+      <c r="D17">
+        <v>0.9247594050743657</v>
+      </c>
+      <c r="E17">
         <v>0.9983319432860718</v>
       </c>
-      <c r="D17">
+      <c r="F17">
+        <v>0.9974979149291076</v>
+      </c>
+      <c r="G17">
         <v>1.78915135608049</v>
       </c>
-      <c r="E17">
+      <c r="H17">
         <v>1.592592592592593</v>
       </c>
-      <c r="F17">
+      <c r="I17">
         <v>1.066108786610879</v>
       </c>
-      <c r="G17">
+      <c r="J17">
         <v>1.537351443123939</v>
       </c>
-      <c r="H17">
+      <c r="K17">
         <v>1.177703269069573</v>
       </c>
-      <c r="K17">
+      <c r="N17">
         <v>2.061603375527426</v>
       </c>
-      <c r="L17">
+      <c r="O17">
         <v>4.984886649874055</v>
       </c>
-      <c r="N17">
+      <c r="Q17">
         <v>1.115481171548117</v>
       </c>
-      <c r="O17">
+      <c r="R17">
         <v>1.5730110775428</v>
       </c>
-      <c r="P17">
+      <c r="S17">
         <v>2.550797649034425</v>
       </c>
-      <c r="Q17">
+      <c r="T17">
         <v>3.874476987447699</v>
       </c>
-      <c r="R17">
+      <c r="U17">
         <v>1.508389261744966</v>
       </c>
-      <c r="S17">
+      <c r="V17">
         <v>1.09419014084507</v>
       </c>
-      <c r="U17">
+      <c r="X17">
         <v>1.115068493150685</v>
       </c>
-      <c r="V17">
+      <c r="Y17">
         <v>6.63855421686747</v>
       </c>
-      <c r="W17">
+      <c r="Z17">
         <v>0.5175</v>
       </c>
-      <c r="X17">
+      <c r="AA17">
         <v>39.69916666666666</v>
       </c>
-      <c r="Y17">
+      <c r="AB17">
         <v>0.9991666666666666</v>
       </c>
-      <c r="Z17">
+      <c r="AC17">
         <v>3.5975</v>
       </c>
-      <c r="AA17">
+      <c r="AD17">
         <v>4.991921005385996</v>
+      </c>
+      <c r="AE17">
+        <v>3.9075</v>
       </c>
     </row>
     <row r="18">
@@ -1883,79 +2092,91 @@
         </is>
       </c>
       <c r="C18">
+        <v>0.9991869918699187</v>
+      </c>
+      <c r="D18">
+        <v>0.8338815789473685</v>
+      </c>
+      <c r="E18">
         <v>0.8876127973748975</v>
       </c>
-      <c r="D18">
+      <c r="F18">
+        <v>0.9770679770679771</v>
+      </c>
+      <c r="G18">
         <v>1.628571428571429</v>
       </c>
-      <c r="E18">
+      <c r="H18">
         <v>2.019607843137255</v>
       </c>
-      <c r="F18">
+      <c r="I18">
         <v>1.472312703583062</v>
       </c>
-      <c r="G18">
+      <c r="J18">
         <v>1.546502057613169</v>
       </c>
-      <c r="H18">
+      <c r="K18">
         <v>1.488562091503268</v>
       </c>
-      <c r="I18">
+      <c r="L18">
         <v>1.640758293838863</v>
       </c>
-      <c r="J18">
+      <c r="M18">
         <v>1.7002457002457</v>
       </c>
-      <c r="K18">
+      <c r="N18">
         <v>1.676734693877551</v>
       </c>
-      <c r="L18">
+      <c r="O18">
         <v>2.590872045639772</v>
       </c>
-      <c r="M18">
+      <c r="P18">
         <v>1.911237785016287</v>
       </c>
-      <c r="N18">
+      <c r="Q18">
         <v>1.466992665036675</v>
       </c>
-      <c r="O18">
+      <c r="R18">
         <v>1.713000817661488</v>
       </c>
-      <c r="P18">
+      <c r="S18">
         <v>1.71638141809291</v>
       </c>
-      <c r="Q18">
+      <c r="T18">
         <v>2.929095354523227</v>
       </c>
-      <c r="R18">
+      <c r="U18">
         <v>1.500814332247557</v>
       </c>
-      <c r="S18">
+      <c r="V18">
         <v>1.502852485737571</v>
       </c>
-      <c r="T18">
+      <c r="W18">
         <v>1.521986970684039</v>
       </c>
-      <c r="U18">
+      <c r="X18">
         <v>1.581699346405229</v>
       </c>
-      <c r="V18">
+      <c r="Y18">
         <v>2.13121434392828</v>
       </c>
-      <c r="W18">
+      <c r="Z18">
         <v>0.5056910569105691</v>
       </c>
-      <c r="X18">
+      <c r="AA18">
         <v>31.92682926829268</v>
       </c>
-      <c r="Y18">
+      <c r="AB18">
         <v>0.9983726606997559</v>
       </c>
-      <c r="Z18">
+      <c r="AC18">
         <v>3.024509803921569</v>
       </c>
-      <c r="AA18">
+      <c r="AD18">
         <v>4.381107491856677</v>
+      </c>
+      <c r="AE18">
+        <v>5.5</v>
       </c>
     </row>
     <row r="19">
@@ -1970,76 +2191,88 @@
         </is>
       </c>
       <c r="C19">
+        <v>0.4931891025641026</v>
+      </c>
+      <c r="D19">
+        <v>0.4720647773279352</v>
+      </c>
+      <c r="E19">
         <v>0.258746948738812</v>
       </c>
-      <c r="D19">
+      <c r="F19">
+        <v>0.414949494949495</v>
+      </c>
+      <c r="G19">
         <v>1.979449398991857</v>
       </c>
-      <c r="E19">
+      <c r="H19">
         <v>2.53046177726038</v>
       </c>
-      <c r="F19">
+      <c r="I19">
         <v>1.48338485316847</v>
       </c>
-      <c r="G19">
+      <c r="J19">
         <v>1.790634674922601</v>
       </c>
-      <c r="H19">
+      <c r="K19">
         <v>1.423833397608947</v>
       </c>
-      <c r="I19">
+      <c r="L19">
         <v>7.838620142743854</v>
       </c>
-      <c r="J19">
+      <c r="M19">
         <v>4.858557844690966</v>
       </c>
-      <c r="K19">
+      <c r="N19">
         <v>6.836142689141513</v>
       </c>
-      <c r="L19">
+      <c r="O19">
         <v>7.928487690504103</v>
       </c>
-      <c r="M19">
+      <c r="P19">
         <v>8.162162162162161</v>
       </c>
-      <c r="N19">
+      <c r="Q19">
         <v>4.823743922204214</v>
       </c>
-      <c r="O19">
+      <c r="R19">
         <v>6.742722265932337</v>
       </c>
-      <c r="Q19">
+      <c r="T19">
         <v>1.521604938271605</v>
       </c>
-      <c r="R19">
+      <c r="U19">
         <v>1.621715610510046</v>
       </c>
-      <c r="S19">
+      <c r="V19">
         <v>1.244590417310665</v>
       </c>
-      <c r="T19">
+      <c r="W19">
         <v>6.387109529458284</v>
       </c>
-      <c r="U19">
+      <c r="X19">
         <v>1.421317829457364</v>
       </c>
-      <c r="V19">
+      <c r="Y19">
         <v>4.447100313479623</v>
       </c>
-      <c r="W19">
+      <c r="Z19">
         <v>0.4289596273291926</v>
       </c>
-      <c r="X19">
+      <c r="AA19">
         <v>51.81692993114621</v>
       </c>
-      <c r="Y19">
+      <c r="AB19">
         <v>0.8614130434782609</v>
       </c>
-      <c r="Z19">
+      <c r="AC19">
         <v>5.25010250102501</v>
       </c>
-      <c r="AA19">
+      <c r="AD19">
         <v>5.652475705691809</v>
+      </c>
+      <c r="AE19">
+        <v>7.30738838403793</v>
       </c>
     </row>
     <row r="20">
@@ -2054,79 +2287,91 @@
         </is>
       </c>
       <c r="C20">
+        <v>0.9360068259385665</v>
+      </c>
+      <c r="D20">
+        <v>0.5378071833648393</v>
+      </c>
+      <c r="E20">
         <v>0.4938154138915319</v>
       </c>
-      <c r="D20">
+      <c r="F20">
+        <v>0.5118259224219489</v>
+      </c>
+      <c r="G20">
         <v>1.586756077116513</v>
       </c>
-      <c r="E20">
+      <c r="H20">
         <v>2.388471177944862</v>
       </c>
-      <c r="F20">
+      <c r="I20">
         <v>1.130543933054393</v>
       </c>
-      <c r="G20">
+      <c r="J20">
         <v>1.678960603520536</v>
       </c>
-      <c r="H20">
+      <c r="K20">
         <v>1.37751677852349</v>
       </c>
-      <c r="I20">
+      <c r="L20">
         <v>4.764909248055315</v>
       </c>
-      <c r="J20">
+      <c r="M20">
         <v>3.981244671781756</v>
       </c>
-      <c r="K20">
+      <c r="N20">
         <v>4.575063613231552</v>
       </c>
-      <c r="L20">
+      <c r="O20">
         <v>6.866161616161616</v>
       </c>
-      <c r="M20">
+      <c r="P20">
         <v>7.41687979539642</v>
       </c>
-      <c r="N20">
+      <c r="Q20">
         <v>1.885008517887564</v>
       </c>
-      <c r="O20">
+      <c r="R20">
         <v>3.107047279214987</v>
       </c>
-      <c r="P20">
+      <c r="S20">
         <v>1.131996658312448</v>
       </c>
-      <c r="Q20">
+      <c r="T20">
         <v>1.221202003338898</v>
       </c>
-      <c r="R20">
+      <c r="U20">
         <v>1.190954773869347</v>
       </c>
-      <c r="S20">
+      <c r="V20">
         <v>1.142737195633921</v>
       </c>
-      <c r="T20">
+      <c r="W20">
         <v>5.346973572037511</v>
       </c>
-      <c r="U20">
+      <c r="X20">
         <v>1.451694915254237</v>
       </c>
-      <c r="V20">
+      <c r="Y20">
         <v>2.433450087565674</v>
       </c>
-      <c r="W20">
+      <c r="Z20">
         <v>0.4691666666666667</v>
       </c>
-      <c r="X20">
+      <c r="AA20">
         <v>50.92916666666667</v>
       </c>
-      <c r="Y20">
+      <c r="AB20">
         <v>0.8941666666666667</v>
       </c>
-      <c r="Z20">
+      <c r="AC20">
         <v>4.2325</v>
       </c>
-      <c r="AA20">
+      <c r="AD20">
         <v>4.543006081668115</v>
+      </c>
+      <c r="AE20">
+        <v>6.052276559865093</v>
       </c>
     </row>
     <row r="21">
@@ -2141,79 +2386,91 @@
         </is>
       </c>
       <c r="C21">
+        <v>0.9641985353946297</v>
+      </c>
+      <c r="D21">
+        <v>0.8071602929210741</v>
+      </c>
+      <c r="E21">
         <v>0.7933279088689992</v>
       </c>
-      <c r="D21">
+      <c r="F21">
+        <v>0.8795768917819365</v>
+      </c>
+      <c r="G21">
         <v>4.142384105960265</v>
       </c>
-      <c r="E21">
+      <c r="H21">
         <v>3.698175787728026</v>
       </c>
-      <c r="F21">
+      <c r="I21">
         <v>2.235294117647059</v>
       </c>
-      <c r="G21">
+      <c r="J21">
         <v>2.384808013355593</v>
       </c>
-      <c r="H21">
+      <c r="K21">
         <v>2.30865224625624</v>
       </c>
-      <c r="I21">
+      <c r="L21">
         <v>3.730290456431535</v>
       </c>
-      <c r="J21">
+      <c r="M21">
         <v>3.396825396825397</v>
       </c>
-      <c r="K21">
+      <c r="N21">
         <v>2.959336099585062</v>
       </c>
-      <c r="L21">
+      <c r="O21">
         <v>5.00413564929694</v>
       </c>
-      <c r="M21">
+      <c r="P21">
         <v>4.003319502074689</v>
       </c>
-      <c r="N21">
+      <c r="Q21">
         <v>2.603491271820449</v>
       </c>
-      <c r="O21">
+      <c r="R21">
         <v>3.727272727272727</v>
       </c>
-      <c r="P21">
+      <c r="S21">
         <v>1.87986743993372</v>
       </c>
-      <c r="Q21">
+      <c r="T21">
         <v>4.065</v>
       </c>
-      <c r="R21">
+      <c r="U21">
         <v>2.210963455149502</v>
       </c>
-      <c r="S21">
+      <c r="V21">
         <v>2.08955223880597</v>
       </c>
-      <c r="T21">
+      <c r="W21">
         <v>3.513647642679901</v>
       </c>
-      <c r="U21">
+      <c r="X21">
         <v>2.069941715237302</v>
       </c>
-      <c r="V21">
+      <c r="Y21">
         <v>5.092868988391376</v>
       </c>
-      <c r="W21">
+      <c r="Z21">
         <v>0.4703010577705452</v>
       </c>
-      <c r="X21">
+      <c r="AA21">
         <v>33.49877949552481</v>
       </c>
-      <c r="Y21">
+      <c r="AB21">
         <v>0.9926108374384236</v>
       </c>
-      <c r="Z21">
+      <c r="AC21">
         <v>5.085376162299239</v>
       </c>
-      <c r="AA21">
+      <c r="AD21">
         <v>5.959302325581396</v>
+      </c>
+      <c r="AE21">
+        <v>7.637633525061627</v>
       </c>
     </row>
     <row r="22">
@@ -2228,79 +2485,91 @@
         </is>
       </c>
       <c r="C22">
+        <v>0.544260700389105</v>
+      </c>
+      <c r="D22">
+        <v>0.4261335933690882</v>
+      </c>
+      <c r="E22">
         <v>0.4708761625061185</v>
       </c>
-      <c r="D22">
+      <c r="F22">
+        <v>0.50465914664051</v>
+      </c>
+      <c r="G22">
         <v>3.063376874697629</v>
       </c>
-      <c r="E22">
+      <c r="H22">
         <v>2.474420849420849</v>
       </c>
-      <c r="F22">
+      <c r="I22">
         <v>2.024590163934426</v>
       </c>
-      <c r="G22">
+      <c r="J22">
         <v>2.229357798165138</v>
       </c>
-      <c r="H22">
+      <c r="K22">
         <v>2.010140028971511</v>
       </c>
-      <c r="I22">
+      <c r="L22">
         <v>5.129142300194932</v>
       </c>
-      <c r="J22">
+      <c r="M22">
         <v>3.479398933591856</v>
       </c>
-      <c r="K22">
+      <c r="N22">
         <v>3.920950533462658</v>
       </c>
-      <c r="L22">
+      <c r="O22">
         <v>5.372758119243819</v>
       </c>
-      <c r="M22">
+      <c r="P22">
         <v>5.306013579049466</v>
       </c>
-      <c r="N22">
+      <c r="Q22">
         <v>3.384019370460048</v>
       </c>
-      <c r="O22">
+      <c r="R22">
         <v>5.990799031476998</v>
       </c>
-      <c r="P22">
+      <c r="S22">
         <v>2.064158224794983</v>
       </c>
-      <c r="Q22">
+      <c r="T22">
         <v>3.755673587638822</v>
       </c>
-      <c r="R22">
+      <c r="U22">
         <v>2.30327868852459</v>
       </c>
-      <c r="S22">
+      <c r="V22">
         <v>2.017943743937924</v>
       </c>
-      <c r="T22">
+      <c r="W22">
         <v>3.304895782840524</v>
       </c>
-      <c r="U22">
+      <c r="X22">
         <v>2.493946731234867</v>
       </c>
-      <c r="V22">
+      <c r="Y22">
         <v>4.478197674418604</v>
       </c>
-      <c r="W22">
+      <c r="Z22">
         <v>0.4587951807228915</v>
       </c>
-      <c r="X22">
+      <c r="AA22">
         <v>47.21963070942662</v>
       </c>
-      <c r="Y22">
+      <c r="AB22">
         <v>0.7391513982642237</v>
       </c>
-      <c r="Z22">
+      <c r="AC22">
         <v>5.017366136034732</v>
       </c>
-      <c r="AA22">
+      <c r="AD22">
         <v>4.792553191489362</v>
+      </c>
+      <c r="AE22">
+        <v>7.959942084942085</v>
       </c>
     </row>
     <row r="23">
@@ -2315,79 +2584,91 @@
         </is>
       </c>
       <c r="C23">
+        <v>0.9753047827446076</v>
+      </c>
+      <c r="D23">
+        <v>0.7517974366989685</v>
+      </c>
+      <c r="E23">
         <v>0.7139731165989371</v>
       </c>
-      <c r="D23">
+      <c r="F23">
+        <v>0.8705845576742732</v>
+      </c>
+      <c r="G23">
         <v>3.28023876845743</v>
       </c>
-      <c r="E23">
+      <c r="H23">
         <v>2.737864077669903</v>
       </c>
-      <c r="F23">
+      <c r="I23">
         <v>1.556007509386733</v>
       </c>
-      <c r="G23">
+      <c r="J23">
         <v>2.501409332915753</v>
       </c>
-      <c r="H23">
+      <c r="K23">
         <v>1.931326434619003</v>
       </c>
-      <c r="I23">
+      <c r="L23">
         <v>1.610222640326121</v>
       </c>
-      <c r="J23">
+      <c r="M23">
         <v>1.56628016295832</v>
       </c>
-      <c r="K23">
+      <c r="N23">
         <v>1.576260569996868</v>
       </c>
-      <c r="L23">
+      <c r="O23">
         <v>2.690737833594977</v>
       </c>
-      <c r="M23">
+      <c r="P23">
         <v>1.642365456821026</v>
       </c>
-      <c r="N23">
+      <c r="Q23">
         <v>1.484507042253521</v>
       </c>
-      <c r="O23">
+      <c r="R23">
         <v>2.190655377861399</v>
       </c>
-      <c r="P23">
+      <c r="S23">
         <v>1.668648310387985</v>
       </c>
-      <c r="Q23">
+      <c r="T23">
         <v>2.436619718309859</v>
       </c>
-      <c r="R23">
+      <c r="U23">
         <v>1.863536776212833</v>
       </c>
-      <c r="S23">
+      <c r="V23">
         <v>1.725496375669713</v>
       </c>
-      <c r="T23">
+      <c r="W23">
         <v>1.520062695924765</v>
       </c>
-      <c r="U23">
+      <c r="X23">
         <v>1.782553729456384</v>
       </c>
-      <c r="V23">
+      <c r="Y23">
         <v>3.382111251580278</v>
       </c>
-      <c r="W23">
+      <c r="Z23">
         <v>0.451875</v>
       </c>
-      <c r="X23">
+      <c r="AA23">
         <v>40.0265625</v>
       </c>
-      <c r="Y23">
+      <c r="AB23">
         <v>0.9990625</v>
       </c>
-      <c r="Z23">
+      <c r="AC23">
         <v>3.256642700844014</v>
       </c>
-      <c r="AA23">
+      <c r="AD23">
         <v>4.227301189730746</v>
+      </c>
+      <c r="AE23">
+        <v>4.38125</v>
       </c>
     </row>
     <row r="24">
@@ -2402,79 +2683,91 @@
         </is>
       </c>
       <c r="C24">
+        <v>0.9461077844311377</v>
+      </c>
+      <c r="D24">
+        <v>0.4748102139406487</v>
+      </c>
+      <c r="E24">
         <v>0.5748626373626373</v>
       </c>
-      <c r="D24">
+      <c r="F24">
+        <v>0.6150684931506849</v>
+      </c>
+      <c r="G24">
         <v>2.72259236826166</v>
       </c>
-      <c r="E24">
+      <c r="H24">
         <v>2.313353115727003</v>
       </c>
-      <c r="F24">
+      <c r="I24">
         <v>1.887700534759358</v>
       </c>
-      <c r="G24">
+      <c r="J24">
         <v>2.044296116504854</v>
       </c>
-      <c r="H24">
+      <c r="K24">
         <v>1.926391382405745</v>
       </c>
-      <c r="I24">
+      <c r="L24">
         <v>2.742897727272727</v>
       </c>
-      <c r="J24">
+      <c r="M24">
         <v>2.166040100250627</v>
       </c>
-      <c r="K24">
+      <c r="N24">
         <v>2.784818067754078</v>
       </c>
-      <c r="L24">
+      <c r="O24">
         <v>3.102362204724409</v>
       </c>
-      <c r="M24">
+      <c r="P24">
         <v>2.27819083023544</v>
       </c>
-      <c r="N24">
+      <c r="Q24">
         <v>1.906474820143885</v>
       </c>
-      <c r="O24">
+      <c r="R24">
         <v>2.855781448538755</v>
       </c>
-      <c r="P24">
+      <c r="S24">
         <v>2.048838594401429</v>
       </c>
-      <c r="Q24">
+      <c r="T24">
         <v>3.606761565836299</v>
       </c>
-      <c r="R24">
+      <c r="U24">
         <v>1.929383602633154</v>
       </c>
-      <c r="S24">
+      <c r="V24">
         <v>1.892077354959451</v>
       </c>
-      <c r="T24">
+      <c r="W24">
         <v>1.97717184527584</v>
       </c>
-      <c r="U24">
+      <c r="X24">
         <v>1.833333333333333</v>
       </c>
-      <c r="V24">
+      <c r="Y24">
         <v>3.852923076923077</v>
       </c>
-      <c r="W24">
+      <c r="Z24">
         <v>0.566193853427896</v>
       </c>
-      <c r="X24">
+      <c r="AA24">
         <v>35.80378250591016</v>
       </c>
-      <c r="Y24">
+      <c r="AB24">
         <v>1</v>
       </c>
-      <c r="Z24">
+      <c r="AC24">
         <v>4.202486678507993</v>
       </c>
-      <c r="AA24">
+      <c r="AD24">
         <v>5.43963963963964</v>
+      </c>
+      <c r="AE24">
+        <v>2.982227488151659</v>
       </c>
     </row>
     <row r="25">
@@ -2489,73 +2782,85 @@
         </is>
       </c>
       <c r="C25">
+        <v>0.9933155080213903</v>
+      </c>
+      <c r="D25">
+        <v>0.9212121212121213</v>
+      </c>
+      <c r="E25">
         <v>0.8892617449664429</v>
       </c>
-      <c r="D25">
+      <c r="F25">
+        <v>0.9274193548387096</v>
+      </c>
+      <c r="G25">
         <v>3.598366235534377</v>
       </c>
-      <c r="E25">
+      <c r="H25">
         <v>2.714093959731544</v>
       </c>
-      <c r="F25">
+      <c r="I25">
         <v>1.459893048128342</v>
       </c>
-      <c r="G25">
+      <c r="J25">
         <v>2.332437877770316</v>
       </c>
-      <c r="H25">
+      <c r="K25">
         <v>1.496662216288384</v>
       </c>
-      <c r="I25">
+      <c r="L25">
         <v>1.602013422818792</v>
       </c>
-      <c r="K25">
+      <c r="N25">
         <v>2.729585006693441</v>
       </c>
-      <c r="L25">
+      <c r="O25">
         <v>3.652815013404826</v>
       </c>
-      <c r="M25">
+      <c r="P25">
         <v>2.244652406417112</v>
       </c>
-      <c r="N25">
+      <c r="Q25">
         <v>1.485981308411215</v>
       </c>
-      <c r="O25">
+      <c r="R25">
         <v>3.074576271186441</v>
       </c>
-      <c r="P25">
+      <c r="S25">
         <v>1.496997998665777</v>
       </c>
-      <c r="Q25">
+      <c r="T25">
         <v>2.205607476635514</v>
       </c>
-      <c r="R25">
+      <c r="U25">
         <v>1.807615230460922</v>
       </c>
-      <c r="S25">
+      <c r="V25">
         <v>1.647058823529412</v>
       </c>
-      <c r="U25">
+      <c r="X25">
         <v>1.974025974025974</v>
       </c>
-      <c r="V25">
+      <c r="Y25">
         <v>6.861859838274933</v>
       </c>
-      <c r="W25">
+      <c r="Z25">
         <v>0.5110073382254836</v>
       </c>
-      <c r="X25">
+      <c r="AA25">
         <v>39.47698465643762</v>
       </c>
-      <c r="Y25">
+      <c r="AB25">
         <v>0.9973315543695798</v>
       </c>
-      <c r="Z25">
+      <c r="AC25">
         <v>4.991298527443106</v>
       </c>
-      <c r="AA25">
+      <c r="AD25">
         <v>3.915483434753212</v>
+      </c>
+      <c r="AE25">
+        <v>4.106009453072248</v>
       </c>
     </row>
     <row r="26">
@@ -2569,68 +2874,71 @@
           <t>Iraq</t>
         </is>
       </c>
-      <c r="D26">
+      <c r="G26">
         <v>3.565</v>
       </c>
-      <c r="E26">
+      <c r="H26">
         <v>2.986666666666667</v>
       </c>
-      <c r="F26">
+      <c r="I26">
         <v>2.415833333333333</v>
       </c>
-      <c r="G26">
+      <c r="J26">
         <v>2.735</v>
       </c>
-      <c r="H26">
+      <c r="K26">
         <v>2.6475</v>
       </c>
-      <c r="I26">
+      <c r="L26">
         <v>2.295808383233533</v>
       </c>
-      <c r="K26">
+      <c r="N26">
         <v>2.781666666666667</v>
       </c>
-      <c r="L26">
+      <c r="O26">
         <v>3.771666666666667</v>
       </c>
-      <c r="N26">
+      <c r="Q26">
         <v>2.28</v>
       </c>
-      <c r="O26">
+      <c r="R26">
         <v>2.3975</v>
       </c>
-      <c r="P26">
+      <c r="S26">
         <v>2.615833333333333</v>
       </c>
-      <c r="Q26">
+      <c r="T26">
         <v>3.340833333333333</v>
       </c>
-      <c r="R26">
+      <c r="U26">
         <v>2.491666666666667</v>
       </c>
-      <c r="S26">
+      <c r="V26">
         <v>2.4625</v>
       </c>
-      <c r="U26">
+      <c r="X26">
         <v>2.651666666666667</v>
       </c>
-      <c r="V26">
+      <c r="Y26">
         <v>4.960833333333333</v>
       </c>
-      <c r="W26">
+      <c r="Z26">
         <v>0.5066666666666667</v>
       </c>
-      <c r="X26">
+      <c r="AA26">
         <v>36.6025</v>
       </c>
-      <c r="Y26">
+      <c r="AB26">
         <v>1</v>
       </c>
-      <c r="Z26">
+      <c r="AC26">
         <v>3.847953216374269</v>
       </c>
-      <c r="AA26">
+      <c r="AD26">
         <v>4.454166666666667</v>
+      </c>
+      <c r="AE26">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -2645,70 +2953,82 @@
         </is>
       </c>
       <c r="C27">
+        <v>0.9966694421315571</v>
+      </c>
+      <c r="D27">
+        <v>0.9261744966442953</v>
+      </c>
+      <c r="E27">
         <v>0.97</v>
       </c>
-      <c r="D27">
+      <c r="F27">
+        <v>0.9925062447960034</v>
+      </c>
+      <c r="G27">
         <v>2.994915254237288</v>
       </c>
-      <c r="F27">
+      <c r="I27">
         <v>1.375833333333333</v>
       </c>
-      <c r="G27">
+      <c r="J27">
         <v>2.105616093880972</v>
       </c>
-      <c r="H27">
+      <c r="K27">
         <v>1.443238731218698</v>
       </c>
-      <c r="I27">
+      <c r="L27">
         <v>1.271129707112971</v>
       </c>
-      <c r="K27">
+      <c r="N27">
         <v>1.913879598662207</v>
       </c>
-      <c r="L27">
+      <c r="O27">
         <v>3.808688387635756</v>
       </c>
-      <c r="M27">
+      <c r="P27">
         <v>1.253768844221105</v>
       </c>
-      <c r="N27">
+      <c r="Q27">
         <v>1.235</v>
       </c>
-      <c r="O27">
+      <c r="R27">
         <v>1.5</v>
       </c>
-      <c r="P27">
+      <c r="S27">
         <v>1.592839300582848</v>
       </c>
-      <c r="Q27">
+      <c r="T27">
         <v>2.548414023372287</v>
       </c>
-      <c r="R27">
+      <c r="U27">
         <v>1.409658617818485</v>
       </c>
-      <c r="S27">
+      <c r="V27">
         <v>1.276755852842809</v>
       </c>
-      <c r="U27">
+      <c r="X27">
         <v>1.303765690376569</v>
       </c>
-      <c r="V27">
+      <c r="Y27">
         <v>5.33585222502099</v>
       </c>
-      <c r="W27">
+      <c r="Z27">
         <v>0.5045719035743973</v>
       </c>
-      <c r="X27">
+      <c r="AA27">
         <v>43.3142144638404</v>
       </c>
-      <c r="Y27">
+      <c r="AB27">
         <v>0.8620116375727348</v>
       </c>
-      <c r="Z27">
+      <c r="AC27">
         <v>4.166527893422148</v>
       </c>
-      <c r="AA27">
+      <c r="AD27">
         <v>4.03765690376569</v>
+      </c>
+      <c r="AE27">
+        <v>3.950124688279302</v>
       </c>
     </row>
     <row r="28">
@@ -2723,79 +3043,91 @@
         </is>
       </c>
       <c r="C28">
+        <v>0.5479876160990712</v>
+      </c>
+      <c r="D28">
+        <v>0.4812362030905077</v>
+      </c>
+      <c r="E28">
         <v>0.2812858783008036</v>
       </c>
-      <c r="D28">
+      <c r="F28">
+        <v>0.3875706214689266</v>
+      </c>
+      <c r="G28">
         <v>1.763117283950617</v>
       </c>
-      <c r="E28">
+      <c r="H28">
         <v>1.323795180722892</v>
       </c>
-      <c r="F28">
+      <c r="I28">
         <v>1.106766917293233</v>
       </c>
-      <c r="G28">
+      <c r="J28">
         <v>1.257336343115124</v>
       </c>
-      <c r="H28">
+      <c r="K28">
         <v>1.387169811320755</v>
       </c>
-      <c r="I28">
+      <c r="L28">
         <v>6.710180623973727</v>
       </c>
-      <c r="J28">
+      <c r="M28">
         <v>1.976940814757879</v>
       </c>
-      <c r="K28">
+      <c r="N28">
         <v>4.87037037037037</v>
       </c>
-      <c r="L28">
+      <c r="O28">
         <v>6.802873104549082</v>
       </c>
-      <c r="M28">
+      <c r="P28">
         <v>6.873104549082202</v>
       </c>
-      <c r="N28">
+      <c r="Q28">
         <v>2.708466453674121</v>
       </c>
-      <c r="O28">
+      <c r="R28">
         <v>6.183508488278092</v>
       </c>
-      <c r="P28">
+      <c r="S28">
         <v>1.266365688487585</v>
       </c>
-      <c r="Q28">
+      <c r="T28">
         <v>1.300978179082017</v>
       </c>
-      <c r="R28">
+      <c r="U28">
         <v>1.306706857573474</v>
       </c>
-      <c r="S28">
+      <c r="V28">
         <v>1.20763358778626</v>
       </c>
-      <c r="T28">
+      <c r="W28">
         <v>2.666666666666667</v>
       </c>
-      <c r="U28">
+      <c r="X28">
         <v>1.386697602474865</v>
       </c>
-      <c r="V28">
+      <c r="Y28">
         <v>6.801646090534979</v>
       </c>
-      <c r="W28">
+      <c r="Z28">
         <v>0.4360679970436068</v>
       </c>
-      <c r="X28">
+      <c r="AA28">
         <v>54.78048780487805</v>
       </c>
-      <c r="Y28">
+      <c r="AB28">
         <v>0.9902840059790733</v>
       </c>
-      <c r="Z28">
+      <c r="AC28">
         <v>5.380703066566941</v>
       </c>
-      <c r="AA28">
+      <c r="AD28">
         <v>4.185892116182573</v>
+      </c>
+      <c r="AE28">
+        <v>6.626646010844307</v>
       </c>
     </row>
     <row r="29">
@@ -2810,79 +3142,91 @@
         </is>
       </c>
       <c r="C29">
+        <v>0.9438860971524288</v>
+      </c>
+      <c r="D29">
+        <v>0.6114769520225776</v>
+      </c>
+      <c r="E29">
         <v>0.5957446808510638</v>
       </c>
-      <c r="D29">
+      <c r="F29">
+        <v>0.6450676982591876</v>
+      </c>
+      <c r="G29">
         <v>3.402997502081599</v>
       </c>
-      <c r="E29">
+      <c r="H29">
         <v>4.280971659919028</v>
       </c>
-      <c r="F29">
+      <c r="I29">
         <v>2.192058346839546</v>
       </c>
-      <c r="G29">
+      <c r="J29">
         <v>2.946369636963696</v>
       </c>
-      <c r="H29">
+      <c r="K29">
         <v>2.244914564686737</v>
       </c>
-      <c r="I29">
+      <c r="L29">
         <v>2.220677671589922</v>
       </c>
-      <c r="J29">
+      <c r="M29">
         <v>2.478751084128361</v>
       </c>
-      <c r="K29">
+      <c r="N29">
         <v>3.507502206531333</v>
       </c>
-      <c r="L29">
+      <c r="O29">
         <v>4.711775043936731</v>
       </c>
-      <c r="M29">
+      <c r="P29">
         <v>4.538804638715432</v>
       </c>
-      <c r="N29">
+      <c r="Q29">
         <v>2.276408450704225</v>
       </c>
-      <c r="O29">
+      <c r="R29">
         <v>3.761248852157943</v>
       </c>
-      <c r="P29">
+      <c r="S29">
         <v>2.380912162162162</v>
       </c>
-      <c r="Q29">
+      <c r="T29">
         <v>2.37344398340249</v>
       </c>
-      <c r="R29">
+      <c r="U29">
         <v>2.046511627906977</v>
       </c>
-      <c r="S29">
+      <c r="V29">
         <v>1.82864238410596</v>
       </c>
-      <c r="T29">
+      <c r="W29">
         <v>3.061418685121107</v>
       </c>
-      <c r="U29">
+      <c r="X29">
         <v>2.01510067114094</v>
       </c>
-      <c r="V29">
+      <c r="Y29">
         <v>3.484320557491289</v>
       </c>
-      <c r="W29">
+      <c r="Z29">
         <v>0.4521943573667712</v>
       </c>
-      <c r="X29">
+      <c r="AA29">
         <v>41.24529780564264</v>
       </c>
-      <c r="Y29">
+      <c r="AB29">
         <v>0.9528672427336999</v>
       </c>
-      <c r="Z29">
+      <c r="AC29">
         <v>5.792176039119805</v>
       </c>
-      <c r="AA29">
+      <c r="AD29">
         <v>5.529698942229455</v>
+      </c>
+      <c r="AE29">
+        <v>4.829508196721312</v>
       </c>
     </row>
     <row r="30">
@@ -2897,79 +3241,91 @@
         </is>
       </c>
       <c r="C30">
+        <v>0.9968304278922345</v>
+      </c>
+      <c r="D30">
+        <v>0.8537774167343624</v>
+      </c>
+      <c r="E30">
         <v>0.6636288318144159</v>
       </c>
-      <c r="D30">
+      <c r="F30">
+        <v>0.9293257514216084</v>
+      </c>
+      <c r="G30">
         <v>3.316343042071197</v>
       </c>
-      <c r="E30">
+      <c r="H30">
         <v>3.583197389885807</v>
       </c>
-      <c r="F30">
+      <c r="I30">
         <v>2.917551020408163</v>
       </c>
-      <c r="G30">
+      <c r="J30">
         <v>3.545085296506905</v>
       </c>
-      <c r="H30">
+      <c r="K30">
         <v>3.190746753246753</v>
       </c>
-      <c r="I30">
+      <c r="L30">
         <v>3.006584362139918</v>
       </c>
-      <c r="J30">
+      <c r="M30">
         <v>3.064860426929393</v>
       </c>
-      <c r="K30">
+      <c r="N30">
         <v>3.657679738562091</v>
       </c>
-      <c r="L30">
+      <c r="O30">
         <v>4.737058340180773</v>
       </c>
-      <c r="M30">
+      <c r="P30">
         <v>4.115918367346938</v>
       </c>
-      <c r="N30">
+      <c r="Q30">
         <v>2.990107172300082</v>
       </c>
-      <c r="O30">
+      <c r="R30">
         <v>4.063410454155956</v>
       </c>
-      <c r="P30">
+      <c r="S30">
         <v>3.365415986949429</v>
       </c>
-      <c r="Q30">
+      <c r="T30">
         <v>4.70268074735987</v>
       </c>
-      <c r="R30">
+      <c r="U30">
         <v>3.008203445447088</v>
       </c>
-      <c r="S30">
+      <c r="V30">
         <v>2.88</v>
       </c>
-      <c r="T30">
+      <c r="W30">
         <v>3.526487367563162</v>
       </c>
-      <c r="U30">
+      <c r="X30">
         <v>2.983646770237122</v>
       </c>
-      <c r="V30">
+      <c r="Y30">
         <v>3.651490066225166</v>
       </c>
-      <c r="W30">
+      <c r="Z30">
         <v>0.505957108816521</v>
       </c>
-      <c r="X30">
+      <c r="AA30">
         <v>30.74027005559968</v>
       </c>
-      <c r="Y30">
+      <c r="AB30">
         <v>0.9960443037974683</v>
       </c>
-      <c r="Z30">
+      <c r="AC30">
         <v>4.31031746031746</v>
       </c>
-      <c r="AA30">
+      <c r="AD30">
         <v>4.595813204508857</v>
+      </c>
+      <c r="AE30">
+        <v>6.821656050955414</v>
       </c>
     </row>
     <row r="31">
@@ -2983,77 +3339,83 @@
           <t>Kyrgyzstan</t>
         </is>
       </c>
-      <c r="D31">
+      <c r="C31">
+        <v>0.9715956558061821</v>
+      </c>
+      <c r="G31">
         <v>3.063829787234043</v>
       </c>
-      <c r="E31">
+      <c r="H31">
         <v>2.733506944444445</v>
       </c>
-      <c r="F31">
+      <c r="I31">
         <v>1.707797772065124</v>
       </c>
-      <c r="G31">
+      <c r="J31">
         <v>2.202749140893471</v>
       </c>
-      <c r="H31">
+      <c r="K31">
         <v>1.745283018867924</v>
       </c>
-      <c r="I31">
+      <c r="L31">
         <v>1.482394366197183</v>
       </c>
-      <c r="J31">
+      <c r="M31">
         <v>1.490845684394071</v>
       </c>
-      <c r="K31">
+      <c r="N31">
         <v>1.805217391304348</v>
       </c>
-      <c r="L31">
+      <c r="O31">
         <v>2.256476683937824</v>
       </c>
-      <c r="M31">
+      <c r="P31">
         <v>2.001748251748252</v>
       </c>
-      <c r="N31">
+      <c r="Q31">
         <v>1.419047619047619</v>
       </c>
-      <c r="O31">
+      <c r="R31">
         <v>1.968225948808473</v>
       </c>
-      <c r="P31">
+      <c r="S31">
         <v>1.87510766580534</v>
       </c>
-      <c r="Q31">
+      <c r="T31">
         <v>2.200343938091144</v>
       </c>
-      <c r="R31">
+      <c r="U31">
         <v>1.602067183462532</v>
       </c>
-      <c r="S31">
+      <c r="V31">
         <v>1.481707317073171</v>
       </c>
-      <c r="T31">
+      <c r="W31">
         <v>1.662587412587412</v>
       </c>
-      <c r="U31">
+      <c r="X31">
         <v>1.533158813263525</v>
       </c>
-      <c r="V31">
+      <c r="Y31">
         <v>2.147110332749562</v>
       </c>
-      <c r="W31">
+      <c r="Z31">
         <v>0.3808333333333334</v>
       </c>
-      <c r="X31">
+      <c r="AA31">
         <v>41.3025</v>
       </c>
-      <c r="Y31">
+      <c r="AB31">
         <v>0.9441201000834029</v>
       </c>
-      <c r="Z31">
+      <c r="AC31">
         <v>5.429524603836531</v>
       </c>
-      <c r="AA31">
+      <c r="AD31">
         <v>5.052542372881356</v>
+      </c>
+      <c r="AE31">
+        <v>4.426767676767676</v>
       </c>
     </row>
     <row r="32">
@@ -3068,79 +3430,91 @@
         </is>
       </c>
       <c r="C32">
+        <v>0.406425702811245</v>
+      </c>
+      <c r="D32">
+        <v>0.3373493975903614</v>
+      </c>
+      <c r="E32">
         <v>0.3156626506024096</v>
       </c>
-      <c r="D32">
+      <c r="F32">
+        <v>0.3220883534136546</v>
+      </c>
+      <c r="G32">
         <v>3.235341365461847</v>
       </c>
-      <c r="E32">
+      <c r="H32">
         <v>2.970281124497992</v>
       </c>
-      <c r="F32">
+      <c r="I32">
         <v>2.214457831325301</v>
       </c>
-      <c r="G32">
+      <c r="J32">
         <v>2.223293172690763</v>
       </c>
-      <c r="H32">
+      <c r="K32">
         <v>2.219277108433735</v>
       </c>
-      <c r="I32">
+      <c r="L32">
         <v>3.232128514056225</v>
       </c>
-      <c r="J32">
+      <c r="M32">
         <v>2.65140562248996</v>
       </c>
-      <c r="K32">
+      <c r="N32">
         <v>3.911646586345381</v>
       </c>
-      <c r="L32">
+      <c r="O32">
         <v>5.260240963855422</v>
       </c>
-      <c r="M32">
+      <c r="P32">
         <v>4.779919678714859</v>
       </c>
-      <c r="N32">
+      <c r="Q32">
         <v>2.682730923694779</v>
       </c>
-      <c r="O32">
+      <c r="R32">
         <v>4.434538152610441</v>
       </c>
-      <c r="P32">
+      <c r="S32">
         <v>2.014457831325301</v>
       </c>
-      <c r="Q32">
+      <c r="T32">
         <v>2.398393574297189</v>
       </c>
-      <c r="R32">
+      <c r="U32">
         <v>2.16144578313253</v>
       </c>
-      <c r="S32">
+      <c r="V32">
         <v>2.255421686746988</v>
       </c>
-      <c r="T32">
+      <c r="W32">
         <v>2.514056224899599</v>
       </c>
-      <c r="U32">
+      <c r="X32">
         <v>2.442570281124498</v>
       </c>
-      <c r="V32">
+      <c r="Y32">
         <v>4.339759036144578</v>
       </c>
-      <c r="W32">
+      <c r="Z32">
         <v>0.4875502008032129</v>
       </c>
-      <c r="X32">
+      <c r="AA32">
         <v>45.62971887550201</v>
       </c>
-      <c r="Y32">
+      <c r="AB32">
         <v>0.989558232931727</v>
       </c>
-      <c r="Z32">
+      <c r="AC32">
         <v>5.118072289156626</v>
       </c>
-      <c r="AA32">
+      <c r="AD32">
         <v>4.840160642570281</v>
+      </c>
+      <c r="AE32">
+        <v>7.636947791164658</v>
       </c>
     </row>
     <row r="33">
@@ -3155,73 +3529,85 @@
         </is>
       </c>
       <c r="C33">
+        <v>0.9958333333333333</v>
+      </c>
+      <c r="D33">
+        <v>0.8619528619528619</v>
+      </c>
+      <c r="E33">
         <v>0.8583333333333333</v>
       </c>
-      <c r="D33">
+      <c r="F33">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="G33">
         <v>3.401023890784983</v>
       </c>
-      <c r="F33">
+      <c r="I33">
         <v>1.971356360572873</v>
       </c>
-      <c r="G33">
+      <c r="J33">
         <v>2.56140350877193</v>
       </c>
-      <c r="H33">
+      <c r="K33">
         <v>2.644166666666667</v>
       </c>
-      <c r="I33">
+      <c r="L33">
         <v>2.338926174496644</v>
       </c>
-      <c r="K33">
+      <c r="N33">
         <v>2.361666666666667</v>
       </c>
-      <c r="L33">
+      <c r="O33">
         <v>3.944723618090452</v>
       </c>
-      <c r="M33">
+      <c r="P33">
         <v>2.282845188284519</v>
       </c>
-      <c r="N33">
+      <c r="Q33">
         <v>2.090833333333333</v>
       </c>
-      <c r="O33">
+      <c r="R33">
         <v>2.356839422259983</v>
       </c>
-      <c r="P33">
+      <c r="S33">
         <v>2.045986622073579</v>
       </c>
-      <c r="Q33">
+      <c r="T33">
         <v>2.536108751062022</v>
       </c>
-      <c r="R33">
+      <c r="U33">
         <v>2.014166666666667</v>
       </c>
-      <c r="S33">
+      <c r="V33">
         <v>1.824267782426778</v>
       </c>
-      <c r="T33">
+      <c r="W33">
         <v>2.1825</v>
       </c>
-      <c r="U33">
+      <c r="X33">
         <v>1.967391304347826</v>
       </c>
-      <c r="V33">
+      <c r="Y33">
         <v>3.835769561478934</v>
       </c>
-      <c r="W33">
+      <c r="Z33">
         <v>0.5</v>
       </c>
-      <c r="X33">
+      <c r="AA33">
         <v>40.82666666666667</v>
       </c>
-      <c r="Y33">
+      <c r="AB33">
         <v>0.9933333333333333</v>
       </c>
-      <c r="Z33">
+      <c r="AC33">
         <v>4.693333333333333</v>
       </c>
-      <c r="AA33">
+      <c r="AD33">
         <v>5.5175</v>
+      </c>
+      <c r="AE33">
+        <v>5.365</v>
       </c>
     </row>
     <row r="34">
@@ -3236,79 +3622,91 @@
         </is>
       </c>
       <c r="C34">
+        <v>0.9991624790619765</v>
+      </c>
+      <c r="D34">
+        <v>0.9652247667514843</v>
+      </c>
+      <c r="E34">
         <v>0.9763713080168777</v>
       </c>
-      <c r="D34">
+      <c r="F34">
+        <v>0.9991617770326907</v>
+      </c>
+      <c r="G34">
         <v>2.623693379790941</v>
       </c>
-      <c r="E34">
+      <c r="H34">
         <v>1.606113537117904</v>
       </c>
-      <c r="F34">
+      <c r="I34">
         <v>1.158390410958904</v>
       </c>
-      <c r="G34">
+      <c r="J34">
         <v>1.493528904227783</v>
       </c>
-      <c r="H34">
+      <c r="K34">
         <v>1.244386873920553</v>
       </c>
-      <c r="I34">
+      <c r="L34">
         <v>1.117173524150268</v>
       </c>
-      <c r="J34">
+      <c r="M34">
         <v>1.133453561767358</v>
       </c>
-      <c r="K34">
+      <c r="N34">
         <v>1.581705150976909</v>
       </c>
-      <c r="L34">
+      <c r="O34">
         <v>3.682581786030062</v>
       </c>
-      <c r="M34">
+      <c r="P34">
         <v>1.116197183098592</v>
       </c>
-      <c r="N34">
+      <c r="Q34">
         <v>1.151009657594381</v>
       </c>
-      <c r="O34">
+      <c r="R34">
         <v>1.209405501330967</v>
       </c>
-      <c r="P34">
+      <c r="S34">
         <v>1.699912510936133</v>
       </c>
-      <c r="Q34">
+      <c r="T34">
         <v>3.048993875765529</v>
       </c>
-      <c r="R34">
+      <c r="U34">
         <v>1.306479859894921</v>
       </c>
-      <c r="S34">
+      <c r="V34">
         <v>1.124778761061947</v>
       </c>
-      <c r="T34">
+      <c r="W34">
         <v>1.064601769911504</v>
       </c>
-      <c r="U34">
+      <c r="X34">
         <v>1.193433895297249</v>
       </c>
-      <c r="V34">
+      <c r="Y34">
         <v>4.542039355992844</v>
       </c>
-      <c r="W34">
+      <c r="Z34">
         <v>0.5175585284280937</v>
       </c>
-      <c r="X34">
+      <c r="AA34">
         <v>40.21772151898734</v>
       </c>
-      <c r="Y34">
+      <c r="AB34">
         <v>0.9908026755852842</v>
       </c>
-      <c r="Z34">
+      <c r="AC34">
         <v>5.334728033472803</v>
       </c>
-      <c r="AA34">
+      <c r="AD34">
         <v>5.439407149084569</v>
+      </c>
+      <c r="AE34">
+        <v>4.00418410041841</v>
       </c>
     </row>
     <row r="35">
@@ -3323,79 +3721,91 @@
         </is>
       </c>
       <c r="C35">
+        <v>0.4155206286836935</v>
+      </c>
+      <c r="D35">
+        <v>0.3011811023622047</v>
+      </c>
+      <c r="E35">
         <v>0.3135509396636993</v>
       </c>
-      <c r="D35">
+      <c r="F35">
+        <v>0.3473053892215569</v>
+      </c>
+      <c r="G35">
         <v>2.793542074363992</v>
       </c>
-      <c r="E35">
+      <c r="H35">
         <v>2.515655577299413</v>
       </c>
-      <c r="F35">
+      <c r="I35">
         <v>2.258317025440313</v>
       </c>
-      <c r="G35">
+      <c r="J35">
         <v>2.292156862745098</v>
       </c>
-      <c r="H35">
+      <c r="K35">
         <v>2.375614552605703</v>
       </c>
-      <c r="I35">
+      <c r="L35">
         <v>5.258570029382958</v>
       </c>
-      <c r="J35">
+      <c r="M35">
         <v>3.306862745098039</v>
       </c>
-      <c r="K35">
+      <c r="N35">
         <v>3.877690802348337</v>
       </c>
-      <c r="L35">
+      <c r="O35">
         <v>5.379547689282203</v>
       </c>
-      <c r="M35">
+      <c r="P35">
         <v>5.672227674190383</v>
       </c>
-      <c r="N35">
+      <c r="Q35">
         <v>3.419449901768173</v>
       </c>
-      <c r="O35">
+      <c r="R35">
         <v>5.157016683022571</v>
       </c>
-      <c r="P35">
+      <c r="S35">
         <v>2.225490196078431</v>
       </c>
-      <c r="Q35">
+      <c r="T35">
         <v>3.517173699705594</v>
       </c>
-      <c r="R35">
+      <c r="U35">
         <v>2.314033366045142</v>
       </c>
-      <c r="S35">
+      <c r="V35">
         <v>2.775811209439528</v>
       </c>
-      <c r="T35">
+      <c r="W35">
         <v>3.467059980334317</v>
       </c>
-      <c r="U35">
+      <c r="X35">
         <v>2.557409224730128</v>
       </c>
-      <c r="V35">
+      <c r="Y35">
         <v>3.986247544204322</v>
       </c>
-      <c r="W35">
+      <c r="Z35">
         <v>0.4403131115459882</v>
       </c>
-      <c r="X35">
+      <c r="AA35">
         <v>40.68880688806888</v>
       </c>
-      <c r="Y35">
+      <c r="AB35">
         <v>0.5827619980411362</v>
       </c>
-      <c r="Z35">
+      <c r="AC35">
         <v>4.84984984984985</v>
       </c>
-      <c r="AA35">
+      <c r="AD35">
         <v>5.024557956777996</v>
+      </c>
+      <c r="AE35">
+        <v>6.925563173359452</v>
       </c>
     </row>
     <row r="36">
@@ -3410,79 +3820,91 @@
         </is>
       </c>
       <c r="C36">
+        <v>0.9866666666666667</v>
+      </c>
+      <c r="D36">
+        <v>0.9616666666666667</v>
+      </c>
+      <c r="E36">
         <v>0.9766666666666667</v>
       </c>
-      <c r="D36">
+      <c r="F36">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="G36">
         <v>3.6775</v>
       </c>
-      <c r="E36">
+      <c r="H36">
         <v>3.13</v>
       </c>
-      <c r="F36">
+      <c r="I36">
         <v>2.515833333333333</v>
       </c>
-      <c r="G36">
+      <c r="J36">
         <v>2.830833333333334</v>
       </c>
-      <c r="H36">
+      <c r="K36">
         <v>2.785833333333333</v>
       </c>
-      <c r="I36">
+      <c r="L36">
         <v>2.77</v>
       </c>
-      <c r="J36">
+      <c r="M36">
         <v>2.781666666666667</v>
       </c>
-      <c r="K36">
+      <c r="N36">
         <v>3.62</v>
       </c>
-      <c r="L36">
+      <c r="O36">
         <v>5.710833333333333</v>
       </c>
-      <c r="M36">
+      <c r="P36">
         <v>3.1425</v>
       </c>
-      <c r="N36">
+      <c r="Q36">
         <v>2.940833333333333</v>
       </c>
-      <c r="O36">
+      <c r="R36">
         <v>3.193333333333333</v>
       </c>
-      <c r="P36">
+      <c r="S36">
         <v>3.2725</v>
       </c>
-      <c r="Q36">
+      <c r="T36">
         <v>4.703333333333333</v>
       </c>
-      <c r="R36">
+      <c r="U36">
         <v>2.821666666666667</v>
       </c>
-      <c r="S36">
+      <c r="V36">
         <v>2.345833333333333</v>
       </c>
-      <c r="T36">
+      <c r="W36">
         <v>2.735833333333333</v>
       </c>
-      <c r="U36">
+      <c r="X36">
         <v>2.539166666666667</v>
       </c>
-      <c r="V36">
+      <c r="Y36">
         <v>4.303333333333334</v>
       </c>
-      <c r="W36">
+      <c r="Z36">
         <v>0.5</v>
       </c>
-      <c r="X36">
+      <c r="AA36">
         <v>37.22</v>
       </c>
-      <c r="Y36">
+      <c r="AB36">
         <v>1</v>
       </c>
-      <c r="Z36">
+      <c r="AC36">
         <v>3.479166666666667</v>
       </c>
-      <c r="AA36">
+      <c r="AD36">
         <v>5.228333333333333</v>
+      </c>
+      <c r="AE36">
+        <v>4.066666666666666</v>
       </c>
     </row>
     <row r="37">
@@ -3497,79 +3919,91 @@
         </is>
       </c>
       <c r="C37">
+        <v>0.9990328820116054</v>
+      </c>
+      <c r="D37">
+        <v>0.9874274661508704</v>
+      </c>
+      <c r="E37">
         <v>0.995159728944821</v>
       </c>
-      <c r="D37">
+      <c r="F37">
+        <v>0.9961202715809894</v>
+      </c>
+      <c r="G37">
         <v>1.856316297010608</v>
       </c>
-      <c r="E37">
+      <c r="H37">
         <v>2.423484119345524</v>
       </c>
-      <c r="F37">
+      <c r="I37">
         <v>1.294970986460348</v>
       </c>
-      <c r="G37">
+      <c r="J37">
         <v>1.393822393822394</v>
       </c>
-      <c r="H37">
+      <c r="K37">
         <v>1.28873917228104</v>
       </c>
-      <c r="I37">
+      <c r="L37">
         <v>1.261078998073218</v>
       </c>
-      <c r="J37">
+      <c r="M37">
         <v>1.226615236258438</v>
       </c>
-      <c r="K37">
+      <c r="N37">
         <v>2.530376084860174</v>
       </c>
-      <c r="L37">
+      <c r="O37">
         <v>5.723938223938224</v>
       </c>
-      <c r="M37">
+      <c r="P37">
         <v>1.647683397683398</v>
       </c>
-      <c r="N37">
+      <c r="Q37">
         <v>1.411934552454283</v>
       </c>
-      <c r="O37">
+      <c r="R37">
         <v>2.004840271055179</v>
       </c>
-      <c r="P37">
+      <c r="S37">
         <v>1.162970106075217</v>
       </c>
-      <c r="Q37">
+      <c r="T37">
         <v>1.3747591522158</v>
       </c>
-      <c r="R37">
+      <c r="U37">
         <v>1.240115718418515</v>
       </c>
-      <c r="S37">
+      <c r="V37">
         <v>1.216007714561234</v>
       </c>
-      <c r="T37">
+      <c r="W37">
         <v>1.327552986512524</v>
       </c>
-      <c r="U37">
+      <c r="X37">
         <v>1.215458937198068</v>
       </c>
-      <c r="V37">
+      <c r="Y37">
         <v>7.185149469623915</v>
       </c>
-      <c r="W37">
+      <c r="Z37">
         <v>0.4714975845410628</v>
       </c>
-      <c r="X37">
+      <c r="AA37">
         <v>37.65250965250965</v>
       </c>
-      <c r="Y37">
+      <c r="AB37">
         <v>0.9932627526467758</v>
       </c>
-      <c r="Z37">
+      <c r="AC37">
         <v>3.693719806763285</v>
       </c>
-      <c r="AA37">
+      <c r="AD37">
         <v>5.944820909970958</v>
+      </c>
+      <c r="AE37">
+        <v>4.036644165863066</v>
       </c>
     </row>
     <row r="38">
@@ -3584,79 +4018,91 @@
         </is>
       </c>
       <c r="C38">
+        <v>0.9597469810235768</v>
+      </c>
+      <c r="D38">
+        <v>0.7173659673659674</v>
+      </c>
+      <c r="E38">
         <v>0.6111111111111112</v>
       </c>
-      <c r="D38">
+      <c r="F38">
+        <v>0.7831603229527105</v>
+      </c>
+      <c r="G38">
         <v>4.696916812100058</v>
       </c>
-      <c r="E38">
+      <c r="H38">
         <v>4.300987797791981</v>
       </c>
-      <c r="F38">
+      <c r="I38">
         <v>2.33467974610502</v>
       </c>
-      <c r="G38">
+      <c r="J38">
         <v>2.979674796747967</v>
       </c>
-      <c r="H38">
+      <c r="K38">
         <v>2.647469458987783</v>
       </c>
-      <c r="I38">
+      <c r="L38">
         <v>4.338661930136175</v>
       </c>
-      <c r="J38">
+      <c r="M38">
         <v>3.620164126611958</v>
       </c>
-      <c r="K38">
+      <c r="N38">
         <v>3.251168224299065</v>
       </c>
-      <c r="L38">
+      <c r="O38">
         <v>5.040603248259861</v>
       </c>
-      <c r="M38">
+      <c r="P38">
         <v>4.755711775043936</v>
       </c>
-      <c r="N38">
+      <c r="Q38">
         <v>2.768782760629004</v>
       </c>
-      <c r="O38">
+      <c r="R38">
         <v>3.767867690490254</v>
       </c>
-      <c r="P38">
+      <c r="S38">
         <v>2.197687861271676</v>
       </c>
-      <c r="Q38">
+      <c r="T38">
         <v>3.085217391304348</v>
       </c>
-      <c r="R38">
+      <c r="U38">
         <v>2.391178177597214</v>
       </c>
-      <c r="S38">
+      <c r="V38">
         <v>2.334701055099648</v>
       </c>
-      <c r="T38">
+      <c r="W38">
         <v>3.320921985815603</v>
       </c>
-      <c r="U38">
+      <c r="X38">
         <v>2.491822429906542</v>
       </c>
-      <c r="V38">
+      <c r="Y38">
         <v>3.63785046728972</v>
       </c>
-      <c r="W38">
+      <c r="Z38">
         <v>0.5020103388856979</v>
       </c>
-      <c r="X38">
+      <c r="AA38">
         <v>43.35825186889016</v>
       </c>
-      <c r="Y38">
+      <c r="AB38">
         <v>1</v>
       </c>
-      <c r="Z38">
+      <c r="AC38">
         <v>4.023081361800346</v>
       </c>
-      <c r="AA38">
+      <c r="AD38">
         <v>4.228621291448516</v>
+      </c>
+      <c r="AE38">
+        <v>8.007845503922752</v>
       </c>
     </row>
     <row r="39">
@@ -3671,79 +4117,91 @@
         </is>
       </c>
       <c r="C39">
+        <v>0.9891666666666666</v>
+      </c>
+      <c r="D39">
+        <v>0.845</v>
+      </c>
+      <c r="E39">
         <v>0.9075</v>
       </c>
-      <c r="D39">
+      <c r="F39">
+        <v>0.9375</v>
+      </c>
+      <c r="G39">
         <v>3.654712260216848</v>
       </c>
-      <c r="E39">
+      <c r="H39">
         <v>3.161236424394319</v>
       </c>
-      <c r="F39">
+      <c r="I39">
         <v>1.488740617180984</v>
       </c>
-      <c r="G39">
+      <c r="J39">
         <v>1.621666666666667</v>
       </c>
-      <c r="H39">
+      <c r="K39">
         <v>1.721666666666667</v>
       </c>
-      <c r="I39">
+      <c r="L39">
         <v>1.721434528773978</v>
       </c>
-      <c r="J39">
+      <c r="M39">
         <v>1.849040867389491</v>
       </c>
-      <c r="K39">
+      <c r="N39">
         <v>1.410341951626355</v>
       </c>
-      <c r="L39">
+      <c r="O39">
         <v>2.448247078464107</v>
       </c>
-      <c r="M39">
+      <c r="P39">
         <v>1.629382303839733</v>
       </c>
-      <c r="N39">
+      <c r="Q39">
         <v>1.359466221851543</v>
       </c>
-      <c r="O39">
+      <c r="R39">
         <v>1.946577629382304</v>
       </c>
-      <c r="P39">
+      <c r="S39">
         <v>1.533778148457048</v>
       </c>
-      <c r="Q39">
+      <c r="T39">
         <v>5.039166666666667</v>
       </c>
-      <c r="R39">
+      <c r="U39">
         <v>1.438698915763136</v>
       </c>
-      <c r="S39">
+      <c r="V39">
         <v>1.549624687239366</v>
       </c>
-      <c r="T39">
+      <c r="W39">
         <v>1.386155129274395</v>
       </c>
-      <c r="U39">
+      <c r="X39">
         <v>1.433694745621351</v>
       </c>
-      <c r="V39">
+      <c r="Y39">
         <v>3.932330827067669</v>
       </c>
-      <c r="W39">
+      <c r="Z39">
         <v>0.5008333333333334</v>
       </c>
-      <c r="X39">
+      <c r="AA39">
         <v>40.43166666666666</v>
       </c>
-      <c r="Y39">
+      <c r="AB39">
         <v>1</v>
       </c>
-      <c r="Z39">
+      <c r="AC39">
         <v>3.377295492487479</v>
       </c>
-      <c r="AA39">
+      <c r="AD39">
         <v>4.7025</v>
+      </c>
+      <c r="AE39">
+        <v>2.72</v>
       </c>
     </row>
     <row r="40">
@@ -3758,79 +4216,91 @@
         </is>
       </c>
       <c r="C40">
+        <v>0.6391941391941391</v>
+      </c>
+      <c r="D40">
+        <v>0.539072039072039</v>
+      </c>
+      <c r="E40">
         <v>0.4334554334554335</v>
       </c>
-      <c r="D40">
+      <c r="F40">
+        <v>0.44993894993895</v>
+      </c>
+      <c r="G40">
         <v>3.83302752293578</v>
       </c>
-      <c r="E40">
+      <c r="H40">
         <v>3.964590964590965</v>
       </c>
-      <c r="F40">
+      <c r="I40">
         <v>3.29059829059829</v>
       </c>
-      <c r="G40">
+      <c r="J40">
         <v>3.592796092796093</v>
       </c>
-      <c r="H40">
+      <c r="K40">
         <v>3.427960927960928</v>
       </c>
-      <c r="I40">
+      <c r="L40">
         <v>3.874236874236874</v>
       </c>
-      <c r="J40">
+      <c r="M40">
         <v>3.39010989010989</v>
       </c>
-      <c r="K40">
+      <c r="N40">
         <v>4.178876678876679</v>
       </c>
-      <c r="L40">
+      <c r="O40">
         <v>4.509157509157509</v>
       </c>
-      <c r="M40">
+      <c r="P40">
         <v>4.535409035409035</v>
       </c>
-      <c r="N40">
+      <c r="Q40">
         <v>3.273504273504273</v>
       </c>
-      <c r="O40">
+      <c r="R40">
         <v>3.927350427350427</v>
       </c>
-      <c r="P40">
+      <c r="S40">
         <v>3.337606837606838</v>
       </c>
-      <c r="Q40">
+      <c r="T40">
         <v>3.664835164835165</v>
       </c>
-      <c r="R40">
+      <c r="U40">
         <v>3.190476190476191</v>
       </c>
-      <c r="S40">
+      <c r="V40">
         <v>3.182539682539682</v>
       </c>
-      <c r="T40">
+      <c r="W40">
         <v>3.832722832722833</v>
       </c>
-      <c r="U40">
+      <c r="X40">
         <v>3.297313797313797</v>
       </c>
-      <c r="V40">
+      <c r="Y40">
         <v>5.177045177045177</v>
       </c>
-      <c r="W40">
+      <c r="Z40">
         <v>0.4835164835164835</v>
       </c>
-      <c r="X40">
+      <c r="AA40">
         <v>38.7985347985348</v>
       </c>
-      <c r="Y40">
+      <c r="AB40">
         <v>1</v>
       </c>
-      <c r="Z40">
+      <c r="AC40">
         <v>5.645299145299146</v>
       </c>
-      <c r="AA40">
+      <c r="AD40">
         <v>5.493894993894994</v>
+      </c>
+      <c r="AE40">
+        <v>6.014652014652015</v>
       </c>
     </row>
     <row r="41">
@@ -3845,79 +4315,91 @@
         </is>
       </c>
       <c r="C41">
+        <v>0.952018278750952</v>
+      </c>
+      <c r="D41">
+        <v>0.8187357197258187</v>
+      </c>
+      <c r="E41">
         <v>0.8773800456968773</v>
       </c>
-      <c r="D41">
+      <c r="F41">
+        <v>0.8964204112718964</v>
+      </c>
+      <c r="G41">
         <v>4.395277989337395</v>
       </c>
-      <c r="E41">
+      <c r="H41">
         <v>3.979436405178979</v>
       </c>
-      <c r="F41">
+      <c r="I41">
         <v>3.0997715156131</v>
       </c>
-      <c r="G41">
+      <c r="J41">
         <v>3.408987052551409</v>
       </c>
-      <c r="H41">
+      <c r="K41">
         <v>3.084539223153084</v>
       </c>
-      <c r="I41">
+      <c r="L41">
         <v>3.594059405940594</v>
       </c>
-      <c r="J41">
+      <c r="M41">
         <v>3.387661843107387</v>
       </c>
-      <c r="K41">
+      <c r="N41">
         <v>3.524752475247525</v>
       </c>
-      <c r="L41">
+      <c r="O41">
         <v>4.642802741812643</v>
       </c>
-      <c r="M41">
+      <c r="P41">
         <v>3.821020563594821</v>
       </c>
-      <c r="N41">
+      <c r="Q41">
         <v>3.15003808073115</v>
       </c>
-      <c r="O41">
+      <c r="R41">
         <v>3.953541507996953</v>
       </c>
-      <c r="P41">
+      <c r="S41">
         <v>3.134805788271135</v>
       </c>
-      <c r="Q41">
+      <c r="T41">
         <v>4.466108149276466</v>
       </c>
-      <c r="R41">
+      <c r="U41">
         <v>3.276466108149276</v>
       </c>
-      <c r="S41">
+      <c r="V41">
         <v>3.104341203351104</v>
       </c>
-      <c r="T41">
+      <c r="W41">
         <v>3.594059405940594</v>
       </c>
-      <c r="U41">
+      <c r="X41">
         <v>3.148514851485149</v>
       </c>
-      <c r="V41">
+      <c r="Y41">
         <v>4.575019040365575</v>
       </c>
-      <c r="W41">
+      <c r="Z41">
         <v>0.5003808073115004</v>
       </c>
-      <c r="X41">
+      <c r="AA41">
         <v>38.32977913175933</v>
       </c>
-      <c r="Y41">
+      <c r="AB41">
         <v>0.9885757806549885</v>
       </c>
-      <c r="Z41">
+      <c r="AC41">
         <v>4.344249809596344</v>
       </c>
-      <c r="AA41">
+      <c r="AD41">
         <v>4.601675552170602</v>
+      </c>
+      <c r="AE41">
+        <v>3.155369383092155</v>
       </c>
     </row>
     <row r="42">
@@ -3932,79 +4414,91 @@
         </is>
       </c>
       <c r="C42">
+        <v>0.9886822958771221</v>
+      </c>
+      <c r="D42">
+        <v>0.8302344381568311</v>
+      </c>
+      <c r="E42">
         <v>0.8528698464025869</v>
       </c>
-      <c r="D42">
+      <c r="F42">
+        <v>0.9240097008892482</v>
+      </c>
+      <c r="G42">
         <v>2.0032414910859</v>
       </c>
-      <c r="E42">
+      <c r="H42">
         <v>2.016220600162206</v>
       </c>
-      <c r="F42">
+      <c r="I42">
         <v>1.679352226720648</v>
       </c>
-      <c r="G42">
+      <c r="J42">
         <v>1.789303079416532</v>
       </c>
-      <c r="H42">
+      <c r="K42">
         <v>1.71417004048583</v>
       </c>
-      <c r="I42">
+      <c r="L42">
         <v>1.5</v>
       </c>
-      <c r="J42">
+      <c r="M42">
         <v>1.635036496350365</v>
       </c>
-      <c r="K42">
+      <c r="N42">
         <v>1.708706265256306</v>
       </c>
-      <c r="L42">
+      <c r="O42">
         <v>2.475609756097561</v>
       </c>
-      <c r="M42">
+      <c r="P42">
         <v>2.690923957481603</v>
       </c>
-      <c r="N42">
+      <c r="Q42">
         <v>1.552588996763754</v>
       </c>
-      <c r="O42">
+      <c r="R42">
         <v>1.647506339814032</v>
       </c>
-      <c r="P42">
+      <c r="S42">
         <v>1.944939271255061</v>
       </c>
-      <c r="Q42">
+      <c r="T42">
         <v>6.049352750809062</v>
       </c>
-      <c r="R42">
+      <c r="U42">
         <v>1.854486661277284</v>
       </c>
-      <c r="S42">
+      <c r="V42">
         <v>1.661003236245955</v>
       </c>
-      <c r="T42">
+      <c r="W42">
         <v>2.559902200488998</v>
       </c>
-      <c r="U42">
+      <c r="X42">
         <v>1.704692556634304</v>
       </c>
-      <c r="V42">
+      <c r="Y42">
         <v>2.621311475409836</v>
       </c>
-      <c r="W42">
+      <c r="Z42">
         <v>0.5117219078415521</v>
       </c>
-      <c r="X42">
+      <c r="AA42">
         <v>32.56345998383185</v>
       </c>
-      <c r="Y42">
+      <c r="AB42">
         <v>0.9967663702506063</v>
       </c>
-      <c r="Z42">
+      <c r="AC42">
         <v>3.588762214983714</v>
       </c>
-      <c r="AA42">
+      <c r="AD42">
         <v>4.411908646003263</v>
+      </c>
+      <c r="AE42">
+        <v>5.695052716950527</v>
       </c>
     </row>
     <row r="43">
@@ -4019,79 +4513,91 @@
         </is>
       </c>
       <c r="C43">
+        <v>0.9216666666666666</v>
+      </c>
+      <c r="D43">
+        <v>0.2558333333333334</v>
+      </c>
+      <c r="E43">
         <v>0.2583333333333334</v>
       </c>
-      <c r="D43">
+      <c r="F43">
+        <v>0.3491666666666667</v>
+      </c>
+      <c r="G43">
         <v>4.038333333333333</v>
       </c>
-      <c r="E43">
+      <c r="H43">
         <v>3.65</v>
       </c>
-      <c r="F43">
+      <c r="I43">
         <v>1.66</v>
       </c>
-      <c r="G43">
+      <c r="J43">
         <v>2.19</v>
       </c>
-      <c r="H43">
+      <c r="K43">
         <v>2.134166666666667</v>
       </c>
-      <c r="I43">
+      <c r="L43">
         <v>3.264166666666667</v>
       </c>
-      <c r="J43">
+      <c r="M43">
         <v>2.703333333333333</v>
       </c>
-      <c r="K43">
+      <c r="N43">
         <v>2.0525</v>
       </c>
-      <c r="L43">
+      <c r="O43">
         <v>4.48</v>
       </c>
-      <c r="M43">
+      <c r="P43">
         <v>4.088333333333333</v>
       </c>
-      <c r="N43">
+      <c r="Q43">
         <v>1.800833333333333</v>
       </c>
-      <c r="O43">
+      <c r="R43">
         <v>2.47</v>
       </c>
-      <c r="P43">
+      <c r="S43">
         <v>1.585833333333333</v>
       </c>
-      <c r="Q43">
+      <c r="T43">
         <v>4.3525</v>
       </c>
-      <c r="R43">
+      <c r="U43">
         <v>1.975</v>
       </c>
-      <c r="S43">
+      <c r="V43">
         <v>1.995833333333333</v>
       </c>
-      <c r="T43">
+      <c r="W43">
         <v>3.425</v>
       </c>
-      <c r="U43">
+      <c r="X43">
         <v>2.076666666666667</v>
       </c>
-      <c r="V43">
+      <c r="Y43">
         <v>2.313333333333333</v>
       </c>
-      <c r="W43">
+      <c r="Z43">
         <v>0.4908333333333333</v>
       </c>
-      <c r="X43">
+      <c r="AA43">
         <v>35.1325</v>
       </c>
-      <c r="Y43">
+      <c r="AB43">
         <v>0.9983333333333333</v>
       </c>
-      <c r="Z43">
+      <c r="AC43">
         <v>3.735613010842369</v>
       </c>
-      <c r="AA43">
+      <c r="AD43">
         <v>4.579166666666667</v>
+      </c>
+      <c r="AE43">
+        <v>6.428333333333334</v>
       </c>
     </row>
     <row r="44">
@@ -4106,76 +4612,88 @@
         </is>
       </c>
       <c r="C44">
+        <v>0.7395348837209302</v>
+      </c>
+      <c r="D44">
+        <v>0.6391509433962265</v>
+      </c>
+      <c r="E44">
         <v>0.4797136038186158</v>
       </c>
-      <c r="D44">
+      <c r="F44">
+        <v>0.665083135391924</v>
+      </c>
+      <c r="G44">
         <v>2.173033707865168</v>
       </c>
-      <c r="E44">
+      <c r="H44">
         <v>2.531531531531531</v>
       </c>
-      <c r="F44">
+      <c r="I44">
         <v>1.307174887892377</v>
       </c>
-      <c r="G44">
+      <c r="J44">
         <v>1.954954954954955</v>
       </c>
-      <c r="H44">
+      <c r="K44">
         <v>1.349775784753363</v>
       </c>
-      <c r="I44">
+      <c r="L44">
         <v>6.593533487297922</v>
       </c>
-      <c r="J44">
+      <c r="M44">
         <v>3.850917431192661</v>
       </c>
-      <c r="K44">
+      <c r="N44">
         <v>4.867579908675799</v>
       </c>
-      <c r="L44">
+      <c r="O44">
         <v>6.930022573363432</v>
       </c>
-      <c r="M44">
+      <c r="P44">
         <v>7.091324200913242</v>
       </c>
-      <c r="N44">
+      <c r="Q44">
         <v>3.267281105990783</v>
       </c>
-      <c r="O44">
+      <c r="R44">
         <v>5.619047619047619</v>
       </c>
-      <c r="Q44">
+      <c r="T44">
         <v>1.910112359550562</v>
       </c>
-      <c r="R44">
+      <c r="U44">
         <v>1.677130044843049</v>
       </c>
-      <c r="S44">
+      <c r="V44">
         <v>1.416666666666667</v>
       </c>
-      <c r="T44">
+      <c r="W44">
         <v>5.401805869074492</v>
       </c>
-      <c r="U44">
+      <c r="X44">
         <v>1.556306306306306</v>
       </c>
-      <c r="V44">
+      <c r="Y44">
         <v>4.13963963963964</v>
       </c>
-      <c r="W44">
+      <c r="Z44">
         <v>0.4988814317673378</v>
       </c>
-      <c r="X44">
+      <c r="AA44">
         <v>52.07451923076923</v>
       </c>
-      <c r="Y44">
+      <c r="AB44">
         <v>0.916289592760181</v>
       </c>
-      <c r="Z44">
+      <c r="AC44">
         <v>4.833333333333333</v>
       </c>
-      <c r="AA44">
+      <c r="AD44">
         <v>5.377049180327869</v>
+      </c>
+      <c r="AE44">
+        <v>7.473193473193473</v>
       </c>
     </row>
     <row r="45">
@@ -4190,79 +4708,91 @@
         </is>
       </c>
       <c r="C45">
+        <v>0.3825198637911464</v>
+      </c>
+      <c r="D45">
+        <v>0.3866498740554156</v>
+      </c>
+      <c r="E45">
         <v>0.1370558375634518</v>
       </c>
-      <c r="D45">
+      <c r="F45">
+        <v>0.2717770034843205</v>
+      </c>
+      <c r="G45">
         <v>1.569387755102041</v>
       </c>
-      <c r="E45">
+      <c r="H45">
         <v>2.095383054287164</v>
       </c>
-      <c r="F45">
+      <c r="I45">
         <v>1.347145022738757</v>
       </c>
-      <c r="G45">
+      <c r="J45">
         <v>1.857432775240994</v>
       </c>
-      <c r="H45">
+      <c r="K45">
         <v>1.462259239979178</v>
       </c>
-      <c r="I45">
+      <c r="L45">
         <v>9.03134962805526</v>
       </c>
-      <c r="J45">
+      <c r="M45">
         <v>6.227717391304348</v>
       </c>
-      <c r="K45">
+      <c r="N45">
         <v>7.637894736842105</v>
       </c>
-      <c r="L45">
+      <c r="O45">
         <v>8.193850964043772</v>
       </c>
-      <c r="M45">
+      <c r="P45">
         <v>8.82712215320911</v>
       </c>
-      <c r="N45">
+      <c r="Q45">
         <v>5.38557637705849</v>
       </c>
-      <c r="O45">
+      <c r="R45">
         <v>7.562043795620438</v>
       </c>
-      <c r="P45">
+      <c r="S45">
         <v>1.282542885973764</v>
       </c>
-      <c r="Q45">
+      <c r="T45">
         <v>1.72970247100353</v>
       </c>
-      <c r="R45">
+      <c r="U45">
         <v>1.713853904282116</v>
       </c>
-      <c r="S45">
+      <c r="V45">
         <v>1.192991366175724</v>
       </c>
-      <c r="T45">
+      <c r="W45">
         <v>7.179295624332978</v>
       </c>
-      <c r="U45">
+      <c r="X45">
         <v>1.551706308169597</v>
       </c>
-      <c r="V45">
+      <c r="Y45">
         <v>3.401566579634465</v>
       </c>
-      <c r="W45">
+      <c r="Z45">
         <v>0.4629370629370629</v>
       </c>
-      <c r="X45">
+      <c r="AA45">
         <v>53.35990675990676</v>
       </c>
-      <c r="Y45">
+      <c r="AB45">
         <v>0.8905698436712053</v>
       </c>
-      <c r="Z45">
+      <c r="AC45">
         <v>5.732451678535097</v>
       </c>
-      <c r="AA45">
+      <c r="AD45">
         <v>5.78134284016637</v>
+      </c>
+      <c r="AE45">
+        <v>7.995859213250518</v>
       </c>
     </row>
     <row r="46">
@@ -4277,79 +4807,91 @@
         </is>
       </c>
       <c r="C46">
+        <v>0.565947242206235</v>
+      </c>
+      <c r="D46">
+        <v>0.5222363405336722</v>
+      </c>
+      <c r="E46">
         <v>0.2370637785800241</v>
       </c>
-      <c r="D46">
+      <c r="F46">
+        <v>0.408812729498164</v>
+      </c>
+      <c r="G46">
         <v>1.986247544204322</v>
       </c>
-      <c r="E46">
+      <c r="H46">
         <v>2.148003894839338</v>
       </c>
-      <c r="F46">
+      <c r="I46">
         <v>1.385436893203883</v>
       </c>
-      <c r="G46">
+      <c r="J46">
         <v>1.792801556420234</v>
       </c>
-      <c r="H46">
+      <c r="K46">
         <v>1.343719571567673</v>
       </c>
-      <c r="I46">
+      <c r="L46">
         <v>7.327922077922078</v>
       </c>
-      <c r="J46">
+      <c r="M46">
         <v>5.346356916578669</v>
       </c>
-      <c r="K46">
+      <c r="N46">
         <v>6.809766022380468</v>
       </c>
-      <c r="L46">
+      <c r="O46">
         <v>7.790322580645161</v>
       </c>
-      <c r="M46">
+      <c r="P46">
         <v>7.899897854954035</v>
       </c>
-      <c r="N46">
+      <c r="Q46">
         <v>3.305194805194805</v>
       </c>
-      <c r="O46">
+      <c r="R46">
         <v>7.105858170606372</v>
       </c>
-      <c r="P46">
+      <c r="S46">
         <v>1.136319376825706</v>
       </c>
-      <c r="Q46">
+      <c r="T46">
         <v>1.472195121951219</v>
       </c>
-      <c r="R46">
+      <c r="U46">
         <v>1.650048875855328</v>
       </c>
-      <c r="S46">
+      <c r="V46">
         <v>1.190569744597249</v>
       </c>
-      <c r="T46">
+      <c r="W46">
         <v>5.724173553719008</v>
       </c>
-      <c r="U46">
+      <c r="X46">
         <v>1.792964824120603</v>
       </c>
-      <c r="V46">
+      <c r="Y46">
         <v>4.270298047276465</v>
       </c>
-      <c r="W46">
+      <c r="Z46">
         <v>0.425531914893617</v>
       </c>
-      <c r="X46">
+      <c r="AA46">
         <v>57.8511673151751</v>
       </c>
-      <c r="Y46">
+      <c r="AB46">
         <v>0.7730358874878759</v>
       </c>
-      <c r="Z46">
+      <c r="AC46">
         <v>5.442495126705653</v>
       </c>
-      <c r="AA46">
+      <c r="AD46">
         <v>5.692954784437434</v>
+      </c>
+      <c r="AE46">
+        <v>5.672727272727273</v>
       </c>
     </row>
     <row r="47">
@@ -4364,79 +4906,91 @@
         </is>
       </c>
       <c r="C47">
+        <v>0.9857940131912735</v>
+      </c>
+      <c r="D47">
+        <v>0.9101123595505618</v>
+      </c>
+      <c r="E47">
         <v>0.9221770091556459</v>
       </c>
-      <c r="D47">
+      <c r="F47">
+        <v>0.9811991869918699</v>
+      </c>
+      <c r="G47">
         <v>2.737789203084833</v>
       </c>
-      <c r="E47">
+      <c r="H47">
         <v>2.04251012145749</v>
       </c>
-      <c r="F47">
+      <c r="I47">
         <v>1.786707882534776</v>
       </c>
-      <c r="G47">
+      <c r="J47">
         <v>1.967808930425753</v>
       </c>
-      <c r="H47">
+      <c r="K47">
         <v>1.659090909090909</v>
       </c>
-      <c r="I47">
+      <c r="L47">
         <v>1.582417582417582</v>
       </c>
-      <c r="J47">
+      <c r="M47">
         <v>1.5539090444558</v>
       </c>
-      <c r="K47">
+      <c r="N47">
         <v>1.789727126805778</v>
       </c>
-      <c r="L47">
+      <c r="O47">
         <v>2.329781836631152</v>
       </c>
-      <c r="M47">
+      <c r="P47">
         <v>1.57324516785351</v>
       </c>
-      <c r="N47">
+      <c r="Q47">
         <v>1.554545454545454</v>
       </c>
-      <c r="O47">
+      <c r="R47">
         <v>1.640776699029126</v>
       </c>
-      <c r="P47">
+      <c r="S47">
         <v>1.939425051334702</v>
       </c>
-      <c r="Q47">
+      <c r="T47">
         <v>3.341513292433538</v>
       </c>
-      <c r="R47">
+      <c r="U47">
         <v>1.72177009155646</v>
       </c>
-      <c r="S47">
+      <c r="V47">
         <v>1.652555498193082</v>
       </c>
-      <c r="T47">
+      <c r="W47">
         <v>1.665128205128205</v>
       </c>
-      <c r="U47">
+      <c r="X47">
         <v>1.559875583203733</v>
       </c>
-      <c r="V47">
+      <c r="Y47">
         <v>3.701345755693582</v>
       </c>
-      <c r="W47">
+      <c r="Z47">
         <v>0.5197994987468672</v>
       </c>
-      <c r="X47">
+      <c r="AA47">
         <v>35.64551863041289</v>
       </c>
-      <c r="Y47">
+      <c r="AB47">
         <v>0.9969924812030075</v>
       </c>
-      <c r="Z47">
+      <c r="AC47">
         <v>3.16214859437751</v>
       </c>
-      <c r="AA47">
+      <c r="AD47">
         <v>4.418703506907545</v>
+      </c>
+      <c r="AE47">
+        <v>3.963855421686747</v>
       </c>
     </row>
     <row r="48">
@@ -4451,79 +5005,91 @@
         </is>
       </c>
       <c r="C48">
+        <v>0.9820659971305595</v>
+      </c>
+      <c r="D48">
+        <v>0.7368018362662586</v>
+      </c>
+      <c r="E48">
         <v>0.661608497723824</v>
       </c>
-      <c r="D48">
+      <c r="F48">
+        <v>0.8473684210526315</v>
+      </c>
+      <c r="G48">
         <v>3.489283074648928</v>
       </c>
-      <c r="E48">
+      <c r="H48">
         <v>2.772628530050688</v>
       </c>
-      <c r="F48">
+      <c r="I48">
         <v>1.558106169296987</v>
       </c>
-      <c r="G48">
+      <c r="J48">
         <v>1.857142857142857</v>
       </c>
-      <c r="H48">
+      <c r="K48">
         <v>1.715010877447426</v>
       </c>
-      <c r="I48">
+      <c r="L48">
         <v>2.845864661654135</v>
       </c>
-      <c r="J48">
+      <c r="M48">
         <v>2.316983894582723</v>
       </c>
-      <c r="K48">
+      <c r="N48">
         <v>2.325072886297376</v>
       </c>
-      <c r="L48">
+      <c r="O48">
         <v>4.327761627906977</v>
       </c>
-      <c r="M48">
+      <c r="P48">
         <v>4.368070953436807</v>
       </c>
-      <c r="N48">
+      <c r="Q48">
         <v>1.912472647702407</v>
       </c>
-      <c r="O48">
+      <c r="R48">
         <v>3.454198473282443</v>
       </c>
-      <c r="P48">
+      <c r="S48">
         <v>1.480286738351255</v>
       </c>
-      <c r="Q48">
+      <c r="T48">
         <v>1.90050107372942</v>
       </c>
-      <c r="R48">
+      <c r="U48">
         <v>1.608914450035945</v>
       </c>
-      <c r="S48">
+      <c r="V48">
         <v>1.638313609467456</v>
       </c>
-      <c r="T48">
+      <c r="W48">
         <v>2.687167805618831</v>
       </c>
-      <c r="U48">
+      <c r="X48">
         <v>1.729948491537896</v>
       </c>
-      <c r="V48">
+      <c r="Y48">
         <v>3.955571740713765</v>
       </c>
-      <c r="W48">
+      <c r="Z48">
         <v>0.5014285714285714</v>
       </c>
-      <c r="X48">
+      <c r="AA48">
         <v>40.15857142857143</v>
       </c>
-      <c r="Y48">
+      <c r="AB48">
         <v>0.9957142857142857</v>
       </c>
-      <c r="Z48">
+      <c r="AC48">
         <v>4.309285714285714</v>
       </c>
-      <c r="AA48">
+      <c r="AD48">
         <v>4.949385394070861</v>
+      </c>
+      <c r="AE48">
+        <v>7.440775305096913</v>
       </c>
     </row>
     <row r="49">
@@ -4538,79 +5104,91 @@
         </is>
       </c>
       <c r="C49">
+        <v>0.9966638865721434</v>
+      </c>
+      <c r="D49">
+        <v>0.8244147157190636</v>
+      </c>
+      <c r="E49">
         <v>0.6549707602339181</v>
       </c>
-      <c r="D49">
+      <c r="F49">
+        <v>0.9566305254378649</v>
+      </c>
+      <c r="G49">
         <v>5.284166666666667</v>
       </c>
-      <c r="E49">
+      <c r="H49">
         <v>4.811509591326105</v>
       </c>
-      <c r="F49">
+      <c r="I49">
         <v>3.640768588137009</v>
       </c>
-      <c r="G49">
+      <c r="J49">
         <v>4.079298831385643</v>
       </c>
-      <c r="H49">
+      <c r="K49">
         <v>4.216666666666667</v>
       </c>
-      <c r="I49">
+      <c r="L49">
         <v>4.57</v>
       </c>
-      <c r="J49">
+      <c r="M49">
         <v>3.773978315262719</v>
       </c>
-      <c r="K49">
+      <c r="N49">
         <v>3.018333333333334</v>
       </c>
-      <c r="L49">
+      <c r="O49">
         <v>4.205</v>
       </c>
-      <c r="M49">
+      <c r="P49">
         <v>4.314691151919867</v>
       </c>
-      <c r="N49">
+      <c r="Q49">
         <v>3.125104253544621</v>
       </c>
-      <c r="O49">
+      <c r="R49">
         <v>3.625</v>
       </c>
-      <c r="P49">
+      <c r="S49">
         <v>3.437864887406172</v>
       </c>
-      <c r="Q49">
+      <c r="T49">
         <v>3.964166666666667</v>
       </c>
-      <c r="R49">
+      <c r="U49">
         <v>3.729166666666667</v>
       </c>
-      <c r="S49">
+      <c r="V49">
         <v>4.176814011676397</v>
       </c>
-      <c r="T49">
+      <c r="W49">
         <v>3.870617696160267</v>
       </c>
-      <c r="U49">
+      <c r="X49">
         <v>3.994166666666667</v>
       </c>
-      <c r="V49">
+      <c r="Y49">
         <v>4.12510425354462</v>
       </c>
-      <c r="W49">
+      <c r="Z49">
         <v>0.5</v>
       </c>
-      <c r="X49">
+      <c r="AA49">
         <v>43.71416666666666</v>
       </c>
-      <c r="Y49">
+      <c r="AB49">
         <v>0.9983333333333333</v>
       </c>
-      <c r="Z49">
+      <c r="AC49">
         <v>3.340833333333333</v>
       </c>
-      <c r="AA49">
+      <c r="AD49">
         <v>4.393333333333334</v>
+      </c>
+      <c r="AE49">
+        <v>7.187290969899665</v>
       </c>
     </row>
     <row r="50">
@@ -4625,79 +5203,91 @@
         </is>
       </c>
       <c r="C50">
+        <v>0.9686940966010733</v>
+      </c>
+      <c r="D50">
+        <v>0.7140255009107468</v>
+      </c>
+      <c r="E50">
         <v>0.6158701532912534</v>
       </c>
-      <c r="D50">
+      <c r="F50">
+        <v>0.8588129496402878</v>
+      </c>
+      <c r="G50">
         <v>2.465949820788531</v>
       </c>
-      <c r="E50">
+      <c r="H50">
         <v>2.129811996418979</v>
       </c>
-      <c r="F50">
+      <c r="I50">
         <v>1.360787824529991</v>
       </c>
-      <c r="G50">
+      <c r="J50">
         <v>1.519247985675918</v>
       </c>
-      <c r="H50">
+      <c r="K50">
         <v>1.372866127583109</v>
       </c>
-      <c r="I50">
+      <c r="L50">
         <v>5.578707916287534</v>
       </c>
-      <c r="J50">
+      <c r="M50">
         <v>3.079964061096137</v>
       </c>
-      <c r="K50">
+      <c r="N50">
         <v>2.805729632945389</v>
       </c>
-      <c r="L50">
+      <c r="O50">
         <v>6.06618962432916</v>
       </c>
-      <c r="M50">
+      <c r="P50">
         <v>5.12017937219731</v>
       </c>
-      <c r="N50">
+      <c r="Q50">
         <v>1.804659498207885</v>
       </c>
-      <c r="O50">
+      <c r="R50">
         <v>3.339928057553957</v>
       </c>
-      <c r="P50">
+      <c r="S50">
         <v>1.258728737690242</v>
       </c>
-      <c r="Q50">
+      <c r="T50">
         <v>2.637992831541219</v>
       </c>
-      <c r="R50">
+      <c r="U50">
         <v>1.50762331838565</v>
       </c>
-      <c r="S50">
+      <c r="V50">
         <v>1.343525179856115</v>
       </c>
-      <c r="T50">
+      <c r="W50">
         <v>4.028776978417266</v>
       </c>
-      <c r="U50">
+      <c r="X50">
         <v>1.461883408071749</v>
       </c>
-      <c r="V50">
+      <c r="Y50">
         <v>2.744394618834081</v>
       </c>
-      <c r="W50">
+      <c r="Z50">
         <v>0.3928888888888889</v>
       </c>
-      <c r="X50">
+      <c r="AA50">
         <v>49.78222222222222</v>
       </c>
-      <c r="Y50">
+      <c r="AB50">
         <v>0.9381165919282511</v>
       </c>
-      <c r="Z50">
+      <c r="AC50">
         <v>5.476486246672582</v>
       </c>
-      <c r="AA50">
+      <c r="AD50">
         <v>5.135623869801085</v>
+      </c>
+      <c r="AE50">
+        <v>6.657117278424351</v>
       </c>
     </row>
     <row r="51">
@@ -4712,79 +5302,91 @@
         </is>
       </c>
       <c r="C51">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="D51">
+        <v>0.7353255069370331</v>
+      </c>
+      <c r="E51">
         <v>0.7462845010615711</v>
       </c>
-      <c r="D51">
+      <c r="F51">
+        <v>0.7804621848739496</v>
+      </c>
+      <c r="G51">
         <v>2.162675474814203</v>
       </c>
-      <c r="E51">
+      <c r="H51">
         <v>1.911382113821138</v>
       </c>
-      <c r="F51">
+      <c r="I51">
         <v>1.471636952998379</v>
       </c>
-      <c r="G51">
+      <c r="J51">
         <v>2.108218063466233</v>
       </c>
-      <c r="H51">
+      <c r="K51">
         <v>1.621533442088091</v>
       </c>
-      <c r="I51">
+      <c r="L51">
         <v>2.342442356959864</v>
       </c>
-      <c r="J51">
+      <c r="M51">
         <v>1.964046822742475</v>
       </c>
-      <c r="K51">
+      <c r="N51">
         <v>3.089225589225589</v>
       </c>
-      <c r="L51">
+      <c r="O51">
         <v>4.53628023352794</v>
       </c>
-      <c r="M51">
+      <c r="P51">
         <v>4.746153846153846</v>
       </c>
-      <c r="N51">
+      <c r="Q51">
         <v>1.667493796526055</v>
       </c>
-      <c r="O51">
+      <c r="R51">
         <v>2.131979695431472</v>
       </c>
-      <c r="P51">
+      <c r="S51">
         <v>1.389789303079417</v>
       </c>
-      <c r="Q51">
+      <c r="T51">
         <v>1.765991902834008</v>
       </c>
-      <c r="R51">
+      <c r="U51">
         <v>1.386363636363636</v>
       </c>
-      <c r="S51">
+      <c r="V51">
         <v>1.323481116584565</v>
       </c>
-      <c r="T51">
+      <c r="W51">
         <v>2.631623212783852</v>
       </c>
-      <c r="U51">
+      <c r="X51">
         <v>1.512884455527847</v>
       </c>
-      <c r="V51">
+      <c r="Y51">
         <v>2.355874894336433</v>
       </c>
-      <c r="W51">
+      <c r="Z51">
         <v>0.3953858392999204</v>
       </c>
-      <c r="X51">
+      <c r="AA51">
         <v>48.05483870967742</v>
       </c>
-      <c r="Y51">
+      <c r="AB51">
         <v>0.9984089101034208</v>
       </c>
-      <c r="Z51">
+      <c r="AC51">
         <v>4.204149377593361</v>
       </c>
-      <c r="AA51">
+      <c r="AD51">
         <v>5.389221556886228</v>
+      </c>
+      <c r="AE51">
+        <v>6.216019417475728</v>
       </c>
     </row>
     <row r="52">
@@ -4799,79 +5401,91 @@
         </is>
       </c>
       <c r="C52">
+        <v>0.8458308338332333</v>
+      </c>
+      <c r="D52">
+        <v>0.4851485148514851</v>
+      </c>
+      <c r="E52">
         <v>0.4496330887258172</v>
       </c>
-      <c r="D52">
+      <c r="F52">
+        <v>0.466</v>
+      </c>
+      <c r="G52">
         <v>3.890307603017992</v>
       </c>
-      <c r="E52">
+      <c r="H52">
         <v>4.896338028169014</v>
       </c>
-      <c r="F52">
+      <c r="I52">
         <v>2.272574312955693</v>
       </c>
-      <c r="G52">
+      <c r="J52">
         <v>3.64121699196326</v>
       </c>
-      <c r="H52">
+      <c r="K52">
         <v>2.425652667423383</v>
       </c>
-      <c r="I52">
+      <c r="L52">
         <v>2.604513064133017</v>
       </c>
-      <c r="J52">
+      <c r="M52">
         <v>2.952769679300292</v>
       </c>
-      <c r="K52">
+      <c r="N52">
         <v>4.576855639976622</v>
       </c>
-      <c r="L52">
+      <c r="O52">
         <v>6.095921883974727</v>
       </c>
-      <c r="M52">
+      <c r="P52">
         <v>6.062969381860197</v>
       </c>
-      <c r="N52">
+      <c r="Q52">
         <v>2.708432304038005</v>
       </c>
-      <c r="O52">
+      <c r="R52">
         <v>4.658566221142163</v>
       </c>
-      <c r="P52">
+      <c r="S52">
         <v>2.133600917431193</v>
       </c>
-      <c r="Q52">
+      <c r="T52">
         <v>2.336358479863868</v>
       </c>
-      <c r="R52">
+      <c r="U52">
         <v>2.077141236528644</v>
       </c>
-      <c r="S52">
+      <c r="V52">
         <v>1.886621315192744</v>
       </c>
-      <c r="T52">
+      <c r="W52">
         <v>4.20986920332937</v>
       </c>
-      <c r="U52">
+      <c r="X52">
         <v>2.416374269005848</v>
       </c>
-      <c r="V52">
+      <c r="Y52">
         <v>4.562613430127041</v>
       </c>
-      <c r="W52">
+      <c r="Z52">
         <v>0.4121546961325967</v>
       </c>
-      <c r="X52">
+      <c r="AA52">
         <v>45.40662983425414</v>
       </c>
-      <c r="Y52">
+      <c r="AB52">
         <v>0.9618573797678275</v>
       </c>
-      <c r="Z52">
+      <c r="AC52">
         <v>5.873333333333333</v>
       </c>
-      <c r="AA52">
+      <c r="AD52">
         <v>4.773325701202061</v>
+      </c>
+      <c r="AE52">
+        <v>6.667050691244239</v>
       </c>
     </row>
     <row r="53">
@@ -4886,79 +5500,91 @@
         </is>
       </c>
       <c r="C53">
+        <v>0.8063200815494393</v>
+      </c>
+      <c r="D53">
+        <v>0.6980249480249481</v>
+      </c>
+      <c r="E53">
         <v>0.7000518941359626</v>
       </c>
-      <c r="D53">
+      <c r="F53">
+        <v>0.7284974093264248</v>
+      </c>
+      <c r="G53">
         <v>2.542</v>
       </c>
-      <c r="E53">
+      <c r="H53">
         <v>1.819909954977489</v>
       </c>
-      <c r="F53">
+      <c r="I53">
         <v>1.350175087543772</v>
       </c>
-      <c r="G53">
+      <c r="J53">
         <v>1.532532532532533</v>
       </c>
-      <c r="H53">
+      <c r="K53">
         <v>1.408908908908909</v>
       </c>
-      <c r="I53">
+      <c r="L53">
         <v>3.447686116700201</v>
       </c>
-      <c r="J53">
+      <c r="M53">
         <v>2.776494224008036</v>
       </c>
-      <c r="K53">
+      <c r="N53">
         <v>3.285714285714286</v>
       </c>
-      <c r="L53">
+      <c r="O53">
         <v>4.205025125628141</v>
       </c>
-      <c r="M53">
+      <c r="P53">
         <v>4.035732259687972</v>
       </c>
-      <c r="N53">
+      <c r="Q53">
         <v>2.462079357106981</v>
       </c>
-      <c r="O53">
+      <c r="R53">
         <v>4.188928390045708</v>
       </c>
-      <c r="P53">
+      <c r="S53">
         <v>1.321178821178821</v>
       </c>
-      <c r="Q53">
+      <c r="T53">
         <v>3.361</v>
       </c>
-      <c r="R53">
+      <c r="U53">
         <v>1.584123814278582</v>
       </c>
-      <c r="S53">
+      <c r="V53">
         <v>1.304347826086957</v>
       </c>
-      <c r="T53">
+      <c r="W53">
         <v>2.867203219315895</v>
       </c>
-      <c r="U53">
+      <c r="X53">
         <v>1.550275137568784</v>
       </c>
-      <c r="V53">
+      <c r="Y53">
         <v>4.779175050301811</v>
       </c>
-      <c r="W53">
+      <c r="Z53">
         <v>0.4592445328031809</v>
       </c>
-      <c r="X53">
+      <c r="AA53">
         <v>47.78330019880715</v>
       </c>
-      <c r="Y53">
+      <c r="AB53">
         <v>0.8026838966202783</v>
       </c>
-      <c r="Z53">
+      <c r="AC53">
         <v>5.218127490039841</v>
       </c>
-      <c r="AA53">
+      <c r="AD53">
         <v>4.979038854805726</v>
+      </c>
+      <c r="AE53">
+        <v>5.058648111332008</v>
       </c>
     </row>
     <row r="54">
@@ -4973,79 +5599,91 @@
         </is>
       </c>
       <c r="C54">
+        <v>0.8745098039215686</v>
+      </c>
+      <c r="D54">
+        <v>0.3725701943844493</v>
+      </c>
+      <c r="E54">
         <v>0.3133047210300429</v>
       </c>
-      <c r="D54">
+      <c r="F54">
+        <v>0.3732620320855615</v>
+      </c>
+      <c r="G54">
         <v>3.895325203252033</v>
       </c>
-      <c r="E54">
+      <c r="H54">
         <v>3.939024390243902</v>
       </c>
-      <c r="F54">
+      <c r="I54">
         <v>3.081</v>
       </c>
-      <c r="G54">
+      <c r="J54">
         <v>3.440320962888666</v>
       </c>
-      <c r="H54">
+      <c r="K54">
         <v>3.176113360323887</v>
       </c>
-      <c r="I54">
+      <c r="L54">
         <v>3.855544252288912</v>
       </c>
-      <c r="J54">
+      <c r="M54">
         <v>3.671779141104294</v>
       </c>
-      <c r="K54">
+      <c r="N54">
         <v>4.469262295081967</v>
       </c>
-      <c r="L54">
+      <c r="O54">
         <v>5.527439024390244</v>
       </c>
-      <c r="M54">
+      <c r="P54">
         <v>5.891752577319588</v>
       </c>
-      <c r="N54">
+      <c r="Q54">
         <v>3.269113149847095</v>
       </c>
-      <c r="O54">
+      <c r="R54">
         <v>3.804979253112033</v>
       </c>
-      <c r="P54">
+      <c r="S54">
         <v>3.114228456913827</v>
       </c>
-      <c r="Q54">
+      <c r="T54">
         <v>3.539235412474849</v>
       </c>
-      <c r="R54">
+      <c r="U54">
         <v>3.049098196392785</v>
       </c>
-      <c r="S54">
+      <c r="V54">
         <v>3.038076152304609</v>
       </c>
-      <c r="T54">
+      <c r="W54">
         <v>5.141675284384695</v>
       </c>
-      <c r="U54">
+      <c r="X54">
         <v>3.085714285714286</v>
       </c>
-      <c r="V54">
+      <c r="Y54">
         <v>4.739572736520855</v>
       </c>
-      <c r="W54">
+      <c r="Z54">
         <v>0.4780114722753346</v>
       </c>
-      <c r="X54">
+      <c r="AA54">
         <v>46.13710450623202</v>
       </c>
-      <c r="Y54">
+      <c r="AB54">
         <v>0.9164265129682997</v>
       </c>
-      <c r="Z54">
+      <c r="AC54">
         <v>6.134634146341464</v>
       </c>
-      <c r="AA54">
+      <c r="AD54">
         <v>4.786004056795131</v>
+      </c>
+      <c r="AE54">
+        <v>6.24735322425409</v>
       </c>
     </row>
     <row r="55">
@@ -5060,79 +5698,91 @@
         </is>
       </c>
       <c r="C55">
+        <v>0.7285587975243147</v>
+      </c>
+      <c r="D55">
+        <v>0.5771749298409729</v>
+      </c>
+      <c r="E55">
         <v>0.4608778625954199</v>
       </c>
-      <c r="D55">
+      <c r="F55">
+        <v>0.5410764872521246</v>
+      </c>
+      <c r="G55">
         <v>3.664690939881456</v>
       </c>
-      <c r="E55">
+      <c r="H55">
         <v>3.58972198820556</v>
       </c>
-      <c r="F55">
+      <c r="I55">
         <v>2.353484466834593</v>
       </c>
-      <c r="G55">
+      <c r="J55">
         <v>2.609612141652614</v>
       </c>
-      <c r="H55">
+      <c r="K55">
         <v>2.874894336432798</v>
       </c>
-      <c r="I55">
+      <c r="L55">
         <v>4.909498207885305</v>
       </c>
-      <c r="J55">
+      <c r="M55">
         <v>3.662020905923345</v>
       </c>
-      <c r="K55">
+      <c r="N55">
         <v>4.824500434404865</v>
       </c>
-      <c r="L55">
+      <c r="O55">
         <v>6.241525423728813</v>
       </c>
-      <c r="M55">
+      <c r="P55">
         <v>6.75968992248062</v>
       </c>
-      <c r="N55">
+      <c r="Q55">
         <v>3.132340052585451</v>
       </c>
-      <c r="O55">
+      <c r="R55">
         <v>3.59265890778872</v>
       </c>
-      <c r="P55">
+      <c r="S55">
         <v>1.986463620981388</v>
       </c>
-      <c r="Q55">
+      <c r="T55">
         <v>2.653198653198653</v>
       </c>
-      <c r="R55">
+      <c r="U55">
         <v>2.010906040268456</v>
       </c>
-      <c r="S55">
+      <c r="V55">
         <v>1.946655376799323</v>
       </c>
-      <c r="T55">
+      <c r="W55">
         <v>5.140474100087796</v>
       </c>
-      <c r="U55">
+      <c r="X55">
         <v>2.228813559322034</v>
       </c>
-      <c r="V55">
+      <c r="Y55">
         <v>3.170925110132158</v>
       </c>
-      <c r="W55">
+      <c r="Z55">
         <v>0.46</v>
       </c>
-      <c r="X55">
+      <c r="AA55">
         <v>52.65583333333333</v>
       </c>
-      <c r="Y55">
+      <c r="AB55">
         <v>0.9925</v>
       </c>
-      <c r="Z55">
+      <c r="AC55">
         <v>4.324166666666667</v>
       </c>
-      <c r="AA55">
+      <c r="AD55">
         <v>5.183290707587383</v>
+      </c>
+      <c r="AE55">
+        <v>8.0825</v>
       </c>
     </row>
     <row r="56">
@@ -5147,79 +5797,91 @@
         </is>
       </c>
       <c r="C56">
+        <v>0.4581081081081081</v>
+      </c>
+      <c r="D56">
+        <v>0.581081081081081</v>
+      </c>
+      <c r="E56">
         <v>0.7792823290453622</v>
       </c>
-      <c r="D56">
+      <c r="F56">
+        <v>0.777027027027027</v>
+      </c>
+      <c r="G56">
         <v>2.216362407031778</v>
       </c>
-      <c r="E56">
+      <c r="H56">
         <v>2.216307277628032</v>
       </c>
-      <c r="F56">
+      <c r="I56">
         <v>1.833109017496635</v>
       </c>
-      <c r="G56">
+      <c r="J56">
         <v>1.748317631224765</v>
       </c>
-      <c r="H56">
+      <c r="K56">
         <v>1.767160161507402</v>
       </c>
-      <c r="I56">
+      <c r="L56">
         <v>4.208080808080808</v>
       </c>
-      <c r="J56">
+      <c r="M56">
         <v>2.4949358541526</v>
       </c>
-      <c r="K56">
+      <c r="N56">
         <v>2.394878706199461</v>
       </c>
-      <c r="L56">
+      <c r="O56">
         <v>4.584511784511784</v>
       </c>
-      <c r="M56">
+      <c r="P56">
         <v>4.478378378378379</v>
       </c>
-      <c r="N56">
+      <c r="Q56">
         <v>2.488888888888889</v>
       </c>
-      <c r="O56">
+      <c r="R56">
         <v>2.757596218771101</v>
       </c>
-      <c r="P56">
+      <c r="S56">
         <v>1.997983870967742</v>
       </c>
-      <c r="Q56">
+      <c r="T56">
         <v>2.319435104236718</v>
       </c>
-      <c r="R56">
+      <c r="U56">
         <v>1.895763281775387</v>
       </c>
-      <c r="S56">
+      <c r="V56">
         <v>1.85464333781965</v>
       </c>
-      <c r="T56">
+      <c r="W56">
         <v>2.464959568733154</v>
       </c>
-      <c r="U56">
+      <c r="X56">
         <v>2.289172831203766</v>
       </c>
-      <c r="V56">
+      <c r="Y56">
         <v>4.5</v>
       </c>
-      <c r="W56">
+      <c r="Z56">
         <v>0.4681421864520456</v>
       </c>
-      <c r="X56">
+      <c r="AA56">
         <v>46.21814543028686</v>
       </c>
-      <c r="Y56">
+      <c r="AB56">
         <v>1</v>
       </c>
-      <c r="Z56">
+      <c r="AC56">
         <v>3.159783344617468</v>
       </c>
-      <c r="AA56">
+      <c r="AD56">
         <v>4.735823882588392</v>
+      </c>
+      <c r="AE56">
+        <v>2.232</v>
       </c>
     </row>
     <row r="57">
@@ -5234,76 +5896,88 @@
         </is>
       </c>
       <c r="C57">
+        <v>0.9991666666666666</v>
+      </c>
+      <c r="D57">
+        <v>0.7625</v>
+      </c>
+      <c r="E57">
         <v>0.7933333333333333</v>
       </c>
-      <c r="D57">
+      <c r="F57">
+        <v>0.8658333333333333</v>
+      </c>
+      <c r="G57">
         <v>3.098333333333333</v>
       </c>
-      <c r="E57">
+      <c r="H57">
         <v>2.599166666666667</v>
       </c>
-      <c r="F57">
+      <c r="I57">
         <v>2.190833333333333</v>
       </c>
-      <c r="G57">
+      <c r="J57">
         <v>2.4225</v>
       </c>
-      <c r="H57">
+      <c r="K57">
         <v>2.255833333333333</v>
       </c>
-      <c r="J57">
+      <c r="M57">
         <v>2.106666666666666</v>
       </c>
-      <c r="K57">
+      <c r="N57">
         <v>2.333333333333333</v>
       </c>
-      <c r="L57">
+      <c r="O57">
         <v>2.365833333333333</v>
       </c>
-      <c r="M57">
+      <c r="P57">
         <v>2.130833333333333</v>
       </c>
-      <c r="N57">
+      <c r="Q57">
         <v>2.0825</v>
       </c>
-      <c r="O57">
+      <c r="R57">
         <v>2.353333333333333</v>
       </c>
-      <c r="P57">
+      <c r="S57">
         <v>2.296666666666667</v>
       </c>
-      <c r="Q57">
+      <c r="T57">
         <v>2.29</v>
       </c>
-      <c r="R57">
+      <c r="U57">
         <v>2.249166666666667</v>
       </c>
-      <c r="S57">
+      <c r="V57">
         <v>2.228333333333333</v>
       </c>
-      <c r="T57">
+      <c r="W57">
         <v>2.163333333333334</v>
       </c>
-      <c r="U57">
+      <c r="X57">
         <v>2.215</v>
       </c>
-      <c r="V57">
+      <c r="Y57">
         <v>2.463333333333333</v>
       </c>
-      <c r="W57">
+      <c r="Z57">
         <v>0.495</v>
       </c>
-      <c r="X57">
+      <c r="AA57">
         <v>41.065</v>
       </c>
-      <c r="Y57">
+      <c r="AB57">
         <v>0.995</v>
       </c>
-      <c r="Z57">
+      <c r="AC57">
         <v>5.252312867956266</v>
       </c>
-      <c r="AA57">
+      <c r="AD57">
         <v>5.644166666666667</v>
+      </c>
+      <c r="AE57">
+        <v>4.175</v>
       </c>
     </row>
     <row r="58">
@@ -5318,79 +5992,91 @@
         </is>
       </c>
       <c r="C58">
+        <v>0.997504159733777</v>
+      </c>
+      <c r="D58">
+        <v>0.9190317195325542</v>
+      </c>
+      <c r="E58">
         <v>0.9842061512884456</v>
       </c>
-      <c r="D58">
+      <c r="F58">
+        <v>0.9941763727121464</v>
+      </c>
+      <c r="G58">
         <v>2.763135946622185</v>
       </c>
-      <c r="E58">
+      <c r="H58">
         <v>2.120532003325021</v>
       </c>
-      <c r="F58">
+      <c r="I58">
         <v>1.530340814630091</v>
       </c>
-      <c r="G58">
+      <c r="J58">
         <v>1.920965058236273</v>
       </c>
-      <c r="H58">
+      <c r="K58">
         <v>1.738154613466334</v>
       </c>
-      <c r="I58">
+      <c r="L58">
         <v>1.412010008340284</v>
       </c>
-      <c r="J58">
+      <c r="M58">
         <v>1.671654197838736</v>
       </c>
-      <c r="K58">
+      <c r="N58">
         <v>2.667776852622814</v>
       </c>
-      <c r="L58">
+      <c r="O58">
         <v>4.140365448504983</v>
       </c>
-      <c r="M58">
+      <c r="P58">
         <v>1.537052456286428</v>
       </c>
-      <c r="N58">
+      <c r="Q58">
         <v>1.435215946843854</v>
       </c>
-      <c r="O58">
+      <c r="R58">
         <v>1.848459616985845</v>
       </c>
-      <c r="P58">
+      <c r="S58">
         <v>1.936046511627907</v>
       </c>
-      <c r="Q58">
+      <c r="T58">
         <v>3.004983388704319</v>
       </c>
-      <c r="R58">
+      <c r="U58">
         <v>1.487136929460581</v>
       </c>
-      <c r="S58">
+      <c r="V58">
         <v>1.348585690515807</v>
       </c>
-      <c r="T58">
+      <c r="W58">
         <v>1.369908561928512</v>
       </c>
-      <c r="U58">
+      <c r="X58">
         <v>1.349708576186511</v>
       </c>
-      <c r="V58">
+      <c r="Y58">
         <v>3.355241264559068</v>
       </c>
-      <c r="W58">
+      <c r="Z58">
         <v>0.4626865671641791</v>
       </c>
-      <c r="X58">
+      <c r="AA58">
         <v>43.16348547717843</v>
       </c>
-      <c r="Y58">
+      <c r="AB58">
         <v>0.9883817427385893</v>
       </c>
-      <c r="Z58">
+      <c r="AC58">
         <v>3.555369127516779</v>
       </c>
-      <c r="AA58">
+      <c r="AD58">
         <v>4.706766917293233</v>
+      </c>
+      <c r="AE58">
+        <v>4.059117402164863</v>
       </c>
     </row>
     <row r="59">
@@ -5405,73 +6091,85 @@
         </is>
       </c>
       <c r="C59">
+        <v>0.9531968240702048</v>
+      </c>
+      <c r="D59">
+        <v>0.938585345192715</v>
+      </c>
+      <c r="E59">
         <v>0.919714165615805</v>
       </c>
-      <c r="D59">
+      <c r="F59">
+        <v>0.9264087468460892</v>
+      </c>
+      <c r="G59">
         <v>1.89194826866917</v>
       </c>
-      <c r="E59">
+      <c r="H59">
         <v>2.096733668341709</v>
       </c>
-      <c r="F59">
+      <c r="I59">
         <v>1.610648918469218</v>
       </c>
-      <c r="G59">
+      <c r="J59">
         <v>1.686847599164927</v>
       </c>
-      <c r="H59">
+      <c r="K59">
         <v>1.650667779632721</v>
       </c>
-      <c r="I59">
+      <c r="L59">
         <v>2.077020736352095</v>
       </c>
-      <c r="J59">
+      <c r="M59">
         <v>1.853002939941201</v>
       </c>
-      <c r="K59">
+      <c r="N59">
         <v>2.572696534234996</v>
       </c>
-      <c r="L59">
+      <c r="O59">
         <v>4.402206194314807</v>
       </c>
-      <c r="M59">
+      <c r="P59">
         <v>2.349576271186441</v>
       </c>
-      <c r="N59">
+      <c r="Q59">
         <v>1.800501882057716</v>
       </c>
-      <c r="O59">
+      <c r="R59">
         <v>2.530322580645161</v>
       </c>
-      <c r="P59">
+      <c r="S59">
         <v>1.803831736776343</v>
       </c>
-      <c r="Q59">
+      <c r="T59">
         <v>2.093333333333333</v>
       </c>
-      <c r="R59">
+      <c r="U59">
         <v>1.954962468723937</v>
       </c>
-      <c r="T59">
+      <c r="W59">
         <v>2.346137610806247</v>
       </c>
-      <c r="V59">
+      <c r="Y59">
         <v>3.293967714528462</v>
       </c>
-      <c r="W59">
+      <c r="Z59">
         <v>0.4997929606625259</v>
       </c>
-      <c r="X59">
+      <c r="AA59">
         <v>38.83181441590721</v>
       </c>
-      <c r="Y59">
+      <c r="AB59">
         <v>0.9966873706004141</v>
       </c>
-      <c r="Z59">
+      <c r="AC59">
         <v>3.333748960931006</v>
       </c>
-      <c r="AA59">
+      <c r="AD59">
         <v>5.34349506225848</v>
+      </c>
+      <c r="AE59">
+        <v>4.059657905715477</v>
       </c>
     </row>
     <row r="60">
@@ -5486,79 +6184,91 @@
         </is>
       </c>
       <c r="C60">
+        <v>0.8166939443535188</v>
+      </c>
+      <c r="D60">
+        <v>0.5651105651105651</v>
+      </c>
+      <c r="E60">
         <v>0.6153846153846154</v>
       </c>
-      <c r="D60">
+      <c r="F60">
+        <v>0.6121112929623568</v>
+      </c>
+      <c r="G60">
         <v>3.001635322976288</v>
       </c>
-      <c r="E60">
+      <c r="H60">
         <v>2.239574816026165</v>
       </c>
-      <c r="F60">
+      <c r="I60">
         <v>1.423548650858545</v>
       </c>
-      <c r="G60">
+      <c r="J60">
         <v>1.748160261651676</v>
       </c>
-      <c r="H60">
+      <c r="K60">
         <v>1.573998364677024</v>
       </c>
-      <c r="I60">
+      <c r="L60">
         <v>4.351594439901881</v>
       </c>
-      <c r="J60">
+      <c r="M60">
         <v>3.159443990188062</v>
       </c>
-      <c r="K60">
+      <c r="N60">
         <v>3.395748160261652</v>
       </c>
-      <c r="L60">
+      <c r="O60">
         <v>5.014717906786591</v>
       </c>
-      <c r="M60">
+      <c r="P60">
         <v>5.174161896974653</v>
       </c>
-      <c r="N60">
+      <c r="Q60">
         <v>2.807849550286182</v>
       </c>
-      <c r="O60">
+      <c r="R60">
         <v>6.090760425183974</v>
       </c>
-      <c r="P60">
+      <c r="S60">
         <v>1.589533932951758</v>
       </c>
-      <c r="Q60">
+      <c r="T60">
         <v>4.247751430907604</v>
       </c>
-      <c r="R60">
+      <c r="U60">
         <v>1.626328699918234</v>
       </c>
-      <c r="S60">
+      <c r="V60">
         <v>1.364677023712183</v>
       </c>
-      <c r="T60">
+      <c r="W60">
         <v>3.335241210139003</v>
       </c>
-      <c r="U60">
+      <c r="X60">
         <v>1.654946852003271</v>
       </c>
-      <c r="V60">
+      <c r="Y60">
         <v>6.963175122749591</v>
       </c>
-      <c r="W60">
+      <c r="Z60">
         <v>0.4856909239574816</v>
       </c>
-      <c r="X60">
+      <c r="AA60">
         <v>48.28887070376432</v>
       </c>
-      <c r="Y60">
+      <c r="AB60">
         <v>0.9697465249386754</v>
       </c>
-      <c r="Z60">
+      <c r="AC60">
         <v>5.165302782324058</v>
       </c>
-      <c r="AA60">
+      <c r="AD60">
         <v>4.502861815208504</v>
+      </c>
+      <c r="AE60">
+        <v>2.592804578904333</v>
       </c>
     </row>
     <row r="61">
@@ -5573,79 +6283,91 @@
         </is>
       </c>
       <c r="C61">
+        <v>0.8399311531841652</v>
+      </c>
+      <c r="D61">
+        <v>0.5596707818930041</v>
+      </c>
+      <c r="E61">
         <v>0.5512953367875648</v>
       </c>
-      <c r="D61">
+      <c r="F61">
+        <v>0.5662525879917184</v>
+      </c>
+      <c r="G61">
         <v>3.402308326463314</v>
       </c>
-      <c r="E61">
+      <c r="H61">
         <v>3.614891913530825</v>
       </c>
-      <c r="F61">
+      <c r="I61">
         <v>1.955520254169976</v>
       </c>
-      <c r="G61">
+      <c r="J61">
         <v>3.088356729975227</v>
       </c>
-      <c r="H61">
+      <c r="K61">
         <v>2.465964343598055</v>
       </c>
-      <c r="I61">
+      <c r="L61">
         <v>2.732245681381958</v>
       </c>
-      <c r="J61">
+      <c r="M61">
         <v>2.945584299732382</v>
       </c>
-      <c r="K61">
+      <c r="N61">
         <v>4.055702917771884</v>
       </c>
-      <c r="L61">
+      <c r="O61">
         <v>5.682023486901536</v>
       </c>
-      <c r="M61">
+      <c r="P61">
         <v>5.945420906567993</v>
       </c>
-      <c r="N61">
+      <c r="Q61">
         <v>2.237931034482759</v>
       </c>
-      <c r="O61">
+      <c r="R61">
         <v>4.683778234086242</v>
       </c>
-      <c r="P61">
+      <c r="S61">
         <v>1.991967871485944</v>
       </c>
-      <c r="Q61">
+      <c r="T61">
         <v>2.448136142625608</v>
       </c>
-      <c r="R61">
+      <c r="U61">
         <v>2.097991967871486</v>
       </c>
-      <c r="S61">
+      <c r="V61">
         <v>1.821630347054076</v>
       </c>
-      <c r="T61">
+      <c r="W61">
         <v>3.801675977653631</v>
       </c>
-      <c r="U61">
+      <c r="X61">
         <v>2.165400843881856</v>
       </c>
-      <c r="V61">
+      <c r="Y61">
         <v>4.460727969348659</v>
       </c>
-      <c r="W61">
+      <c r="Z61">
         <v>0.4065166795965865</v>
       </c>
-      <c r="X61">
+      <c r="AA61">
         <v>47.57253685027153</v>
       </c>
-      <c r="Y61">
+      <c r="AB61">
         <v>0.9572317262830482</v>
       </c>
-      <c r="Z61">
+      <c r="AC61">
         <v>5.897496087636933</v>
       </c>
-      <c r="AA61">
+      <c r="AD61">
         <v>4.480971659919028</v>
+      </c>
+      <c r="AE61">
+        <v>6.189773844641102</v>
       </c>
     </row>
     <row r="62">
@@ -5660,79 +6382,91 @@
         </is>
       </c>
       <c r="C62">
+        <v>0.7289340101522843</v>
+      </c>
+      <c r="D62">
+        <v>0.5016008537886874</v>
+      </c>
+      <c r="E62">
         <v>0.2805005213764338</v>
       </c>
-      <c r="D62">
+      <c r="F62">
+        <v>0.5294725956566702</v>
+      </c>
+      <c r="G62">
         <v>2.638232271325796</v>
       </c>
-      <c r="E62">
+      <c r="H62">
         <v>2.509297520661157</v>
       </c>
-      <c r="F62">
+      <c r="I62">
         <v>1.770475227502528</v>
       </c>
-      <c r="G62">
+      <c r="J62">
         <v>2.03763987792472</v>
       </c>
-      <c r="H62">
+      <c r="K62">
         <v>1.594262295081967</v>
       </c>
-      <c r="I62">
+      <c r="L62">
         <v>6.831154684095861</v>
       </c>
-      <c r="J62">
+      <c r="M62">
         <v>4.452554744525547</v>
       </c>
-      <c r="K62">
+      <c r="N62">
         <v>4.81139896373057</v>
       </c>
-      <c r="L62">
+      <c r="O62">
         <v>7.312108559498956</v>
       </c>
-      <c r="M62">
+      <c r="P62">
         <v>7.201047120418848</v>
       </c>
-      <c r="N62">
+      <c r="Q62">
         <v>3.180873180873181</v>
       </c>
-      <c r="O62">
+      <c r="R62">
         <v>5.467941507311586</v>
       </c>
-      <c r="P62">
+      <c r="S62">
         <v>1.393969849246231</v>
       </c>
-      <c r="Q62">
+      <c r="T62">
         <v>2.284561049445005</v>
       </c>
-      <c r="R62">
+      <c r="U62">
         <v>1.783838383838384</v>
       </c>
-      <c r="S62">
+      <c r="V62">
         <v>1.623601220752798</v>
       </c>
-      <c r="T62">
+      <c r="W62">
         <v>5.239704329461457</v>
       </c>
-      <c r="U62">
+      <c r="X62">
         <v>1.927477017364658</v>
       </c>
-      <c r="V62">
+      <c r="Y62">
         <v>3.749488752556237</v>
       </c>
-      <c r="W62">
+      <c r="Z62">
         <v>0.316</v>
       </c>
-      <c r="X62">
+      <c r="AA62">
         <v>49.83</v>
       </c>
-      <c r="Y62">
+      <c r="AB62">
         <v>0.970970970970971</v>
       </c>
-      <c r="Z62">
+      <c r="AC62">
         <v>4.342685370741483</v>
       </c>
-      <c r="AA62">
+      <c r="AD62">
         <v>5.007201646090535</v>
+      </c>
+      <c r="AE62">
+        <v>8.30784708249497</v>
       </c>
     </row>
     <row r="63">
@@ -5747,79 +6481,91 @@
         </is>
       </c>
       <c r="C63">
+        <v>0.7902534113060429</v>
+      </c>
+      <c r="D63">
+        <v>0.6945871197155274</v>
+      </c>
+      <c r="E63">
         <v>0.6603250099088387</v>
       </c>
-      <c r="D63">
+      <c r="F63">
+        <v>0.6538007089405278</v>
+      </c>
+      <c r="G63">
         <v>2.530763239875389</v>
       </c>
-      <c r="E63">
+      <c r="H63">
         <v>2.932632398753894</v>
       </c>
-      <c r="F63">
+      <c r="I63">
         <v>1.892133956386293</v>
       </c>
-      <c r="G63">
+      <c r="J63">
         <v>2.110031104199067</v>
       </c>
-      <c r="H63">
+      <c r="K63">
         <v>1.771206225680934</v>
       </c>
-      <c r="I63">
+      <c r="L63">
         <v>6.496865203761756</v>
       </c>
-      <c r="J63">
+      <c r="M63">
         <v>3.835216205687573</v>
       </c>
-      <c r="K63">
+      <c r="N63">
         <v>5.067004285157772</v>
       </c>
-      <c r="L63">
+      <c r="O63">
         <v>6.597432905484247</v>
       </c>
-      <c r="M63">
+      <c r="P63">
         <v>6.715009746588694</v>
       </c>
-      <c r="N63">
+      <c r="Q63">
         <v>3.333333333333333</v>
       </c>
-      <c r="O63">
+      <c r="R63">
         <v>5.384315255559891</v>
       </c>
-      <c r="P63">
+      <c r="S63">
         <v>1.414396887159533</v>
       </c>
-      <c r="Q63">
+      <c r="T63">
         <v>1.991054064566317</v>
       </c>
-      <c r="R63">
+      <c r="U63">
         <v>2.406152647975078</v>
       </c>
-      <c r="S63">
+      <c r="V63">
         <v>1.556420233463035</v>
       </c>
-      <c r="T63">
+      <c r="W63">
         <v>5.77561355668095</v>
       </c>
-      <c r="U63">
+      <c r="X63">
         <v>2.221269964939618</v>
       </c>
-      <c r="V63">
+      <c r="Y63">
         <v>5.511301636788776</v>
       </c>
-      <c r="W63">
+      <c r="Z63">
         <v>0.5354391371340523</v>
       </c>
-      <c r="X63">
+      <c r="AA63">
         <v>43.42218798151001</v>
       </c>
-      <c r="Y63">
+      <c r="AB63">
         <v>0.8943217665615142</v>
       </c>
-      <c r="Z63">
+      <c r="AC63">
         <v>5.882123341139734</v>
       </c>
-      <c r="AA63">
+      <c r="AD63">
         <v>5.051221434200158</v>
+      </c>
+      <c r="AE63">
+        <v>7.714172917489143</v>
       </c>
     </row>
     <row r="64">
@@ -5834,76 +6580,88 @@
         </is>
       </c>
       <c r="C64">
+        <v>0.9812855980471928</v>
+      </c>
+      <c r="D64">
+        <v>0.8631669535283993</v>
+      </c>
+      <c r="E64">
         <v>0.900523560209424</v>
       </c>
-      <c r="D64">
+      <c r="F64">
+        <v>0.9154443485763589</v>
+      </c>
+      <c r="G64">
         <v>3.133671742808799</v>
       </c>
-      <c r="E64">
+      <c r="H64">
         <v>5.57189811010682</v>
       </c>
-      <c r="F64">
+      <c r="I64">
         <v>1.992628992628993</v>
       </c>
-      <c r="G64">
+      <c r="J64">
         <v>3.284426229508197</v>
       </c>
-      <c r="H64">
+      <c r="K64">
         <v>2.068908941755538</v>
       </c>
-      <c r="J64">
+      <c r="M64">
         <v>1.984387838948233</v>
       </c>
-      <c r="K64">
+      <c r="N64">
         <v>2.88934764657308</v>
       </c>
-      <c r="L64">
+      <c r="O64">
         <v>3.408381265406738</v>
       </c>
-      <c r="M64">
+      <c r="P64">
         <v>2.329166666666667</v>
       </c>
-      <c r="N64">
+      <c r="Q64">
         <v>2.099337748344371</v>
       </c>
-      <c r="O64">
+      <c r="R64">
         <v>2.711489361702128</v>
       </c>
-      <c r="P64">
+      <c r="S64">
         <v>2.435177539223782</v>
       </c>
-      <c r="Q64">
+      <c r="T64">
         <v>2.66885784716516</v>
       </c>
-      <c r="R64">
+      <c r="U64">
         <v>2.038587848932676</v>
       </c>
-      <c r="S64">
+      <c r="V64">
         <v>1.809958506224066</v>
       </c>
-      <c r="T64">
+      <c r="W64">
         <v>1.909991742361685</v>
       </c>
-      <c r="U64">
+      <c r="X64">
         <v>1.813798836242726</v>
       </c>
-      <c r="V64">
+      <c r="Y64">
         <v>2.710570469798658</v>
       </c>
-      <c r="W64">
+      <c r="Z64">
         <v>0.5072</v>
       </c>
-      <c r="X64">
+      <c r="AA64">
         <v>35.9031224979984</v>
       </c>
-      <c r="Y64">
+      <c r="AB64">
         <v>0.9888</v>
       </c>
-      <c r="Z64">
+      <c r="AC64">
         <v>5.800670016750419</v>
       </c>
-      <c r="AA64">
+      <c r="AD64">
         <v>5.642282958199357</v>
+      </c>
+      <c r="AE64">
+        <v>7.526612903225806</v>
       </c>
     </row>
     <row r="65">
@@ -5918,79 +6676,91 @@
         </is>
       </c>
       <c r="C65">
+        <v>0.9764705882352941</v>
+      </c>
+      <c r="D65">
+        <v>0.5722689075630252</v>
+      </c>
+      <c r="E65">
         <v>0.5798319327731093</v>
       </c>
-      <c r="D65">
+      <c r="F65">
+        <v>0.7831932773109244</v>
+      </c>
+      <c r="G65">
         <v>4.169747899159664</v>
       </c>
-      <c r="E65">
+      <c r="H65">
         <v>3.08655462184874</v>
       </c>
-      <c r="F65">
+      <c r="I65">
         <v>1.899159663865546</v>
       </c>
-      <c r="G65">
+      <c r="J65">
         <v>2.214285714285714</v>
       </c>
-      <c r="H65">
+      <c r="K65">
         <v>2.112605042016807</v>
       </c>
-      <c r="I65">
+      <c r="L65">
         <v>4.180672268907563</v>
       </c>
-      <c r="J65">
+      <c r="M65">
         <v>3.285714285714286</v>
       </c>
-      <c r="K65">
+      <c r="N65">
         <v>2.842016806722689</v>
       </c>
-      <c r="L65">
+      <c r="O65">
         <v>5.526890756302521</v>
       </c>
-      <c r="M65">
+      <c r="P65">
         <v>5.226050420168067</v>
       </c>
-      <c r="N65">
+      <c r="Q65">
         <v>2.404201680672269</v>
       </c>
-      <c r="O65">
+      <c r="R65">
         <v>3.332197614991482</v>
       </c>
-      <c r="P65">
+      <c r="S65">
         <v>2.099159663865546</v>
       </c>
-      <c r="Q65">
+      <c r="T65">
         <v>3.576470588235294</v>
       </c>
-      <c r="R65">
+      <c r="U65">
         <v>2.37563025210084</v>
       </c>
-      <c r="S65">
+      <c r="V65">
         <v>2.10672268907563</v>
       </c>
-      <c r="T65">
+      <c r="W65">
         <v>4.530252100840336</v>
       </c>
-      <c r="U65">
+      <c r="X65">
         <v>2.378991596638655</v>
       </c>
-      <c r="V65">
+      <c r="Y65">
         <v>3.33109243697479</v>
       </c>
-      <c r="W65">
+      <c r="Z65">
         <v>0.4798319327731093</v>
       </c>
-      <c r="X65">
+      <c r="AA65">
         <v>38.30924369747899</v>
       </c>
-      <c r="Y65">
+      <c r="AB65">
         <v>0.9882352941176471</v>
       </c>
-      <c r="Z65">
+      <c r="AC65">
         <v>4.111858704793945</v>
       </c>
-      <c r="AA65">
+      <c r="AD65">
         <v>4.478991596638656</v>
+      </c>
+      <c r="AE65">
+        <v>7.632773109243698</v>
       </c>
     </row>
     <row r="66">
@@ -6005,79 +6775,91 @@
         </is>
       </c>
       <c r="C66">
+        <v>0.485</v>
+      </c>
+      <c r="D66">
+        <v>0.3408333333333333</v>
+      </c>
+      <c r="E66">
         <v>0.2983333333333333</v>
       </c>
-      <c r="D66">
+      <c r="F66">
+        <v>0.3016666666666667</v>
+      </c>
+      <c r="G66">
         <v>4.524166666666667</v>
       </c>
-      <c r="E66">
+      <c r="H66">
         <v>3.424166666666667</v>
       </c>
-      <c r="F66">
+      <c r="I66">
         <v>2.495</v>
       </c>
-      <c r="G66">
+      <c r="J66">
         <v>2.8325</v>
       </c>
-      <c r="H66">
+      <c r="K66">
         <v>2.8975</v>
       </c>
-      <c r="I66">
+      <c r="L66">
         <v>5.6425</v>
       </c>
-      <c r="J66">
+      <c r="M66">
         <v>3.946666666666667</v>
       </c>
-      <c r="K66">
+      <c r="N66">
         <v>4.1675</v>
       </c>
-      <c r="L66">
+      <c r="O66">
         <v>5.233333333333333</v>
       </c>
-      <c r="M66">
+      <c r="P66">
         <v>5.526666666666666</v>
       </c>
-      <c r="N66">
+      <c r="Q66">
         <v>4.469166666666666</v>
       </c>
-      <c r="O66">
+      <c r="R66">
         <v>4.883333333333334</v>
       </c>
-      <c r="P66">
+      <c r="S66">
         <v>2.801666666666667</v>
       </c>
-      <c r="Q66">
+      <c r="T66">
         <v>4.541666666666667</v>
       </c>
-      <c r="R66">
+      <c r="U66">
         <v>3.0475</v>
       </c>
-      <c r="S66">
+      <c r="V66">
         <v>3.095</v>
       </c>
-      <c r="T66">
+      <c r="W66">
         <v>4.900833333333333</v>
       </c>
-      <c r="U66">
+      <c r="X66">
         <v>3.336666666666666</v>
       </c>
-      <c r="V66">
+      <c r="Y66">
         <v>4.1725</v>
       </c>
-      <c r="W66">
+      <c r="Z66">
         <v>0.4541666666666667</v>
       </c>
-      <c r="X66">
+      <c r="AA66">
         <v>37.8925</v>
       </c>
-      <c r="Y66">
+      <c r="AB66">
         <v>1</v>
       </c>
-      <c r="Z66">
+      <c r="AC66">
         <v>4.234166666666667</v>
       </c>
-      <c r="AA66">
+      <c r="AD66">
         <v>5.105833333333333</v>
+      </c>
+      <c r="AE66">
+        <v>7.341666666666667</v>
       </c>
     </row>
     <row r="67">
@@ -6092,79 +6874,91 @@
         </is>
       </c>
       <c r="C67">
+        <v>0.9983539094650206</v>
+      </c>
+      <c r="D67">
+        <v>0.7913907284768212</v>
+      </c>
+      <c r="E67">
         <v>0.7035803497085762</v>
       </c>
-      <c r="D67">
+      <c r="F67">
+        <v>0.9453189726594863</v>
+      </c>
+      <c r="G67">
         <v>2.216171617161716</v>
       </c>
-      <c r="E67">
+      <c r="H67">
         <v>2.099752679307502</v>
       </c>
-      <c r="F67">
+      <c r="I67">
         <v>1.679571663920923</v>
       </c>
-      <c r="G67">
+      <c r="J67">
         <v>1.855144032921811</v>
       </c>
-      <c r="H67">
+      <c r="K67">
         <v>1.915156507413509</v>
       </c>
-      <c r="I67">
+      <c r="L67">
         <v>1.716996699669967</v>
       </c>
-      <c r="J67">
+      <c r="M67">
         <v>1.797530864197531</v>
       </c>
-      <c r="K67">
+      <c r="N67">
         <v>1.769991755976917</v>
       </c>
-      <c r="L67">
+      <c r="O67">
         <v>2.714756801319044</v>
       </c>
-      <c r="M67">
+      <c r="P67">
         <v>2.360628618693135</v>
       </c>
-      <c r="N67">
+      <c r="Q67">
         <v>1.647155812036274</v>
       </c>
-      <c r="O67">
+      <c r="R67">
         <v>1.887510339123242</v>
       </c>
-      <c r="P67">
+      <c r="S67">
         <v>1.903465346534653</v>
       </c>
-      <c r="Q67">
+      <c r="T67">
         <v>4.328073089700997</v>
       </c>
-      <c r="R67">
+      <c r="U67">
         <v>1.738664468260511</v>
       </c>
-      <c r="S67">
+      <c r="V67">
         <v>1.776218001651528</v>
       </c>
-      <c r="T67">
+      <c r="W67">
         <v>1.964550700741962</v>
       </c>
-      <c r="U67">
+      <c r="X67">
         <v>1.703305785123967</v>
       </c>
-      <c r="V67">
+      <c r="Y67">
         <v>2.473118279569892</v>
       </c>
-      <c r="W67">
+      <c r="Z67">
         <v>0.4938271604938271</v>
       </c>
-      <c r="X67">
+      <c r="AA67">
         <v>39.1494632535095</v>
       </c>
-      <c r="Y67">
+      <c r="AB67">
         <v>0.9934102141680395</v>
       </c>
-      <c r="Z67">
+      <c r="AC67">
         <v>3.452596867271228</v>
       </c>
-      <c r="AA67">
+      <c r="AD67">
         <v>3.462489694971146</v>
+      </c>
+      <c r="AE67">
+        <v>7.351440329218107</v>
       </c>
     </row>
   </sheetData>
